--- a/deliverables/绿城·潮鸣外滩-营销验收单（甲方交付）.xlsx
+++ b/deliverables/绿城·潮鸣外滩-营销验收单（甲方交付）.xlsx
@@ -7,21 +7,24 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="营销验收单" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="权益核验清单" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="效果评估表" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="赞助权益执行回执" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="绿城·潮鸣外滩露出" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="照片索引" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="按重要顺序分类" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="权益核验清单" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="效果评估表" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="赞助权益执行回执" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="绿城·潮鸣外滩露出" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="照片索引" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'营销验收单'!$A$2:$D$18</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'权益核验清单'!$A$1:$F$24</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="2">'效果评估表'!$A$1:$D$22</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="3">'赞助权益执行回执'!$A$1:$D$21</definedName>
-    <definedName name="_xlnm.Print_Titles" localSheetId="4">'绿城·潮鸣外滩露出'!$1:$2</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="4">'绿城·潮鸣外滩露出'!$A$1:$D$23</definedName>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="5" hidden="1">'照片索引'!$A$3:$F$21</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="5">'照片索引'!$A$1:$F$21</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="1">'按重要顺序分类'!$1:$2</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'按重要顺序分类'!$A$1:$D$35</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="2">'权益核验清单'!$A$1:$F$29</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="3">'效果评估表'!$A$1:$D$22</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="4">'赞助权益执行回执'!$A$1:$D$21</definedName>
+    <definedName name="_xlnm.Print_Titles" localSheetId="5">'绿城·潮鸣外滩露出'!$1:$2</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="5">'绿城·潮鸣外滩露出'!$A$1:$D$30</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="6" hidden="1">'照片索引'!$A$3:$G$21</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="6">'照片索引'!$A$1:$G$21</definedName>
   </definedNames>
   <calcPr calcId="191029" fullCalcOnLoad="1"/>
 </workbook>
@@ -30,7 +33,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="45">
+  <fonts count="50">
     <font>
       <name val="等线"/>
       <charset val="134"/>
@@ -267,6 +270,33 @@
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="10"/>
+    </font>
+    <font>
+      <name val="微软雅黑"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="微软雅黑"/>
+      <b val="1"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="微软雅黑"/>
+      <color rgb="00000000"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="黑体"/>
+      <b val="1"/>
+      <sz val="13"/>
+    </font>
+    <font>
+      <name val="黑体"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="13"/>
     </font>
     <font>
       <name val="黑体"/>
@@ -530,12 +560,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFF8E1"/>
+        <fgColor rgb="00F5F5F5"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00F5F5F5"/>
+        <fgColor rgb="00FFF8E1"/>
       </patternFill>
     </fill>
   </fills>
@@ -1130,7 +1160,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="77">
+  <cellXfs count="96">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1229,6 +1259,56 @@
     <xf numFmtId="0" fontId="35" fillId="34" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="36" fillId="34" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="35" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="35" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="36" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="36" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="37" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="37" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="37" fillId="33" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="33" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="36" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="36" borderId="27" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="40" fillId="34" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="29" fillId="36" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="35" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="36" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="37" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="37" borderId="27" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="39" fillId="33" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="29" fillId="33" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -1241,32 +1321,29 @@
     <xf numFmtId="0" fontId="31" fillId="36" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="37" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="31" fillId="38" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="36" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="36" borderId="27" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="37" fillId="34" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="42" fillId="34" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="35" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="37" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="28" fillId="38" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="38" borderId="27" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="27" fillId="35" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="36" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="38" fillId="33" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="43" fillId="33" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="39" fillId="33" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="44" fillId="33" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="29" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -1276,30 +1353,30 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="34" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="35" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="37" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="40" fillId="33" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="45" fillId="33" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="28" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="38" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="27" fillId="38" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="27" fillId="37" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="40" fillId="33" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="45" fillId="33" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="38" fillId="37" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="43" fillId="38" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="37" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="29" fillId="38" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="42" fillId="36" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="47" fillId="36" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="33" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="43" fillId="34" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="48" fillId="34" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="27" fillId="36" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1308,7 +1385,13 @@
     <xf numFmtId="0" fontId="27" fillId="33" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="26" fillId="36" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="37" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="26" fillId="33" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="29" fillId="36" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1607,10 +1690,10 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>13</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1600200" cy="1123950"/>
+      <row>12</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1771650" cy="1257300"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -1632,10 +1715,10 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>13</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1600200" cy="1123950"/>
+      <row>12</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1771650" cy="1257300"/>
     <pic>
       <nvPicPr>
         <cNvPr id="2" name="Image 2" descr="Picture"/>
@@ -1657,10 +1740,10 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>13</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1600200" cy="1123950"/>
+      <row>12</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1771650" cy="1257300"/>
     <pic>
       <nvPicPr>
         <cNvPr id="3" name="Image 3" descr="Picture"/>
@@ -1682,10 +1765,10 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>13</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1600200" cy="1123950"/>
+      <row>12</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1771650" cy="1257300"/>
     <pic>
       <nvPicPr>
         <cNvPr id="4" name="Image 4" descr="Picture"/>
@@ -1707,10 +1790,10 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>16</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1600200" cy="1123950"/>
+      <row>17</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1771650" cy="1257300"/>
     <pic>
       <nvPicPr>
         <cNvPr id="5" name="Image 5" descr="Picture"/>
@@ -1732,10 +1815,10 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>16</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1600200" cy="1123950"/>
+      <row>17</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1771650" cy="1257300"/>
     <pic>
       <nvPicPr>
         <cNvPr id="6" name="Image 6" descr="Picture"/>
@@ -1757,10 +1840,10 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>16</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1600200" cy="1123950"/>
+      <row>17</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1771650" cy="1257300"/>
     <pic>
       <nvPicPr>
         <cNvPr id="7" name="Image 7" descr="Picture"/>
@@ -1782,10 +1865,10 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>16</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1600200" cy="1123950"/>
+      <row>17</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1771650" cy="1257300"/>
     <pic>
       <nvPicPr>
         <cNvPr id="8" name="Image 8" descr="Picture"/>
@@ -1807,10 +1890,10 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>19</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1600200" cy="1123950"/>
+      <row>22</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1771650" cy="1257300"/>
     <pic>
       <nvPicPr>
         <cNvPr id="9" name="Image 9" descr="Picture"/>
@@ -1832,10 +1915,10 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>19</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1600200" cy="1123950"/>
+      <row>22</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1771650" cy="1257300"/>
     <pic>
       <nvPicPr>
         <cNvPr id="10" name="Image 10" descr="Picture"/>
@@ -1855,19 +1938,69 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>22</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1771650" cy="1257300"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="11" name="Image 11" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId11"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>22</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1771650" cy="1257300"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="12" name="Image 12" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId12"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>22</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1600200" cy="1123950"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="11" name="Image 11" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId11"/>
+      <row>27</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1771650" cy="1257300"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="13" name="Image 13" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId13"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -1882,17 +2015,17 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>22</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1600200" cy="1123950"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="12" name="Image 12" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId12"/>
+      <row>27</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1771650" cy="1257300"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="14" name="Image 14" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId14"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -1907,42 +2040,92 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>22</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1600200" cy="1123950"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="13" name="Image 13" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId13"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>3</col>
-      <colOff>0</colOff>
-      <row>22</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1600200" cy="1123950"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="14" name="Image 14" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId14"/>
+      <row>27</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1771650" cy="1257300"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="15" name="Image 15" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId15"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>32</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1771650" cy="1257300"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="16" name="Image 16" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId16"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>32</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1771650" cy="1257300"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="17" name="Image 17" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId17"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>32</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1771650" cy="1257300"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="18" name="Image 18" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId18"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -1960,19 +2143,69 @@
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>13</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1600200" cy="1123950"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>5</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="3238500" cy="2667000"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="1" name="Image 1" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+      <row>13</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1600200" cy="1123950"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId2"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>13</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1600200" cy="1123950"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId3"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -1987,17 +2220,42 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>5</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="2381250" cy="2667000"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="2" name="Image 2" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId2"/>
+      <row>13</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1600200" cy="1123950"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId4"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>15</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1600200" cy="1123950"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId5"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -2012,17 +2270,92 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>9</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="3238500" cy="2667000"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="3" name="Image 3" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId3"/>
+      <row>15</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1600200" cy="1123950"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId6"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>18</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1600200" cy="1123950"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId7"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>18</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1600200" cy="1123950"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId8"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>18</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1600200" cy="1123950"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="9" name="Image 9" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId9"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -2037,17 +2370,267 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>9</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="2381250" cy="2667000"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="4" name="Image 4" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId4"/>
+      <row>18</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1600200" cy="1123950"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="10" name="Image 10" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId10"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>20</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1600200" cy="1123950"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="11" name="Image 11" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId11"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>20</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1600200" cy="1123950"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="12" name="Image 12" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId12"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>20</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1600200" cy="1123950"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="13" name="Image 13" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId13"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>20</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1600200" cy="1123950"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="14" name="Image 14" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId14"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>23</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1600200" cy="1123950"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="15" name="Image 15" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId15"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>23</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1600200" cy="1123950"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="16" name="Image 16" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId16"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>27</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1600200" cy="1123950"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="17" name="Image 17" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId17"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>27</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1600200" cy="1123950"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="18" name="Image 18" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId18"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>27</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1600200" cy="1123950"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="19" name="Image 19" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId19"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>27</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1600200" cy="1123950"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="20" name="Image 20" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId20"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -2065,12 +2648,12 @@
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
-      <col>0</col>
-      <colOff>0</colOff>
-      <row>19</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1600200" cy="1123950"/>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>5</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3238500" cy="2667000"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -2090,37 +2673,37 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>5</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2381250" cy="2667000"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId2"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>19</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1600200" cy="1123950"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="2" name="Image 2" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId2"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>0</colOff>
-      <row>19</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1600200" cy="1123950"/>
+      <row>9</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="3238500" cy="2667000"/>
     <pic>
       <nvPicPr>
         <cNvPr id="3" name="Image 3" descr="Picture"/>
@@ -2142,10 +2725,10 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>19</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1600200" cy="1123950"/>
+      <row>9</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2381250" cy="2667000"/>
     <pic>
       <nvPicPr>
         <cNvPr id="4" name="Image 4" descr="Picture"/>
@@ -2172,7 +2755,112 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>3</row>
+      <row>19</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1600200" cy="1123950"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>19</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1600200" cy="1123950"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId2"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>19</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1600200" cy="1123950"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId3"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>3</col>
+      <colOff>0</colOff>
+      <row>19</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1600200" cy="1123950"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId4"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
+</file>
+
+<file path=xl/drawings/drawing6.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>4</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="2762250" cy="1952625"/>
@@ -2197,7 +2885,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>3</row>
+      <row>4</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="2762250" cy="1952625"/>
@@ -2222,7 +2910,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>5</row>
+      <row>6</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="2762250" cy="1952625"/>
@@ -2247,7 +2935,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>5</row>
+      <row>6</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="2762250" cy="1952625"/>
@@ -2272,7 +2960,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>7</row>
+      <row>9</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="2762250" cy="1952625"/>
@@ -2297,7 +2985,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>7</row>
+      <row>9</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="2762250" cy="1952625"/>
@@ -2322,7 +3010,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>9</row>
+      <row>11</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="2762250" cy="1952625"/>
@@ -2347,7 +3035,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>9</row>
+      <row>11</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="2762250" cy="1952625"/>
@@ -2372,7 +3060,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>11</row>
+      <row>14</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="2762250" cy="1952625"/>
@@ -2397,7 +3085,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>11</row>
+      <row>14</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="2762250" cy="1952625"/>
@@ -2422,7 +3110,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>13</row>
+      <row>16</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="2762250" cy="1952625"/>
@@ -2447,7 +3135,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>13</row>
+      <row>16</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="2762250" cy="1952625"/>
@@ -2472,7 +3160,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>15</row>
+      <row>19</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="2762250" cy="1952625"/>
@@ -2497,7 +3185,7 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>15</row>
+      <row>19</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="2762250" cy="1952625"/>
@@ -2522,7 +3210,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>17</row>
+      <row>21</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="2762250" cy="1952625"/>
@@ -2545,19 +3233,44 @@
   </oneCellAnchor>
   <oneCellAnchor>
     <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>24</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="2762250" cy="1952625"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="16" name="Image 16" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId16"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>17</row>
+      <row>24</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="2762250" cy="1952625"/>
     <pic>
       <nvPicPr>
-        <cNvPr id="16" name="Image 16" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId16"/>
+        <cNvPr id="17" name="Image 17" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId17"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -2572,32 +3285,7 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>19</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="2762250" cy="1952625"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="17" name="Image 17" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId17"/>
-        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
-          <a:fillRect/>
-        </a:stretch>
-      </blipFill>
-      <spPr>
-        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
-      </spPr>
-    </pic>
-    <clientData/>
-  </oneCellAnchor>
-  <oneCellAnchor>
-    <from>
-      <col>2</col>
-      <colOff>0</colOff>
-      <row>19</row>
+      <row>26</row>
       <rowOff>0</rowOff>
     </from>
     <ext cx="2762250" cy="1952625"/>
@@ -3065,7 +3753,7 @@
       </c>
       <c r="B13" s="32" t="inlineStr">
         <is>
-          <t>【露出】本页 9 张均为绿城 / 潮鸣可核验露出，含图注；更多大图见「绿城·潮鸣外滩露出」页。
+          <t>【露出】本页 9 张为封面摘要；全部 18 张已按一级至五级嵌入「按重要顺序分类」。
 【营销评估】非常好（☐）　良好（☑）　一般（☐）　较差（☐）
 【打包验收】四模块整体打包。参观邀约无单独成片、朋友圈九宫格 / 回顾视频未附本表，见「权益核验清单」黄底项。已核验露出效果良好，符合约定要求。</t>
         </is>
@@ -3106,7 +3794,7 @@
       </c>
       <c r="D15" s="23" t="n"/>
     </row>
-    <row r="16" ht="92" customHeight="1" s="17">
+    <row r="16" ht="108" customHeight="1" s="17">
       <c r="A16" s="13" t="inlineStr">
         <is>
           <t>附件</t>
@@ -3114,7 +3802,7 @@
       </c>
       <c r="B16" s="33" t="inlineStr">
         <is>
-          <t>①本页 9 张均为绿城 / 潮鸣可辨露出，含图注；②「权益核验清单」按报价单 4 模块对照照片；③「绿城·潮鸣外滩露出」页为精华大图；④「效果评估表」按绿城中国策划活动类效果评估表结构；⑤「赞助权益执行回执」供绿城复核盖章；⑥「照片索引」含拍摄时间与模块对照；⑦拍立享直播 https://live.pailixiang.com/album/a12523836160（相册约 425 张，本表为精华筛选）；⑧全程录像 https://pan.baidu.com/s/1S8cNdqnCR_anuVPD6vlhjg 提取码 8888；⑨费用清单（经办人签字）。本表不与 2026年3月开盘花束验收混用。未把美年大健康 / 泰隆银行 / 腾讯云 / 蔚来展位当作绿城露出。</t>
+          <t>①本页 9 张为封面摘要，含图注；②「按重要顺序分类」将 18 张精华图全部按五级嵌入表格；③「权益核验清单」按报价单 4 模块嵌全部对应照片；④「绿城·潮鸣外滩露出」为大图（同序分级）；⑤「效果评估表」按绿城中国策划活动类效果评估表结构；⑥「赞助权益执行回执」供绿城复核盖章；⑦「照片索引」含重要等级、拍摄时间与模块对照；⑧拍立享直播 https://live.pailixiang.com/album/a12523836160（相册约 425 张，本表为精华筛选）；⑨全程录像 https://pan.baidu.com/s/1S8cNdqnCR_anuVPD6vlhjg 提取码 8888。本表不与 2026年3月开盘花束验收混用。未把美年大健康 / 泰隆银行 / 腾讯云 / 蔚来展位当作绿城露出。</t>
         </is>
       </c>
       <c r="C16" s="22" t="n"/>
@@ -3217,11 +3905,443 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
+    <tabColor rgb="001F6B4A"/>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
+  <dimension ref="A1:D34"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="28" customWidth="1" style="17" min="1" max="1"/>
+    <col width="28" customWidth="1" style="17" min="2" max="2"/>
+    <col width="28" customWidth="1" style="17" min="3" max="3"/>
+    <col width="28" customWidth="1" style="17" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1" ht="32" customHeight="1" s="17">
+      <c r="A1" s="37" t="inlineStr">
+        <is>
+          <t>绿城·潮鸣外滩 · 精华照片按重要顺序分类（18 张全部嵌入本表）</t>
+        </is>
+      </c>
+      <c r="B1" s="38" t="n"/>
+      <c r="C1" s="38" t="n"/>
+      <c r="D1" s="38" t="n"/>
+    </row>
+    <row r="2" ht="36" customHeight="1" s="17">
+      <c r="A2" s="39" t="inlineStr">
+        <is>
+          <t>排序：一级核心品牌露出 → 二级主会场执行 → 三级冠名位合影 → 四级主办致辞 → 五级晚宴氛围。只收录绿城 / 潮鸣 / GREENTOWN 可核验露出。本页表格已嵌入全部精华原图，可直接给甲方按等级复核。</t>
+        </is>
+      </c>
+      <c r="B2" s="40" t="n"/>
+      <c r="C2" s="40" t="n"/>
+      <c r="D2" s="40" t="n"/>
+    </row>
+    <row r="3" ht="22" customHeight="1" s="17">
+      <c r="A3" s="41" t="inlineStr">
+        <is>
+          <t>重要等级</t>
+        </is>
+      </c>
+      <c r="B3" s="41" t="inlineStr">
+        <is>
+          <t>分类</t>
+        </is>
+      </c>
+      <c r="C3" s="41" t="inlineStr">
+        <is>
+          <t>张数</t>
+        </is>
+      </c>
+      <c r="D3" s="41" t="inlineStr">
+        <is>
+          <t>核验要点</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="36" customHeight="1" s="17">
+      <c r="A4" s="41" t="inlineStr">
+        <is>
+          <t>一级</t>
+        </is>
+      </c>
+      <c r="B4" s="41" t="inlineStr">
+        <is>
+          <t>核心品牌露出（必看）</t>
+        </is>
+      </c>
+      <c r="C4" s="41" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D4" s="42" t="inlineStr">
+        <is>
+          <t>绿城 / 潮鸣 / GREENTOWN 字样可直接核验，对应报价主体，建议甲方优先复核。</t>
+        </is>
+      </c>
+    </row>
+    <row r="5" ht="36" customHeight="1" s="17">
+      <c r="A5" s="43" t="inlineStr">
+        <is>
+          <t>二级</t>
+        </is>
+      </c>
+      <c r="B5" s="43" t="inlineStr">
+        <is>
+          <t>主会场执行（重点）</t>
+        </is>
+      </c>
+      <c r="C5" s="43" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D5" s="44" t="inlineStr">
+        <is>
+          <t>展台接待、双屏、主持、主视觉，证明主会场权益已落地。</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="36" customHeight="1" s="17">
+      <c r="A6" s="45" t="inlineStr">
+        <is>
+          <t>三级</t>
+        </is>
+      </c>
+      <c r="B6" s="45" t="inlineStr">
+        <is>
+          <t>冠名位合影核验</t>
+        </is>
+      </c>
+      <c r="C6" s="45" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="D6" s="46" t="inlineStr">
+        <is>
+          <t>主背景板合影，可复核晚宴冠名位「绿城中国」。</t>
+        </is>
+      </c>
+    </row>
+    <row r="7" ht="36" customHeight="1" s="17">
+      <c r="A7" s="47" t="inlineStr">
+        <is>
+          <t>四级</t>
+        </is>
+      </c>
+      <c r="B7" s="47" t="inlineStr">
+        <is>
+          <t>主办致辞现场</t>
+        </is>
+      </c>
+      <c r="C7" s="47" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D7" s="48" t="inlineStr">
+        <is>
+          <t>主会场致辞与讲台，补充现场执行；不作参观邀约专项成片。</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="36" customHeight="1" s="17">
+      <c r="A8" s="49" t="inlineStr">
+        <is>
+          <t>五级</t>
+        </is>
+      </c>
+      <c r="B8" s="49" t="inlineStr">
+        <is>
+          <t>冠名晚宴氛围</t>
+        </is>
+      </c>
+      <c r="C8" s="49" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="D8" s="50" t="inlineStr">
+        <is>
+          <t>江景厅冠名晚宴现场。席卡为嘉宾姓名卡，不作「潮鳴」logo 桌卡证据。</t>
+        </is>
+      </c>
+    </row>
+    <row r="9" ht="24" customHeight="1" s="17">
+      <c r="A9" s="51" t="inlineStr">
+        <is>
+          <t>合计 18 张，全部按上表顺序嵌在下方各分类单元格中。参观邀约 / 证书 / 朋友圈无成片，不在本页拔高。</t>
+        </is>
+      </c>
+      <c r="B9" s="52" t="n"/>
+      <c r="C9" s="52" t="n"/>
+      <c r="D9" s="52" t="n"/>
+    </row>
+    <row r="11" ht="26" customHeight="1" s="17">
+      <c r="A11" s="53" t="inlineStr">
+        <is>
+          <t>一级｜核心品牌露出（必看）（4 张）</t>
+        </is>
+      </c>
+      <c r="B11" s="38" t="n"/>
+      <c r="C11" s="38" t="n"/>
+      <c r="D11" s="38" t="n"/>
+    </row>
+    <row r="12" ht="22" customHeight="1" s="17">
+      <c r="A12" s="54" t="inlineStr">
+        <is>
+          <t>绿城 / 潮鸣 / GREENTOWN 字样可直接核验，对应报价主体，建议甲方优先复核。</t>
+        </is>
+      </c>
+      <c r="B12" s="52" t="n"/>
+      <c r="C12" s="52" t="n"/>
+      <c r="D12" s="52" t="n"/>
+    </row>
+    <row r="13" ht="132" customHeight="1" s="17">
+      <c r="A13" s="25" t="n"/>
+      <c r="B13" s="25" t="n"/>
+      <c r="C13" s="25" t="n"/>
+      <c r="D13" s="25" t="n"/>
+    </row>
+    <row r="14" ht="36" customHeight="1" s="17">
+      <c r="A14" s="29" t="inlineStr">
+        <is>
+          <t>议程看板【绿城·潮鸣】星耀北外滩晚宴</t>
+        </is>
+      </c>
+      <c r="B14" s="29" t="inlineStr">
+        <is>
+          <t>主背景板：晚宴冠名战略合作伙伴·绿城中国</t>
+        </is>
+      </c>
+      <c r="C14" s="29" t="inlineStr">
+        <is>
+          <t>展台立牌：绿城中国 GREENTOWN</t>
+        </is>
+      </c>
+      <c r="D14" s="29" t="inlineStr">
+        <is>
+          <t>晚宴大屏播放绿城中国品牌片</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="26" customHeight="1" s="17">
+      <c r="A16" s="55" t="inlineStr">
+        <is>
+          <t>二级｜主会场执行（重点）（4 张）</t>
+        </is>
+      </c>
+      <c r="B16" s="40" t="n"/>
+      <c r="C16" s="40" t="n"/>
+      <c r="D16" s="40" t="n"/>
+    </row>
+    <row r="17" ht="22" customHeight="1" s="17">
+      <c r="A17" s="54" t="inlineStr">
+        <is>
+          <t>展台接待、双屏、主持、主视觉，证明主会场权益已落地。</t>
+        </is>
+      </c>
+      <c r="B17" s="52" t="n"/>
+      <c r="C17" s="52" t="n"/>
+      <c r="D17" s="52" t="n"/>
+    </row>
+    <row r="18" ht="132" customHeight="1" s="17">
+      <c r="A18" s="25" t="n"/>
+      <c r="B18" s="25" t="n"/>
+      <c r="C18" s="25" t="n"/>
+      <c r="D18" s="25" t="n"/>
+    </row>
+    <row r="19" ht="36" customHeight="1" s="17">
+      <c r="A19" s="29" t="inlineStr">
+        <is>
+          <t>展台接待：绿城立牌、礼袋与物料</t>
+        </is>
+      </c>
+      <c r="B19" s="29" t="inlineStr">
+        <is>
+          <t>主会场双屏同款主视觉（含晚宴冠名·绿城中国）</t>
+        </is>
+      </c>
+      <c r="C19" s="29" t="inlineStr">
+        <is>
+          <t>主持现场：主会场露出</t>
+        </is>
+      </c>
+      <c r="D19" s="29" t="inlineStr">
+        <is>
+          <t>主视觉 KV：战略合作名单含绿城中国</t>
+        </is>
+      </c>
+    </row>
+    <row r="21" ht="26" customHeight="1" s="17">
+      <c r="A21" s="56" t="inlineStr">
+        <is>
+          <t>三级｜冠名位合影核验（4 张）</t>
+        </is>
+      </c>
+      <c r="B21" s="52" t="n"/>
+      <c r="C21" s="52" t="n"/>
+      <c r="D21" s="52" t="n"/>
+    </row>
+    <row r="22" ht="22" customHeight="1" s="17">
+      <c r="A22" s="54" t="inlineStr">
+        <is>
+          <t>主背景板合影，可复核晚宴冠名位「绿城中国」。</t>
+        </is>
+      </c>
+      <c r="B22" s="52" t="n"/>
+      <c r="C22" s="52" t="n"/>
+      <c r="D22" s="52" t="n"/>
+    </row>
+    <row r="23" ht="132" customHeight="1" s="17">
+      <c r="A23" s="25" t="n"/>
+      <c r="B23" s="25" t="n"/>
+      <c r="C23" s="25" t="n"/>
+      <c r="D23" s="25" t="n"/>
+    </row>
+    <row r="24" ht="36" customHeight="1" s="17">
+      <c r="A24" s="29" t="inlineStr">
+        <is>
+          <t>主背景板合影核验冠名位</t>
+        </is>
+      </c>
+      <c r="B24" s="29" t="inlineStr">
+        <is>
+          <t>主背景板合影（冠名位特写）</t>
+        </is>
+      </c>
+      <c r="C24" s="29" t="inlineStr">
+        <is>
+          <t>主背景板双人合影核验冠名位</t>
+        </is>
+      </c>
+      <c r="D24" s="29" t="inlineStr">
+        <is>
+          <t>主背景板合影：晚宴冠名战略合作伙伴·绿城中国</t>
+        </is>
+      </c>
+    </row>
+    <row r="26" ht="26" customHeight="1" s="17">
+      <c r="A26" s="57" t="inlineStr">
+        <is>
+          <t>四级｜主办致辞现场（3 张）</t>
+        </is>
+      </c>
+      <c r="B26" s="58" t="n"/>
+      <c r="C26" s="58" t="n"/>
+      <c r="D26" s="58" t="n"/>
+    </row>
+    <row r="27" ht="22" customHeight="1" s="17">
+      <c r="A27" s="54" t="inlineStr">
+        <is>
+          <t>主会场致辞与讲台，补充现场执行；不作参观邀约专项成片。</t>
+        </is>
+      </c>
+      <c r="B27" s="52" t="n"/>
+      <c r="C27" s="52" t="n"/>
+      <c r="D27" s="52" t="n"/>
+    </row>
+    <row r="28" ht="132" customHeight="1" s="17">
+      <c r="A28" s="25" t="n"/>
+      <c r="B28" s="25" t="n"/>
+      <c r="C28" s="25" t="n"/>
+      <c r="D28" s="25" t="n"/>
+    </row>
+    <row r="29" ht="36" customHeight="1" s="17">
+      <c r="A29" s="29" t="inlineStr">
+        <is>
+          <t>主办致辞全景：主会场双屏与讲台</t>
+        </is>
+      </c>
+      <c r="B29" s="29" t="inlineStr">
+        <is>
+          <t>主办致辞：姚志勇，主会场主视觉</t>
+        </is>
+      </c>
+      <c r="C29" s="29" t="inlineStr">
+        <is>
+          <t>主办致辞讲台特写</t>
+        </is>
+      </c>
+      <c r="D29" s="25" t="n"/>
+    </row>
+    <row r="31" ht="26" customHeight="1" s="17">
+      <c r="A31" s="59" t="inlineStr">
+        <is>
+          <t>五级｜冠名晚宴氛围（3 张）</t>
+        </is>
+      </c>
+      <c r="B31" s="25" t="n"/>
+      <c r="C31" s="25" t="n"/>
+      <c r="D31" s="25" t="n"/>
+    </row>
+    <row r="32" ht="22" customHeight="1" s="17">
+      <c r="A32" s="54" t="inlineStr">
+        <is>
+          <t>江景厅冠名晚宴现场。席卡为嘉宾姓名卡，不作「潮鳴」logo 桌卡证据。</t>
+        </is>
+      </c>
+      <c r="B32" s="52" t="n"/>
+      <c r="C32" s="52" t="n"/>
+      <c r="D32" s="52" t="n"/>
+    </row>
+    <row r="33" ht="132" customHeight="1" s="17">
+      <c r="A33" s="25" t="n"/>
+      <c r="B33" s="25" t="n"/>
+      <c r="C33" s="25" t="n"/>
+      <c r="D33" s="25" t="n"/>
+    </row>
+    <row r="34" ht="36" customHeight="1" s="17">
+      <c r="A34" s="29" t="inlineStr">
+        <is>
+          <t>冠名晚宴合影（江景厅）</t>
+        </is>
+      </c>
+      <c r="B34" s="29" t="inlineStr">
+        <is>
+          <t>冠名晚宴桌次（江景厅圆桌）</t>
+        </is>
+      </c>
+      <c r="C34" s="29" t="inlineStr">
+        <is>
+          <t>冠名晚宴现场举杯</t>
+        </is>
+      </c>
+      <c r="D34" s="25" t="n"/>
+    </row>
+  </sheetData>
+  <mergeCells count="13">
+    <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A17:D17"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A27:D27"/>
+    <mergeCell ref="A31:D31"/>
+    <mergeCell ref="A22:D22"/>
+    <mergeCell ref="A12:D12"/>
+    <mergeCell ref="A26:D26"/>
+    <mergeCell ref="A21:D21"/>
+    <mergeCell ref="A2:D2"/>
+    <mergeCell ref="A11:D11"/>
+    <mergeCell ref="A16:D16"/>
+    <mergeCell ref="A32:D32"/>
+  </mergeCells>
+  <pageMargins left="0.5" right="0.5" top="0.55" bottom="0.55" header="0.2" footer="0.2"/>
+  <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
     <tabColor rgb="00FFF8E1"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F24"/>
+  <dimension ref="A1:F29"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="6" customWidth="1" style="17" min="1" max="1"/>
@@ -3247,7 +4367,7 @@
     <row r="2" ht="36" customHeight="1" s="17">
       <c r="A2" s="39" t="inlineStr">
         <is>
-          <t>活动：2026-05-22 上海·北外滩·一滴水　身份：晚宴冠名战略合作伙伴　金额：含税 ¥100,000（报价单 4 模块整体打包，不拆子项验收）　依据：绿城中国-潮鸣外滩-10万元晚宴冠名服务报价单　本页照片已嵌进表格，可直接给甲方核对。</t>
+          <t>活动：2026-05-22 上海·北外滩·一滴水　身份：晚宴冠名战略合作伙伴　金额：含税 ¥100,000（报价单 4 模块整体打包，不拆子项验收）　依据：绿城中国-潮鸣外滩-10万元晚宴冠名服务报价单　本页按四模块嵌全部对应照片；若按重要程度查阅，见工作表「按重要顺序分类」。</t>
         </is>
       </c>
       <c r="B2" s="40" t="n"/>
@@ -3289,213 +4409,213 @@
       </c>
     </row>
     <row r="4" ht="76" customHeight="1" s="17">
-      <c r="A4" s="42" t="inlineStr">
+      <c r="A4" s="60" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B4" s="43" t="inlineStr">
+      <c r="B4" s="61" t="inlineStr">
         <is>
           <t>晚宴冠名和专属权益</t>
         </is>
       </c>
-      <c r="C4" s="44" t="inlineStr">
+      <c r="C4" s="62" t="inlineStr">
         <is>
           <t>晚宴主题冠名、专场PPT/视频、主持人口播、席卡等物料植入</t>
         </is>
       </c>
-      <c r="D4" s="43" t="inlineStr">
+      <c r="D4" s="61" t="inlineStr">
         <is>
           <t>55,000</t>
         </is>
       </c>
-      <c r="E4" s="44" t="inlineStr">
+      <c r="E4" s="62" t="inlineStr">
         <is>
           <t>图①议程看板晚宴冠名【绿城·潮鸣】；图②⑤主背景板「晚宴冠名战略合作伙伴·绿城中国」；图⑧晚宴大屏播放绿城中国品牌片（理想生活综合服务商 / LIGHT HEAT POWER）。现场席卡为嘉宾姓名卡，相册未见单独「潮鳴」logo 桌卡特写。</t>
         </is>
       </c>
-      <c r="F4" s="45" t="inlineStr">
+      <c r="F4" s="63" t="inlineStr">
         <is>
           <t>通过（冠名/品牌片）</t>
         </is>
       </c>
     </row>
     <row r="5" ht="76" customHeight="1" s="17">
-      <c r="A5" s="42" t="inlineStr">
+      <c r="A5" s="60" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B5" s="43" t="inlineStr">
+      <c r="B5" s="61" t="inlineStr">
         <is>
           <t>主会场权益</t>
         </is>
       </c>
-      <c r="C5" s="44" t="inlineStr">
+      <c r="C5" s="62" t="inlineStr">
         <is>
           <t>1号位展台、手拎袋项目物料、视频轮播/奖项颁发画面</t>
         </is>
       </c>
-      <c r="D5" s="43" t="inlineStr">
+      <c r="D5" s="61" t="inlineStr">
         <is>
           <t>30,000</t>
         </is>
       </c>
-      <c r="E5" s="44" t="inlineStr">
+      <c r="E5" s="62" t="inlineStr">
         <is>
           <t>图③展台立牌「绿城中国 GREENTOWN」；图④展台接待（礼袋与物料）；图⑥主会场双屏同款主视觉；图⑨主视觉KV含绿城中国。奖项颁发证书未见特写。</t>
         </is>
       </c>
-      <c r="F5" s="45" t="inlineStr">
+      <c r="F5" s="63" t="inlineStr">
         <is>
           <t>通过（展台/双屏）</t>
         </is>
       </c>
     </row>
     <row r="6" ht="76" customHeight="1" s="17">
-      <c r="A6" s="42" t="inlineStr">
+      <c r="A6" s="60" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B6" s="43" t="inlineStr">
+      <c r="B6" s="61" t="inlineStr">
         <is>
           <t>专场项目参观邀约</t>
         </is>
       </c>
-      <c r="C6" s="44" t="inlineStr">
+      <c r="C6" s="62" t="inlineStr">
         <is>
           <t>论坛/颁奖结束后主持人口播 + 动线引导，邀约前往案场</t>
         </is>
       </c>
-      <c r="D6" s="43" t="inlineStr">
+      <c r="D6" s="61" t="inlineStr">
         <is>
           <t>5,000</t>
         </is>
       </c>
-      <c r="E6" s="44" t="inlineStr">
+      <c r="E6" s="62" t="inlineStr">
         <is>
           <t>图⑦证明主会场主持人口播位已具备。相册未见「参观邀约 / 案场接驳」专项成片，请以全程录像及现场执行回执为准。</t>
         </is>
       </c>
-      <c r="F6" s="46" t="inlineStr">
+      <c r="F6" s="64" t="inlineStr">
         <is>
           <t>待录像核验</t>
         </is>
       </c>
     </row>
     <row r="7" ht="76" customHeight="1" s="17">
-      <c r="A7" s="42" t="inlineStr">
+      <c r="A7" s="60" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B7" s="43" t="inlineStr">
+      <c r="B7" s="61" t="inlineStr">
         <is>
           <t>宣发配合</t>
         </is>
       </c>
-      <c r="C7" s="44" t="inlineStr">
+      <c r="C7" s="62" t="inlineStr">
         <is>
           <t>现场摄影、朋友圈九宫格、回顾视频项目鸣谢、执行回执</t>
         </is>
       </c>
-      <c r="D7" s="43" t="inlineStr">
+      <c r="D7" s="61" t="inlineStr">
         <is>
           <t>10,000</t>
         </is>
       </c>
-      <c r="E7" s="44" t="inlineStr">
+      <c r="E7" s="62" t="inlineStr">
         <is>
           <t>现场摄影：本表精华照片 + 拍立享约 425 张 + 网盘录像。本工作簿「赞助权益执行回执」即执行报告。朋友圈九宫格、回顾视频片头鸣谢未附，不以照片推定已发。</t>
         </is>
       </c>
-      <c r="F7" s="46" t="inlineStr">
+      <c r="F7" s="64" t="inlineStr">
         <is>
           <t>摄影通过；其余待补</t>
         </is>
       </c>
     </row>
     <row r="8" ht="76" customHeight="1" s="17">
-      <c r="A8" s="42" t="inlineStr">
+      <c r="A8" s="60" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="B8" s="43" t="inlineStr">
+      <c r="B8" s="61" t="inlineStr">
         <is>
           <t>合计（含税）</t>
         </is>
       </c>
-      <c r="C8" s="44" t="inlineStr">
+      <c r="C8" s="62" t="inlineStr">
         <is>
           <t>4 模块整体打包，一次性验收</t>
         </is>
       </c>
-      <c r="D8" s="43" t="inlineStr">
+      <c r="D8" s="61" t="inlineStr">
         <is>
           <t>100,000</t>
         </is>
       </c>
-      <c r="E8" s="44" t="inlineStr">
+      <c r="E8" s="62" t="inlineStr">
         <is>
           <t>已核验项以绿城 / 潮鸣字样可辨露出为准；黄底项需录像或另行回执，不在本表拔高为已完成。</t>
         </is>
       </c>
-      <c r="F8" s="46" t="inlineStr">
+      <c r="F8" s="64" t="inlineStr">
         <is>
           <t>主体已交，部分待补</t>
         </is>
       </c>
     </row>
     <row r="9" ht="76" customHeight="1" s="17">
-      <c r="A9" s="42" t="inlineStr">
+      <c r="A9" s="60" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="B9" s="43" t="inlineStr">
+      <c r="B9" s="61" t="inlineStr">
         <is>
           <t>证书</t>
         </is>
       </c>
-      <c r="C9" s="44" t="inlineStr">
+      <c r="C9" s="62" t="inlineStr">
         <is>
           <t>2026年度智慧人居新质资产领军企业 暨卓越战略合作伙伴</t>
         </is>
       </c>
-      <c r="D9" s="43" t="inlineStr">
+      <c r="D9" s="61" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E9" s="44" t="inlineStr">
+      <c r="E9" s="62" t="inlineStr">
         <is>
           <t>事项描述已载明颁发。本相册未见证书 / 颁奖特写，不作为已交付证据。</t>
         </is>
       </c>
-      <c r="F9" s="46" t="inlineStr">
+      <c r="F9" s="64" t="inlineStr">
         <is>
           <t>待补照片</t>
         </is>
       </c>
     </row>
     <row r="10" ht="48" customHeight="1" s="17">
-      <c r="A10" s="47" t="inlineStr">
+      <c r="A10" s="54" t="inlineStr">
         <is>
           <t>验收口径：报价单约定「不逐项贴照片、四模块整体打包」。本清单把精华照片映射到模块，便于甲方复核，不等于把未成片的子项改成已交付。营销评估预勾「良好」，请绿城营销负责人复核签字。本清单仅对应 2026-05-22 峰会，不与 3 月开盘花束验收混用。</t>
         </is>
       </c>
-      <c r="B10" s="48" t="n"/>
-      <c r="C10" s="48" t="n"/>
-      <c r="D10" s="48" t="n"/>
-      <c r="E10" s="48" t="n"/>
-      <c r="F10" s="48" t="n"/>
+      <c r="B10" s="52" t="n"/>
+      <c r="C10" s="52" t="n"/>
+      <c r="D10" s="52" t="n"/>
+      <c r="E10" s="52" t="n"/>
+      <c r="F10" s="52" t="n"/>
     </row>
     <row r="12" ht="24" customHeight="1" s="17">
-      <c r="A12" s="49" t="inlineStr">
-        <is>
-          <t>四模块现场证据照片（已嵌入本表，可直接给甲方核对）</t>
+      <c r="A12" s="65" t="inlineStr">
+        <is>
+          <t>四模块现场证据照片（各模块全部对应图已嵌入，可直接给甲方核对）</t>
         </is>
       </c>
       <c r="B12" s="38" t="n"/>
@@ -3505,9 +4625,9 @@
       <c r="F12" s="38" t="n"/>
     </row>
     <row r="13" ht="22" customHeight="1" s="17">
-      <c r="A13" s="50" t="inlineStr">
-        <is>
-          <t>1. 晚宴冠名和专属权益　¥55,000　☑ 已执行（冠名 / 品牌片）</t>
+      <c r="A13" s="66" t="inlineStr">
+        <is>
+          <t>1. 晚宴冠名和专属权益　¥55,000　☑ 已执行（冠名 / 品牌片）　本模块 6 张（全部嵌入）</t>
         </is>
       </c>
       <c r="B13" s="40" t="n"/>
@@ -3524,7 +4644,7 @@
       <c r="E14" s="25" t="n"/>
       <c r="F14" s="25" t="n"/>
     </row>
-    <row r="15" ht="32" customHeight="1" s="17">
+    <row r="15" ht="36" customHeight="1" s="17">
       <c r="A15" s="29" t="inlineStr">
         <is>
           <t>议程看板【绿城·潮鸣】晚宴</t>
@@ -3548,152 +4668,209 @@
       <c r="E15" s="25" t="n"/>
       <c r="F15" s="25" t="n"/>
     </row>
-    <row r="16" ht="22" customHeight="1" s="17">
-      <c r="A16" s="50" t="inlineStr">
-        <is>
-          <t>2. 主会场权益　¥30,000　☑ 已执行（展台 / 双屏）</t>
-        </is>
-      </c>
-      <c r="B16" s="40" t="n"/>
-      <c r="C16" s="40" t="n"/>
-      <c r="D16" s="40" t="n"/>
-      <c r="E16" s="40" t="n"/>
-      <c r="F16" s="40" t="n"/>
-    </row>
-    <row r="17" ht="118" customHeight="1" s="17">
-      <c r="A17" s="25" t="n"/>
-      <c r="B17" s="25" t="n"/>
+    <row r="16" ht="118" customHeight="1" s="17">
+      <c r="A16" s="25" t="n"/>
+      <c r="B16" s="25" t="n"/>
+      <c r="C16" s="25" t="n"/>
+      <c r="D16" s="25" t="n"/>
+      <c r="E16" s="25" t="n"/>
+      <c r="F16" s="25" t="n"/>
+    </row>
+    <row r="17" ht="36" customHeight="1" s="17">
+      <c r="A17" s="29" t="inlineStr">
+        <is>
+          <t>冠名晚宴现场举杯</t>
+        </is>
+      </c>
+      <c r="B17" s="29" t="inlineStr">
+        <is>
+          <t>冠名晚宴桌次（江景厅）</t>
+        </is>
+      </c>
       <c r="C17" s="25" t="n"/>
       <c r="D17" s="25" t="n"/>
       <c r="E17" s="25" t="n"/>
       <c r="F17" s="25" t="n"/>
     </row>
-    <row r="18" ht="32" customHeight="1" s="17">
-      <c r="A18" s="29" t="inlineStr">
+    <row r="18" ht="22" customHeight="1" s="17">
+      <c r="A18" s="66" t="inlineStr">
+        <is>
+          <t>2. 主会场权益　¥30,000　☑ 已执行（展台 / 双屏）　本模块 8 张（全部嵌入）</t>
+        </is>
+      </c>
+      <c r="B18" s="40" t="n"/>
+      <c r="C18" s="40" t="n"/>
+      <c r="D18" s="40" t="n"/>
+      <c r="E18" s="40" t="n"/>
+      <c r="F18" s="40" t="n"/>
+    </row>
+    <row r="19" ht="118" customHeight="1" s="17">
+      <c r="A19" s="25" t="n"/>
+      <c r="B19" s="25" t="n"/>
+      <c r="C19" s="25" t="n"/>
+      <c r="D19" s="25" t="n"/>
+      <c r="E19" s="25" t="n"/>
+      <c r="F19" s="25" t="n"/>
+    </row>
+    <row r="20" ht="36" customHeight="1" s="17">
+      <c r="A20" s="29" t="inlineStr">
         <is>
           <t>展台立牌：绿城中国 GREENTOWN</t>
         </is>
       </c>
-      <c r="B18" s="29" t="inlineStr">
+      <c r="B20" s="29" t="inlineStr">
         <is>
           <t>展台接待：礼袋与物料</t>
         </is>
       </c>
-      <c r="C18" s="29" t="inlineStr">
+      <c r="C20" s="29" t="inlineStr">
         <is>
           <t>主会场双屏同款主视觉</t>
         </is>
       </c>
-      <c r="D18" s="29" t="inlineStr">
+      <c r="D20" s="29" t="inlineStr">
         <is>
           <t>主视觉 KV 含绿城中国</t>
         </is>
       </c>
-      <c r="E18" s="25" t="n"/>
-      <c r="F18" s="25" t="n"/>
-    </row>
-    <row r="19" ht="22" customHeight="1" s="17">
-      <c r="A19" s="50" t="inlineStr">
-        <is>
-          <t>3. 专场项目参观邀约　¥5,000　☐ 待录像核验（无专项成片）</t>
-        </is>
-      </c>
-      <c r="B19" s="40" t="n"/>
-      <c r="C19" s="40" t="n"/>
-      <c r="D19" s="40" t="n"/>
-      <c r="E19" s="40" t="n"/>
-      <c r="F19" s="40" t="n"/>
-    </row>
-    <row r="20" ht="118" customHeight="1" s="17">
-      <c r="A20" s="25" t="n"/>
-      <c r="B20" s="25" t="n"/>
-      <c r="C20" s="25" t="n"/>
-      <c r="D20" s="25" t="n"/>
       <c r="E20" s="25" t="n"/>
       <c r="F20" s="25" t="n"/>
     </row>
-    <row r="21" ht="32" customHeight="1" s="17">
-      <c r="A21" s="29" t="inlineStr">
-        <is>
-          <t>主持口播位已具备</t>
-        </is>
-      </c>
-      <c r="B21" s="29" t="inlineStr">
-        <is>
-          <t>主背景板冠名位（非参观成片）</t>
-        </is>
-      </c>
-      <c r="C21" s="51" t="inlineStr">
-        <is>
-          <t>（无更多成片）</t>
-        </is>
-      </c>
-      <c r="D21" s="51" t="inlineStr">
-        <is>
-          <t>（无更多成片）</t>
-        </is>
-      </c>
-      <c r="E21" s="51" t="inlineStr">
-        <is>
-          <t>相册未见参观 / 接驳专项成片</t>
-        </is>
-      </c>
+    <row r="21" ht="118" customHeight="1" s="17">
+      <c r="A21" s="25" t="n"/>
+      <c r="B21" s="25" t="n"/>
+      <c r="C21" s="25" t="n"/>
+      <c r="D21" s="25" t="n"/>
+      <c r="E21" s="25" t="n"/>
       <c r="F21" s="25" t="n"/>
     </row>
-    <row r="22" ht="22" customHeight="1" s="17">
-      <c r="A22" s="50" t="inlineStr">
-        <is>
-          <t>4. 宣发配合　¥10,000　☑ 现场摄影已交　☐ 朋友圈 / 回顾视频待补</t>
-        </is>
-      </c>
-      <c r="B22" s="40" t="n"/>
-      <c r="C22" s="40" t="n"/>
-      <c r="D22" s="40" t="n"/>
-      <c r="E22" s="40" t="n"/>
-      <c r="F22" s="40" t="n"/>
-    </row>
-    <row r="23" ht="118" customHeight="1" s="17">
-      <c r="A23" s="25" t="n"/>
-      <c r="B23" s="25" t="n"/>
-      <c r="C23" s="25" t="n"/>
-      <c r="D23" s="25" t="n"/>
-      <c r="E23" s="25" t="n"/>
-      <c r="F23" s="25" t="n"/>
-    </row>
-    <row r="24" ht="32" customHeight="1" s="17">
-      <c r="A24" s="29" t="inlineStr">
-        <is>
-          <t>主背景板合影（执行回执用）</t>
-        </is>
-      </c>
-      <c r="B24" s="29" t="inlineStr">
-        <is>
-          <t>主办致辞现场</t>
-        </is>
-      </c>
-      <c r="C24" s="29" t="inlineStr">
-        <is>
-          <t>冠名晚宴桌次</t>
-        </is>
-      </c>
-      <c r="D24" s="29" t="inlineStr">
-        <is>
-          <t>主背景板合影核验冠名</t>
-        </is>
-      </c>
+    <row r="22" ht="36" customHeight="1" s="17">
+      <c r="A22" s="29" t="inlineStr">
+        <is>
+          <t>主持现场</t>
+        </is>
+      </c>
+      <c r="B22" s="29" t="inlineStr">
+        <is>
+          <t>主办致辞全景</t>
+        </is>
+      </c>
+      <c r="C22" s="29" t="inlineStr">
+        <is>
+          <t>主办致辞：姚志勇</t>
+        </is>
+      </c>
+      <c r="D22" s="29" t="inlineStr">
+        <is>
+          <t>主办致辞讲台特写</t>
+        </is>
+      </c>
+      <c r="E22" s="25" t="n"/>
+      <c r="F22" s="25" t="n"/>
+    </row>
+    <row r="23" ht="22" customHeight="1" s="17">
+      <c r="A23" s="66" t="inlineStr">
+        <is>
+          <t>3. 专场项目参观邀约　¥5,000　☐ 待录像核验（无专项成片）　本模块 2 张（全部嵌入）</t>
+        </is>
+      </c>
+      <c r="B23" s="40" t="n"/>
+      <c r="C23" s="40" t="n"/>
+      <c r="D23" s="40" t="n"/>
+      <c r="E23" s="40" t="n"/>
+      <c r="F23" s="40" t="n"/>
+    </row>
+    <row r="24" ht="118" customHeight="1" s="17">
+      <c r="A24" s="25" t="n"/>
+      <c r="B24" s="25" t="n"/>
+      <c r="C24" s="25" t="n"/>
+      <c r="D24" s="25" t="n"/>
       <c r="E24" s="25" t="n"/>
       <c r="F24" s="25" t="n"/>
     </row>
+    <row r="25" ht="36" customHeight="1" s="17">
+      <c r="A25" s="29" t="inlineStr">
+        <is>
+          <t>主持口播位已具备</t>
+        </is>
+      </c>
+      <c r="B25" s="29" t="inlineStr">
+        <is>
+          <t>主背景板冠名位（非参观成片）</t>
+        </is>
+      </c>
+      <c r="C25" s="25" t="n"/>
+      <c r="D25" s="25" t="n"/>
+      <c r="E25" s="25" t="n"/>
+      <c r="F25" s="25" t="n"/>
+    </row>
+    <row r="26" ht="28" customHeight="1" s="17">
+      <c r="A26" s="67" t="inlineStr">
+        <is>
+          <t>相册未见参观 / 接驳专项成片。上图仅证明主持口播位与冠名位，不作为参观邀约已完成证据。</t>
+        </is>
+      </c>
+      <c r="B26" s="68" t="n"/>
+      <c r="C26" s="68" t="n"/>
+      <c r="D26" s="68" t="n"/>
+      <c r="E26" s="68" t="n"/>
+      <c r="F26" s="68" t="n"/>
+    </row>
+    <row r="27" ht="22" customHeight="1" s="17">
+      <c r="A27" s="66" t="inlineStr">
+        <is>
+          <t>4. 宣发配合　¥10,000　☑ 现场摄影已交　☐ 朋友圈 / 回顾视频待补　本模块 4 张（全部嵌入）</t>
+        </is>
+      </c>
+      <c r="B27" s="40" t="n"/>
+      <c r="C27" s="40" t="n"/>
+      <c r="D27" s="40" t="n"/>
+      <c r="E27" s="40" t="n"/>
+      <c r="F27" s="40" t="n"/>
+    </row>
+    <row r="28" ht="118" customHeight="1" s="17">
+      <c r="A28" s="25" t="n"/>
+      <c r="B28" s="25" t="n"/>
+      <c r="C28" s="25" t="n"/>
+      <c r="D28" s="25" t="n"/>
+      <c r="E28" s="25" t="n"/>
+      <c r="F28" s="25" t="n"/>
+    </row>
+    <row r="29" ht="36" customHeight="1" s="17">
+      <c r="A29" s="29" t="inlineStr">
+        <is>
+          <t>主背景板合影（执行回执用）</t>
+        </is>
+      </c>
+      <c r="B29" s="29" t="inlineStr">
+        <is>
+          <t>主背景板双人合影核验冠名</t>
+        </is>
+      </c>
+      <c r="C29" s="29" t="inlineStr">
+        <is>
+          <t>主背景板合影核验冠名</t>
+        </is>
+      </c>
+      <c r="D29" s="29" t="inlineStr">
+        <is>
+          <t>冠名晚宴桌次</t>
+        </is>
+      </c>
+      <c r="E29" s="25" t="n"/>
+      <c r="F29" s="25" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="8">
+  <mergeCells count="9">
     <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A16:F16"/>
     <mergeCell ref="A10:F10"/>
     <mergeCell ref="A13:F13"/>
-    <mergeCell ref="A19:F19"/>
     <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A22:F22"/>
+    <mergeCell ref="A23:F23"/>
+    <mergeCell ref="A27:F27"/>
     <mergeCell ref="A12:F12"/>
+    <mergeCell ref="A18:F18"/>
+    <mergeCell ref="A26:F26"/>
   </mergeCells>
   <pageMargins left="0.5" right="0.5" top="0.55" bottom="0.55" header="0.2" footer="0.2"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
@@ -3701,7 +4878,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00C8E6C9"/>
@@ -3728,7 +4905,7 @@
       <c r="D1" s="38" t="n"/>
     </row>
     <row r="2" ht="22" customHeight="1" s="17">
-      <c r="A2" s="52" t="inlineStr">
+      <c r="A2" s="69" t="inlineStr">
         <is>
           <t>（冠名、活动赞助、活动执行等）　项目：绿城·潮鸣外滩　活动：2026-05-22 晚宴冠名</t>
         </is>
@@ -3738,12 +4915,12 @@
       <c r="D2" s="40" t="n"/>
     </row>
     <row r="3" ht="28" customHeight="1" s="17">
-      <c r="A3" s="53" t="inlineStr">
+      <c r="A3" s="70" t="inlineStr">
         <is>
           <t>活动主题</t>
         </is>
       </c>
-      <c r="B3" s="54" t="inlineStr">
+      <c r="B3" s="71" t="inlineStr">
         <is>
           <t>【绿城·潮鸣】星耀北外滩——AI领袖定制晚宴</t>
         </is>
@@ -3752,12 +4929,12 @@
       <c r="D3" s="25" t="n"/>
     </row>
     <row r="4" ht="28" customHeight="1" s="17">
-      <c r="A4" s="53" t="inlineStr">
+      <c r="A4" s="70" t="inlineStr">
         <is>
           <t>活动举办时间</t>
         </is>
       </c>
-      <c r="B4" s="55" t="inlineStr">
+      <c r="B4" s="72" t="inlineStr">
         <is>
           <t>2026年5月22日 13:00–20:30　　上海·北外滩·一滴水</t>
         </is>
@@ -3766,7 +4943,7 @@
       <c r="D4" s="25" t="n"/>
     </row>
     <row r="5" ht="28" customHeight="1" s="17">
-      <c r="A5" s="53" t="inlineStr">
+      <c r="A5" s="70" t="inlineStr">
         <is>
           <t>活动
 现场氛围</t>
@@ -3787,20 +4964,20 @@
     <row r="6" ht="78" customHeight="1" s="17">
       <c r="A6" s="25" t="n"/>
       <c r="B6" s="25" t="n"/>
-      <c r="C6" s="56" t="n"/>
+      <c r="C6" s="73" t="n"/>
       <c r="D6" s="25" t="n"/>
     </row>
     <row r="7" ht="78" customHeight="1" s="17">
       <c r="A7" s="25" t="n"/>
-      <c r="B7" s="57" t="n"/>
-      <c r="C7" s="58" t="n"/>
-      <c r="D7" s="59" t="n"/>
+      <c r="B7" s="74" t="n"/>
+      <c r="C7" s="75" t="n"/>
+      <c r="D7" s="76" t="n"/>
     </row>
     <row r="8" ht="78" customHeight="1" s="17">
       <c r="A8" s="25" t="n"/>
-      <c r="B8" s="60" t="n"/>
-      <c r="C8" s="61" t="n"/>
-      <c r="D8" s="62" t="n"/>
+      <c r="B8" s="77" t="n"/>
+      <c r="C8" s="78" t="n"/>
+      <c r="D8" s="79" t="n"/>
     </row>
     <row r="9" ht="28" customHeight="1" s="17">
       <c r="A9" s="25" t="n"/>
@@ -3819,28 +4996,28 @@
     <row r="10" ht="78" customHeight="1" s="17">
       <c r="A10" s="25" t="n"/>
       <c r="B10" s="25" t="n"/>
-      <c r="C10" s="56" t="n"/>
+      <c r="C10" s="73" t="n"/>
       <c r="D10" s="25" t="n"/>
     </row>
     <row r="11" ht="78" customHeight="1" s="17">
       <c r="A11" s="25" t="n"/>
-      <c r="B11" s="57" t="n"/>
-      <c r="C11" s="58" t="n"/>
-      <c r="D11" s="59" t="n"/>
+      <c r="B11" s="74" t="n"/>
+      <c r="C11" s="75" t="n"/>
+      <c r="D11" s="76" t="n"/>
     </row>
     <row r="12" ht="78" customHeight="1" s="17">
       <c r="A12" s="25" t="n"/>
-      <c r="B12" s="60" t="n"/>
-      <c r="C12" s="61" t="n"/>
-      <c r="D12" s="62" t="n"/>
+      <c r="B12" s="77" t="n"/>
+      <c r="C12" s="78" t="n"/>
+      <c r="D12" s="79" t="n"/>
     </row>
     <row r="13" ht="24" customHeight="1" s="17">
-      <c r="A13" s="53" t="inlineStr">
+      <c r="A13" s="70" t="inlineStr">
         <is>
           <t>策划负责人填写</t>
         </is>
       </c>
-      <c r="B13" s="50" t="inlineStr">
+      <c r="B13" s="66" t="inlineStr">
         <is>
           <t>总体活动评价：</t>
         </is>
@@ -3850,23 +5027,23 @@
     </row>
     <row r="14" ht="36" customHeight="1" s="17">
       <c r="A14" s="25" t="n"/>
-      <c r="B14" s="63" t="inlineStr">
+      <c r="B14" s="80" t="inlineStr">
         <is>
           <t>本次活动为「2026人工智能商业化落地与硬核投资破局峰会」晚宴冠名。绿城中国 | 绿城·潮鸣外滩作为晚宴冠名战略合作伙伴，主背景板、议程看板、展台立牌、主会场双屏及晚宴大屏品牌片均完成品牌露出。按照约定完成整体策划与执行，现场氛围良好，活动取得圆满成功。</t>
         </is>
       </c>
-      <c r="C14" s="64" t="n"/>
-      <c r="D14" s="56" t="n"/>
+      <c r="C14" s="81" t="n"/>
+      <c r="D14" s="73" t="n"/>
     </row>
     <row r="15" ht="36" customHeight="1" s="17">
       <c r="A15" s="25" t="n"/>
-      <c r="B15" s="60" t="n"/>
-      <c r="C15" s="65" t="n"/>
-      <c r="D15" s="61" t="n"/>
+      <c r="B15" s="77" t="n"/>
+      <c r="C15" s="82" t="n"/>
+      <c r="D15" s="78" t="n"/>
     </row>
     <row r="16" ht="32" customHeight="1" s="17">
       <c r="A16" s="25" t="n"/>
-      <c r="B16" s="66" t="inlineStr">
+      <c r="B16" s="83" t="inlineStr">
         <is>
           <t>策划负责人签名：胡继刚 ____________________　　日期：2026-05-22　　（请补签）</t>
         </is>
@@ -3875,12 +5052,12 @@
       <c r="D16" s="31" t="n"/>
     </row>
     <row r="17" ht="24" customHeight="1" s="17">
-      <c r="A17" s="53" t="inlineStr">
+      <c r="A17" s="70" t="inlineStr">
         <is>
           <t>营销负责人填写</t>
         </is>
       </c>
-      <c r="B17" s="50" t="inlineStr">
+      <c r="B17" s="66" t="inlineStr">
         <is>
           <t>对活动【总体效果】评估（文字说明）：</t>
         </is>
@@ -3890,7 +5067,7 @@
     </row>
     <row r="18" ht="42" customHeight="1" s="17">
       <c r="A18" s="25" t="n"/>
-      <c r="B18" s="67" t="inlineStr">
+      <c r="B18" s="84" t="inlineStr">
         <is>
           <t>绿城中国 / 潮鸣字样可辨露出已核验，效果良好，符合约定要求。参观邀约口播、朋友圈九宫格、回顾视频、证书特写见执行回执待补项，不在此拔高。</t>
         </is>
@@ -3900,7 +5077,7 @@
     </row>
     <row r="19" ht="28" customHeight="1" s="17">
       <c r="A19" s="25" t="n"/>
-      <c r="B19" s="68" t="inlineStr">
+      <c r="B19" s="85" t="inlineStr">
         <is>
           <t>非常好（☐）　　良好（☑）　　一般（☐）　　较差（☐）</t>
         </is>
@@ -3910,7 +5087,7 @@
     </row>
     <row r="20" ht="42" customHeight="1" s="17">
       <c r="A20" s="25" t="n"/>
-      <c r="B20" s="69" t="inlineStr">
+      <c r="B20" s="86" t="inlineStr">
         <is>
           <t>勾选说明：按《基础营销验收单》模板默认口径「效果良好，符合要求」预勾「良好」，不拔高为「非常好」。请绿城营销负责人复核。</t>
         </is>
@@ -3920,7 +5097,7 @@
     </row>
     <row r="21" ht="32" customHeight="1" s="17">
       <c r="A21" s="25" t="n"/>
-      <c r="B21" s="66" t="inlineStr">
+      <c r="B21" s="83" t="inlineStr">
         <is>
           <t>营销负责人签名：____________________　　日期：____________________　　对接：笪浩 18678408669（评估表请补签）</t>
         </is>
@@ -3929,9 +5106,9 @@
       <c r="D21" s="31" t="n"/>
     </row>
     <row r="22" ht="36" customHeight="1" s="17">
-      <c r="A22" s="44" t="inlineStr">
-        <is>
-          <t>详见附件：本工作簿「营销验收单」「权益核验清单」「赞助权益执行回执」及拍立享相册、网盘录像。合作金额含税 ¥100,000，四模块整体打包。本表仅对应 5 月 22 日峰会。</t>
+      <c r="A22" s="62" t="inlineStr">
+        <is>
+          <t>详见附件：本工作簿「按重要顺序分类」（18 张分级）「营销验收单」「权益核验清单」「赞助权益执行回执」及拍立享相册、网盘录像。合作金额含税 ¥100,000，四模块整体打包。本表仅对应 5 月 22 日峰会。</t>
         </is>
       </c>
       <c r="B22" s="25" t="n"/>
@@ -3969,7 +5146,7 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="001F6B4A"/>
@@ -4006,117 +5183,117 @@
       <c r="D2" s="40" t="n"/>
     </row>
     <row r="3" ht="28" customHeight="1" s="17">
-      <c r="A3" s="70" t="inlineStr">
+      <c r="A3" s="87" t="inlineStr">
         <is>
           <t>出具方（主办）</t>
         </is>
       </c>
-      <c r="B3" s="71" t="inlineStr">
+      <c r="B3" s="88" t="inlineStr">
         <is>
           <t>上海市杨浦区科技企业联合会</t>
         </is>
       </c>
-      <c r="C3" s="70" t="inlineStr">
+      <c r="C3" s="87" t="inlineStr">
         <is>
           <t>接收方（赞助）</t>
         </is>
       </c>
-      <c r="D3" s="71" t="inlineStr">
+      <c r="D3" s="88" t="inlineStr">
         <is>
           <t>上海绿城泓盛建设发展有限公司</t>
         </is>
       </c>
     </row>
     <row r="4" ht="28" customHeight="1" s="17">
-      <c r="A4" s="70" t="inlineStr">
+      <c r="A4" s="87" t="inlineStr">
         <is>
           <t>对接人</t>
         </is>
       </c>
-      <c r="B4" s="71" t="inlineStr">
+      <c r="B4" s="88" t="inlineStr">
         <is>
           <t>胡继刚　13262607888</t>
         </is>
       </c>
-      <c r="C4" s="70" t="inlineStr">
+      <c r="C4" s="87" t="inlineStr">
         <is>
           <t>对接人</t>
         </is>
       </c>
-      <c r="D4" s="71" t="inlineStr">
+      <c r="D4" s="88" t="inlineStr">
         <is>
           <t>笪浩　18678408669</t>
         </is>
       </c>
     </row>
     <row r="5" ht="28" customHeight="1" s="17">
-      <c r="A5" s="70" t="inlineStr">
+      <c r="A5" s="87" t="inlineStr">
         <is>
           <t>活动名称</t>
         </is>
       </c>
-      <c r="B5" s="71" t="inlineStr">
+      <c r="B5" s="88" t="inlineStr">
         <is>
           <t>2026人工智能商业化落地与硬核投资破局峰会</t>
         </is>
       </c>
-      <c r="C5" s="70" t="inlineStr">
+      <c r="C5" s="87" t="inlineStr">
         <is>
           <t>活动时间/地点</t>
         </is>
       </c>
-      <c r="D5" s="71" t="inlineStr">
+      <c r="D5" s="88" t="inlineStr">
         <is>
           <t>2026-05-22　上海·北外滩·一滴水</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1" s="17">
-      <c r="A6" s="70" t="inlineStr">
+      <c r="A6" s="87" t="inlineStr">
         <is>
           <t>合作身份</t>
         </is>
       </c>
-      <c r="B6" s="71" t="inlineStr">
+      <c r="B6" s="88" t="inlineStr">
         <is>
           <t>晚宴冠名战略合作伙伴</t>
         </is>
       </c>
-      <c r="C6" s="70" t="inlineStr">
+      <c r="C6" s="87" t="inlineStr">
         <is>
           <t>合作金额</t>
         </is>
       </c>
-      <c r="D6" s="71" t="inlineStr">
+      <c r="D6" s="88" t="inlineStr">
         <is>
           <t>人民币 100,000 元整（含税）</t>
         </is>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1" s="17">
-      <c r="A7" s="70" t="inlineStr">
+      <c r="A7" s="87" t="inlineStr">
         <is>
           <t>晚宴场次</t>
         </is>
       </c>
-      <c r="B7" s="71" t="inlineStr">
+      <c r="B7" s="88" t="inlineStr">
         <is>
           <t>【绿城·潮鸣】星耀北外滩——AI领袖定制晚宴</t>
         </is>
       </c>
-      <c r="C7" s="70" t="inlineStr">
+      <c r="C7" s="87" t="inlineStr">
         <is>
           <t>项目品牌</t>
         </is>
       </c>
-      <c r="D7" s="71" t="inlineStr">
+      <c r="D7" s="88" t="inlineStr">
         <is>
           <t>绿城中国 · 绿城·潮鸣外滩</t>
         </is>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1" s="17">
-      <c r="A8" s="72" t="inlineStr">
+      <c r="A8" s="89" t="inlineStr">
         <is>
           <t>四模块执行确认（整体打包，不拆子项计价）</t>
         </is>
@@ -4148,119 +5325,119 @@
       </c>
     </row>
     <row r="10" ht="48" customHeight="1" s="17">
-      <c r="A10" s="43" t="inlineStr">
+      <c r="A10" s="61" t="inlineStr">
         <is>
           <t>1. 晚宴冠名和专属权益</t>
         </is>
       </c>
-      <c r="B10" s="43" t="inlineStr">
+      <c r="B10" s="61" t="inlineStr">
         <is>
           <t>55,000</t>
         </is>
       </c>
-      <c r="C10" s="45" t="inlineStr">
+      <c r="C10" s="63" t="inlineStr">
         <is>
           <t>☑ 已执行（冠名/品牌片）</t>
         </is>
       </c>
-      <c r="D10" s="44" t="inlineStr">
+      <c r="D10" s="62" t="inlineStr">
         <is>
           <t>议程看板【绿城·潮鸣】晚宴；主背景板「晚宴冠名战略合作伙伴·绿城中国」；晚宴大屏绿城中国品牌片</t>
         </is>
       </c>
     </row>
     <row r="11" ht="48" customHeight="1" s="17">
-      <c r="A11" s="43" t="inlineStr">
+      <c r="A11" s="61" t="inlineStr">
         <is>
           <t>2. 主会场权益</t>
         </is>
       </c>
-      <c r="B11" s="43" t="inlineStr">
+      <c r="B11" s="61" t="inlineStr">
         <is>
           <t>30,000</t>
         </is>
       </c>
-      <c r="C11" s="45" t="inlineStr">
+      <c r="C11" s="63" t="inlineStr">
         <is>
           <t>☑ 已执行（展台/双屏）</t>
         </is>
       </c>
-      <c r="D11" s="44" t="inlineStr">
+      <c r="D11" s="62" t="inlineStr">
         <is>
           <t>展台立牌「绿城中国 GREENTOWN」；展台接待礼袋物料；主会场双屏同款主视觉；主视觉KV含绿城中国</t>
         </is>
       </c>
     </row>
     <row r="12" ht="48" customHeight="1" s="17">
-      <c r="A12" s="43" t="inlineStr">
+      <c r="A12" s="61" t="inlineStr">
         <is>
           <t>3. 专场项目参观邀约</t>
         </is>
       </c>
-      <c r="B12" s="43" t="inlineStr">
+      <c r="B12" s="61" t="inlineStr">
         <is>
           <t>5,000</t>
         </is>
       </c>
-      <c r="C12" s="46" t="inlineStr">
+      <c r="C12" s="64" t="inlineStr">
         <is>
           <t>☐ 待录像核验</t>
         </is>
       </c>
-      <c r="D12" s="44" t="inlineStr">
+      <c r="D12" s="62" t="inlineStr">
         <is>
           <t>主持人口播位已具备。相册未见参观/接驳专项成片，请以全程录像确认是否口播执行。</t>
         </is>
       </c>
     </row>
     <row r="13" ht="48" customHeight="1" s="17">
-      <c r="A13" s="43" t="inlineStr">
+      <c r="A13" s="61" t="inlineStr">
         <is>
           <t>4. 宣发配合</t>
         </is>
       </c>
-      <c r="B13" s="43" t="inlineStr">
+      <c r="B13" s="61" t="inlineStr">
         <is>
           <t>10,000</t>
         </is>
       </c>
-      <c r="C13" s="46" t="inlineStr">
+      <c r="C13" s="64" t="inlineStr">
         <is>
           <t>☑ 摄影已交　☐ 其余待补</t>
         </is>
       </c>
-      <c r="D13" s="44" t="inlineStr">
+      <c r="D13" s="62" t="inlineStr">
         <is>
           <t>现场摄影+本回执。朋友圈九宫格、回顾视频片头鸣谢未附本回执。</t>
         </is>
       </c>
     </row>
     <row r="14" ht="48" customHeight="1" s="17">
-      <c r="A14" s="43" t="inlineStr">
+      <c r="A14" s="61" t="inlineStr">
         <is>
           <t>合计（含税）</t>
         </is>
       </c>
-      <c r="B14" s="43" t="inlineStr">
+      <c r="B14" s="61" t="inlineStr">
         <is>
           <t>100,000</t>
         </is>
       </c>
-      <c r="C14" s="46" t="inlineStr">
+      <c r="C14" s="64" t="inlineStr">
         <is>
           <t>主体已交，部分待补</t>
         </is>
       </c>
-      <c r="D14" s="44" t="inlineStr">
+      <c r="D14" s="62" t="inlineStr">
         <is>
           <t>四模块整体打包验收。已核验项以绿城/潮鸣字样可辨露出为准。</t>
         </is>
       </c>
     </row>
     <row r="15" ht="52" customHeight="1" s="17">
-      <c r="A15" s="44" t="inlineStr">
-        <is>
-          <t>证据目录：①本工作簿营销验收单（首页 9 张图注）②权益核验清单 ③效果评估表 ④绿城·潮鸣外滩露出大图 ⑤拍立享 https://live.pailixiang.com/album/a12523836160（约 425 张）⑥网盘录像 https://pan.baidu.com/s/1S8cNdqnCR_anuVPD6vlhjg 提取码 8888。证书特写未见，不以本回执推定证书已颁。</t>
+      <c r="A15" s="62" t="inlineStr">
+        <is>
+          <t>证据目录：①营销验收单（封面 9 张）②按重要顺序分类（18 张全部按五级嵌入）③权益核验清单 ④效果评估表 ⑤绿城·潮鸣外滩露出大图 ⑥拍立享 https://live.pailixiang.com/album/a12523836160（约 425 张）⑦网盘录像 https://pan.baidu.com/s/1S8cNdqnCR_anuVPD6vlhjg 提取码 8888。证书特写未见，不以本回执推定证书已颁。</t>
         </is>
       </c>
       <c r="B15" s="25" t="n"/>
@@ -4268,22 +5445,22 @@
       <c r="D15" s="25" t="n"/>
     </row>
     <row r="16" ht="56" customHeight="1" s="17">
-      <c r="A16" s="73" t="inlineStr">
+      <c r="A16" s="90" t="inlineStr">
         <is>
           <t>总体结论：晚宴冠名与主会场露出已按约定落地，效果良好，符合要求（预勾「良好」）。参观邀约、朋友圈九宫格、回顾视频、证书特写为待补项，不影响四模块整体打包之主体验收，由绿城营销负责人复核后签字盖章。本回执不与 2026 年 3 月开盘花束验收混用。</t>
         </is>
       </c>
-      <c r="B16" s="48" t="n"/>
-      <c r="C16" s="48" t="n"/>
-      <c r="D16" s="48" t="n"/>
+      <c r="B16" s="52" t="n"/>
+      <c r="C16" s="52" t="n"/>
+      <c r="D16" s="52" t="n"/>
     </row>
     <row r="17" ht="36" customHeight="1" s="17">
-      <c r="A17" s="70" t="inlineStr">
+      <c r="A17" s="87" t="inlineStr">
         <is>
           <t>主办方（出具）</t>
         </is>
       </c>
-      <c r="B17" s="74" t="inlineStr">
+      <c r="B17" s="91" t="inlineStr">
         <is>
           <t>单位：上海市杨浦区科技企业联合会
 授权代表：胡继刚
@@ -4292,12 +5469,12 @@
 （公章）</t>
         </is>
       </c>
-      <c r="C17" s="70" t="inlineStr">
+      <c r="C17" s="87" t="inlineStr">
         <is>
           <t>赞助方（接收）</t>
         </is>
       </c>
-      <c r="D17" s="74" t="inlineStr">
+      <c r="D17" s="91" t="inlineStr">
         <is>
           <t>单位：上海绿城泓盛建设发展有限公司
 授权代表：____________________
@@ -4308,13 +5485,13 @@
       </c>
     </row>
     <row r="18" ht="72" customHeight="1" s="17">
-      <c r="A18" s="62" t="n"/>
+      <c r="A18" s="79" t="n"/>
       <c r="B18" s="25" t="n"/>
-      <c r="C18" s="62" t="n"/>
+      <c r="C18" s="79" t="n"/>
       <c r="D18" s="25" t="n"/>
     </row>
     <row r="19" ht="22" customHeight="1" s="17">
-      <c r="A19" s="72" t="inlineStr">
+      <c r="A19" s="89" t="inlineStr">
         <is>
           <t>回执附图（代表性证据，已嵌入本页）</t>
         </is>
@@ -4370,14 +5547,14 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="001F6B4A"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D23"/>
+  <dimension ref="A1:D30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" style="17" min="1" max="1"/>
@@ -4389,7 +5566,7 @@
     <row r="1" ht="28" customHeight="1" s="17">
       <c r="A1" s="37" t="inlineStr">
         <is>
-          <t>绿城中国｜绿城·潮鸣外滩 现场露出精华照片（甲方交付）</t>
+          <t>绿城中国｜绿城·潮鸣外滩 现场露出精华照片（按重要顺序 · 甲方交付）</t>
         </is>
       </c>
       <c r="B1" s="38" t="n"/>
@@ -4399,163 +5576,293 @@
     <row r="2" ht="36" customHeight="1" s="17">
       <c r="A2" s="39" t="inlineStr">
         <is>
-          <t>活动时间：2026-05-22　地点：上海·北外滩·一滴水　本页 18 张精华（首页 9 张 + 续图）　完整相册约 425 张：https://live.pailixiang.com/album/a12523836160　录像：https://pan.baidu.com/s/1S8cNdqnCR_anuVPD6vlhjg（提取码 8888）</t>
+          <t>活动时间：2026-05-22　地点：上海·北外滩·一滴水　本页 18 张按一级→五级排列（与「按重要顺序分类」同序）　完整相册约 425 张：https://live.pailixiang.com/album/a12523836160　录像：https://pan.baidu.com/s/1S8cNdqnCR_anuVPD6vlhjg（提取码 8888）</t>
         </is>
       </c>
       <c r="B2" s="40" t="n"/>
       <c r="C2" s="40" t="n"/>
       <c r="D2" s="40" t="n"/>
     </row>
-    <row r="4" ht="168" customHeight="1" s="17"/>
-    <row r="5" ht="36" customHeight="1" s="17">
-      <c r="A5" s="75" t="inlineStr">
-        <is>
-          <t>1. 议程看板：【绿城·潮鸣】星耀北外滩——AI领袖定制晚宴</t>
-        </is>
-      </c>
-      <c r="C5" s="75" t="inlineStr">
-        <is>
-          <t>2. 主背景板全幅：晚宴冠名战略合作伙伴·绿城中国</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="168" customHeight="1" s="17"/>
-    <row r="7" ht="36" customHeight="1" s="17">
-      <c r="A7" s="75" t="inlineStr">
-        <is>
-          <t>3. 主会场展台立牌：绿城中国 / GREENTOWN 可辨</t>
-        </is>
-      </c>
-      <c r="C7" s="75" t="inlineStr">
-        <is>
-          <t>4. 展台接待：绿城立牌、礼袋与纸质物料，嘉宾问询</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="168" customHeight="1" s="17"/>
-    <row r="9" ht="36" customHeight="1" s="17">
-      <c r="A9" s="75" t="inlineStr">
-        <is>
-          <t>5. 主背景板合影：晚宴冠名位「绿城中国」可核验</t>
-        </is>
-      </c>
-      <c r="C9" s="75" t="inlineStr">
-        <is>
-          <t>6. 主会场双屏主视觉与背景板同款，含晚宴冠名·绿城中国</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="168" customHeight="1" s="17"/>
+    <row r="4" ht="28" customHeight="1" s="17">
+      <c r="A4" s="89" t="inlineStr">
+        <is>
+          <t>一级｜核心品牌露出（必看）（4 张）　绿城 / 潮鸣 / GREENTOWN 字样可直接核验，对应报价主体，建议甲方优先复核。</t>
+        </is>
+      </c>
+      <c r="B4" s="38" t="n"/>
+      <c r="C4" s="38" t="n"/>
+      <c r="D4" s="38" t="n"/>
+    </row>
+    <row r="5" ht="168" customHeight="1" s="17">
+      <c r="A5" s="25" t="n"/>
+      <c r="B5" s="25" t="n"/>
+      <c r="C5" s="25" t="n"/>
+      <c r="D5" s="25" t="n"/>
+    </row>
+    <row r="6" ht="36" customHeight="1" s="17">
+      <c r="A6" s="62" t="inlineStr">
+        <is>
+          <t>1. 议程看板【绿城·潮鸣】星耀北外滩晚宴</t>
+        </is>
+      </c>
+      <c r="B6" s="31" t="n"/>
+      <c r="C6" s="62" t="inlineStr">
+        <is>
+          <t>2. 主背景板：晚宴冠名战略合作伙伴·绿城中国</t>
+        </is>
+      </c>
+      <c r="D6" s="31" t="n"/>
+    </row>
+    <row r="7" ht="168" customHeight="1" s="17">
+      <c r="A7" s="25" t="n"/>
+      <c r="B7" s="25" t="n"/>
+      <c r="C7" s="25" t="n"/>
+      <c r="D7" s="25" t="n"/>
+    </row>
+    <row r="8" ht="36" customHeight="1" s="17">
+      <c r="A8" s="62" t="inlineStr">
+        <is>
+          <t>3. 展台立牌：绿城中国 GREENTOWN</t>
+        </is>
+      </c>
+      <c r="B8" s="31" t="n"/>
+      <c r="C8" s="62" t="inlineStr">
+        <is>
+          <t>4. 晚宴大屏播放绿城中国品牌片</t>
+        </is>
+      </c>
+      <c r="D8" s="31" t="n"/>
+    </row>
+    <row r="9" ht="28" customHeight="1" s="17">
+      <c r="A9" s="66" t="inlineStr">
+        <is>
+          <t>二级｜主会场执行（重点）（4 张）　展台接待、双屏、主持、主视觉，证明主会场权益已落地。</t>
+        </is>
+      </c>
+      <c r="B9" s="40" t="n"/>
+      <c r="C9" s="40" t="n"/>
+      <c r="D9" s="40" t="n"/>
+    </row>
+    <row r="10" ht="168" customHeight="1" s="17">
+      <c r="A10" s="25" t="n"/>
+      <c r="B10" s="25" t="n"/>
+      <c r="C10" s="25" t="n"/>
+      <c r="D10" s="25" t="n"/>
+    </row>
     <row r="11" ht="36" customHeight="1" s="17">
-      <c r="A11" s="75" t="inlineStr">
-        <is>
-          <t>7. 主持环节主会场全幅露出，便于核验现场执行</t>
-        </is>
-      </c>
-      <c r="C11" s="75" t="inlineStr">
-        <is>
-          <t>8. 晚宴弧形大屏播放绿城中国「理想生活综合服务商」</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="168" customHeight="1" s="17"/>
+      <c r="A11" s="62" t="inlineStr">
+        <is>
+          <t>5. 展台接待：绿城立牌、礼袋与物料</t>
+        </is>
+      </c>
+      <c r="B11" s="31" t="n"/>
+      <c r="C11" s="62" t="inlineStr">
+        <is>
+          <t>6. 主会场双屏同款主视觉（含晚宴冠名·绿城中国）</t>
+        </is>
+      </c>
+      <c r="D11" s="31" t="n"/>
+    </row>
+    <row r="12" ht="168" customHeight="1" s="17">
+      <c r="A12" s="25" t="n"/>
+      <c r="B12" s="25" t="n"/>
+      <c r="C12" s="25" t="n"/>
+      <c r="D12" s="25" t="n"/>
+    </row>
     <row r="13" ht="36" customHeight="1" s="17">
-      <c r="A13" s="75" t="inlineStr">
-        <is>
-          <t>9. 主视觉 KV：战略合作伙伴名单含绿城中国</t>
-        </is>
-      </c>
-      <c r="C13" s="75" t="inlineStr">
-        <is>
-          <t>10. 主背景板合影（晚宴冠名位特写）</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="168" customHeight="1" s="17"/>
-    <row r="15" ht="36" customHeight="1" s="17">
-      <c r="A15" s="75" t="inlineStr">
+      <c r="A13" s="62" t="inlineStr">
+        <is>
+          <t>7. 主持现场：主会场露出</t>
+        </is>
+      </c>
+      <c r="B13" s="31" t="n"/>
+      <c r="C13" s="62" t="inlineStr">
+        <is>
+          <t>8. 主视觉 KV：战略合作名单含绿城中国</t>
+        </is>
+      </c>
+      <c r="D13" s="31" t="n"/>
+    </row>
+    <row r="14" ht="28" customHeight="1" s="17">
+      <c r="A14" s="92" t="inlineStr">
+        <is>
+          <t>三级｜冠名位合影核验（4 张）　主背景板合影，可复核晚宴冠名位「绿城中国」。</t>
+        </is>
+      </c>
+      <c r="B14" s="52" t="n"/>
+      <c r="C14" s="52" t="n"/>
+      <c r="D14" s="52" t="n"/>
+    </row>
+    <row r="15" ht="168" customHeight="1" s="17">
+      <c r="A15" s="25" t="n"/>
+      <c r="B15" s="25" t="n"/>
+      <c r="C15" s="25" t="n"/>
+      <c r="D15" s="25" t="n"/>
+    </row>
+    <row r="16" ht="36" customHeight="1" s="17">
+      <c r="A16" s="62" t="inlineStr">
+        <is>
+          <t>9. 主背景板合影核验冠名位</t>
+        </is>
+      </c>
+      <c r="B16" s="31" t="n"/>
+      <c r="C16" s="62" t="inlineStr">
+        <is>
+          <t>10. 主背景板合影（冠名位特写）</t>
+        </is>
+      </c>
+      <c r="D16" s="31" t="n"/>
+    </row>
+    <row r="17" ht="168" customHeight="1" s="17">
+      <c r="A17" s="25" t="n"/>
+      <c r="B17" s="25" t="n"/>
+      <c r="C17" s="25" t="n"/>
+      <c r="D17" s="25" t="n"/>
+    </row>
+    <row r="18" ht="36" customHeight="1" s="17">
+      <c r="A18" s="62" t="inlineStr">
         <is>
           <t>11. 主背景板双人合影核验冠名位</t>
         </is>
       </c>
-      <c r="C15" s="75" t="inlineStr">
+      <c r="B18" s="31" t="n"/>
+      <c r="C18" s="62" t="inlineStr">
         <is>
           <t>12. 主背景板合影：晚宴冠名战略合作伙伴·绿城中国</t>
         </is>
       </c>
-    </row>
-    <row r="16" ht="168" customHeight="1" s="17"/>
-    <row r="17" ht="36" customHeight="1" s="17">
-      <c r="A17" s="75" t="inlineStr">
+      <c r="D18" s="31" t="n"/>
+    </row>
+    <row r="19" ht="28" customHeight="1" s="17">
+      <c r="A19" s="93" t="inlineStr">
+        <is>
+          <t>四级｜主办致辞现场（3 张）　主会场致辞与讲台，补充现场执行；不作参观邀约专项成片。</t>
+        </is>
+      </c>
+      <c r="B19" s="58" t="n"/>
+      <c r="C19" s="58" t="n"/>
+      <c r="D19" s="58" t="n"/>
+    </row>
+    <row r="20" ht="168" customHeight="1" s="17">
+      <c r="A20" s="25" t="n"/>
+      <c r="B20" s="25" t="n"/>
+      <c r="C20" s="25" t="n"/>
+      <c r="D20" s="25" t="n"/>
+    </row>
+    <row r="21" ht="36" customHeight="1" s="17">
+      <c r="A21" s="62" t="inlineStr">
         <is>
           <t>13. 主办致辞全景：主会场双屏与讲台</t>
         </is>
       </c>
-      <c r="C17" s="75" t="inlineStr">
+      <c r="B21" s="31" t="n"/>
+      <c r="C21" s="62" t="inlineStr">
         <is>
           <t>14. 主办致辞：姚志勇，主会场主视觉</t>
         </is>
       </c>
-    </row>
-    <row r="18" ht="168" customHeight="1" s="17"/>
-    <row r="19" ht="36" customHeight="1" s="17">
-      <c r="A19" s="75" t="inlineStr">
+      <c r="D21" s="31" t="n"/>
+    </row>
+    <row r="22" ht="168" customHeight="1" s="17">
+      <c r="A22" s="25" t="n"/>
+      <c r="B22" s="25" t="n"/>
+      <c r="C22" s="25" t="n"/>
+      <c r="D22" s="25" t="n"/>
+    </row>
+    <row r="23" ht="36" customHeight="1" s="17">
+      <c r="A23" s="62" t="inlineStr">
         <is>
           <t>15. 主办致辞讲台特写</t>
         </is>
       </c>
-      <c r="C19" s="75" t="inlineStr">
-        <is>
-          <t>16. 冠名晚宴合影（江景厅）</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="168" customHeight="1" s="17"/>
-    <row r="21" ht="36" customHeight="1" s="17">
-      <c r="A21" s="75" t="inlineStr">
-        <is>
-          <t>17. 冠名晚宴桌次（江景厅圆桌）</t>
-        </is>
-      </c>
-      <c r="C21" s="75" t="inlineStr">
-        <is>
-          <t>18. 冠名晚宴现场举杯</t>
-        </is>
-      </c>
-    </row>
-    <row r="23" ht="42" customHeight="1" s="17">
-      <c r="A23" s="44" t="inlineStr">
-        <is>
-          <t>说明：本页只收录绿城中国、绿城·潮鸣、GREENTOWN 可辨露出及冠名晚宴现场。未收录美年大健康、泰隆银行、腾讯云、蔚来、长江商学院等他方展位。完整 425 张以拍立享为准；MP4 以网盘「5.22」为准。不与开盘花束混用。</t>
-        </is>
-      </c>
-      <c r="B23" s="25" t="n"/>
+      <c r="B23" s="31" t="n"/>
       <c r="C23" s="25" t="n"/>
       <c r="D23" s="25" t="n"/>
     </row>
+    <row r="24" ht="28" customHeight="1" s="17">
+      <c r="A24" s="94" t="inlineStr">
+        <is>
+          <t>五级｜冠名晚宴氛围（3 张）　江景厅冠名晚宴现场。席卡为嘉宾姓名卡，不作「潮鳴」logo 桌卡证据。</t>
+        </is>
+      </c>
+      <c r="B24" s="25" t="n"/>
+      <c r="C24" s="25" t="n"/>
+      <c r="D24" s="25" t="n"/>
+    </row>
+    <row r="25" ht="168" customHeight="1" s="17">
+      <c r="A25" s="25" t="n"/>
+      <c r="B25" s="25" t="n"/>
+      <c r="C25" s="25" t="n"/>
+      <c r="D25" s="25" t="n"/>
+    </row>
+    <row r="26" ht="36" customHeight="1" s="17">
+      <c r="A26" s="62" t="inlineStr">
+        <is>
+          <t>16. 冠名晚宴合影（江景厅）</t>
+        </is>
+      </c>
+      <c r="B26" s="31" t="n"/>
+      <c r="C26" s="62" t="inlineStr">
+        <is>
+          <t>17. 冠名晚宴桌次（江景厅圆桌）</t>
+        </is>
+      </c>
+      <c r="D26" s="31" t="n"/>
+    </row>
+    <row r="27" ht="168" customHeight="1" s="17">
+      <c r="A27" s="25" t="n"/>
+      <c r="B27" s="25" t="n"/>
+      <c r="C27" s="25" t="n"/>
+      <c r="D27" s="25" t="n"/>
+    </row>
+    <row r="28" ht="36" customHeight="1" s="17">
+      <c r="A28" s="62" t="inlineStr">
+        <is>
+          <t>18. 冠名晚宴现场举杯</t>
+        </is>
+      </c>
+      <c r="B28" s="31" t="n"/>
+      <c r="C28" s="25" t="n"/>
+      <c r="D28" s="25" t="n"/>
+    </row>
+    <row r="30" ht="42" customHeight="1" s="17">
+      <c r="A30" s="62" t="inlineStr">
+        <is>
+          <t>说明：本页只收录绿城中国、绿城·潮鸣、GREENTOWN 可辨露出及冠名晚宴现场。未收录美年大健康、泰隆银行、腾讯云、蔚来、长江商学院等他方展位。完整 425 张以拍立享为准；MP4 以网盘「5.22」为准。不与开盘花束混用。</t>
+        </is>
+      </c>
+      <c r="B30" s="25" t="n"/>
+      <c r="C30" s="25" t="n"/>
+      <c r="D30" s="25" t="n"/>
+    </row>
   </sheetData>
-  <mergeCells count="21">
-    <mergeCell ref="A23:D23"/>
-    <mergeCell ref="A15:B15"/>
-    <mergeCell ref="C15:D15"/>
+  <mergeCells count="26">
+    <mergeCell ref="C6:D6"/>
+    <mergeCell ref="A4:D4"/>
     <mergeCell ref="A11:B11"/>
-    <mergeCell ref="C5:D5"/>
-    <mergeCell ref="A7:B7"/>
-    <mergeCell ref="C9:D9"/>
+    <mergeCell ref="A19:D19"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="A6:B6"/>
+    <mergeCell ref="A9:D9"/>
+    <mergeCell ref="A16:B16"/>
+    <mergeCell ref="C16:D16"/>
+    <mergeCell ref="A30:D30"/>
+    <mergeCell ref="A24:D24"/>
+    <mergeCell ref="A18:B18"/>
     <mergeCell ref="A1:D1"/>
+    <mergeCell ref="A26:B26"/>
     <mergeCell ref="A21:B21"/>
     <mergeCell ref="C21:D21"/>
     <mergeCell ref="C11:D11"/>
-    <mergeCell ref="A5:B5"/>
-    <mergeCell ref="A17:B17"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="C7:D7"/>
-    <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:D19"/>
+    <mergeCell ref="A23:B23"/>
+    <mergeCell ref="A8:B8"/>
+    <mergeCell ref="C8:D8"/>
+    <mergeCell ref="A28:B28"/>
     <mergeCell ref="A13:B13"/>
     <mergeCell ref="C13:D13"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A9:B9"/>
+    <mergeCell ref="C18:D18"/>
+    <mergeCell ref="A14:D14"/>
   </mergeCells>
   <hyperlinks>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A2" r:id="rId1"/>
@@ -4566,28 +5873,29 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
     <tabColor rgb="00C8E6C9"/>
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:F21"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="8" customWidth="1" style="17" min="1" max="1"/>
-    <col width="18" customWidth="1" style="17" min="2" max="2"/>
-    <col width="22" customWidth="1" style="17" min="3" max="3"/>
-    <col width="44" customWidth="1" style="17" min="4" max="4"/>
-    <col width="16" customWidth="1" style="17" min="5" max="5"/>
-    <col width="10" customWidth="1" style="17" min="6" max="6"/>
+    <col width="22" customWidth="1" style="17" min="2" max="2"/>
+    <col width="18" customWidth="1" style="17" min="3" max="3"/>
+    <col width="22" customWidth="1" style="17" min="4" max="4"/>
+    <col width="44" customWidth="1" style="17" min="5" max="5"/>
+    <col width="16" customWidth="1" style="17" min="6" max="6"/>
+    <col width="10" customWidth="1" style="17" min="7" max="7"/>
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1" s="17">
       <c r="A1" s="37" t="inlineStr">
         <is>
-          <t>绿城·潮鸣外滩露出 · 精华照片索引（含拍摄时间）</t>
+          <t>绿城·潮鸣外滩露出 · 精华照片索引（按重要等级）</t>
         </is>
       </c>
       <c r="B1" s="38" t="n"/>
@@ -4595,11 +5903,12 @@
       <c r="D1" s="38" t="n"/>
       <c r="E1" s="38" t="n"/>
       <c r="F1" s="38" t="n"/>
+      <c r="G1" s="38" t="n"/>
     </row>
     <row r="2" ht="28" customHeight="1" s="17">
       <c r="A2" s="39" t="inlineStr">
         <is>
-          <t>拍摄时间取自拍立享相册元数据。首页 9 张为绿城 / 潮鸣字样可辨主证据。不收录他方展位（美年大健康、泰隆银行、腾讯云、蔚来、长江商学院）。</t>
+          <t>按一级→五级排列，与「按重要顺序分类」同序。拍摄时间取自拍立享相册元数据。不收录他方展位（美年大健康、泰隆银行、腾讯云、蔚来、长江商学院）。</t>
         </is>
       </c>
       <c r="B2" s="40" t="n"/>
@@ -4607,6 +5916,7 @@
       <c r="D2" s="40" t="n"/>
       <c r="E2" s="40" t="n"/>
       <c r="F2" s="40" t="n"/>
+      <c r="G2" s="40" t="n"/>
     </row>
     <row r="3">
       <c r="A3" s="41" t="inlineStr">
@@ -4616,611 +5926,706 @@
       </c>
       <c r="B3" s="41" t="inlineStr">
         <is>
+          <t>重要等级</t>
+        </is>
+      </c>
+      <c r="C3" s="41" t="inlineStr">
+        <is>
           <t>文件名</t>
         </is>
       </c>
-      <c r="C3" s="41" t="inlineStr">
+      <c r="D3" s="41" t="inlineStr">
         <is>
           <t>拍摄时间</t>
         </is>
       </c>
-      <c r="D3" s="41" t="inlineStr">
+      <c r="E3" s="41" t="inlineStr">
         <is>
           <t>露出点</t>
         </is>
       </c>
-      <c r="E3" s="41" t="inlineStr">
+      <c r="F3" s="41" t="inlineStr">
         <is>
           <t>对应模块</t>
         </is>
       </c>
-      <c r="F3" s="41" t="inlineStr">
-        <is>
-          <t>首页</t>
+      <c r="G3" s="41" t="inlineStr">
+        <is>
+          <t>封面</t>
         </is>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1" s="17">
-      <c r="A4" s="76" t="inlineStr">
+      <c r="A4" s="95" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B4" s="47" t="inlineStr">
+      <c r="B4" s="51" t="inlineStr">
+        <is>
+          <t>一级 核心品牌露出（必看）</t>
+        </is>
+      </c>
+      <c r="C4" s="54" t="inlineStr">
         <is>
           <t>941A7785.JPG</t>
         </is>
       </c>
-      <c r="C4" s="76" t="inlineStr">
+      <c r="D4" s="95" t="inlineStr">
         <is>
           <t>2026-05-22 13:20:53</t>
         </is>
       </c>
-      <c r="D4" s="47" t="inlineStr">
-        <is>
-          <t>议程看板：【绿城·潮鸣】星耀北外滩——AI领袖定制晚宴</t>
-        </is>
-      </c>
-      <c r="E4" s="76" t="inlineStr">
+      <c r="E4" s="54" t="inlineStr">
+        <is>
+          <t>议程看板【绿城·潮鸣】星耀北外滩晚宴</t>
+        </is>
+      </c>
+      <c r="F4" s="95" t="inlineStr">
         <is>
           <t>晚宴冠名</t>
         </is>
       </c>
-      <c r="F4" s="76" t="inlineStr">
+      <c r="G4" s="95" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1" s="17">
-      <c r="A5" s="76" t="inlineStr">
+      <c r="A5" s="95" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B5" s="47" t="inlineStr">
+      <c r="B5" s="51" t="inlineStr">
+        <is>
+          <t>一级 核心品牌露出（必看）</t>
+        </is>
+      </c>
+      <c r="C5" s="54" t="inlineStr">
         <is>
           <t>941A7663.JPG</t>
         </is>
       </c>
-      <c r="C5" s="76" t="inlineStr">
+      <c r="D5" s="95" t="inlineStr">
         <is>
           <t>2026-05-22 12:54:38</t>
         </is>
       </c>
-      <c r="D5" s="47" t="inlineStr">
-        <is>
-          <t>主背景板全幅：晚宴冠名战略合作伙伴·绿城中国</t>
-        </is>
-      </c>
-      <c r="E5" s="76" t="inlineStr">
+      <c r="E5" s="54" t="inlineStr">
+        <is>
+          <t>主背景板：晚宴冠名战略合作伙伴·绿城中国</t>
+        </is>
+      </c>
+      <c r="F5" s="95" t="inlineStr">
         <is>
           <t>晚宴冠名</t>
         </is>
       </c>
-      <c r="F5" s="76" t="inlineStr">
+      <c r="G5" s="95" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1" s="17">
-      <c r="A6" s="76" t="inlineStr">
+      <c r="A6" s="95" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B6" s="47" t="inlineStr">
+      <c r="B6" s="51" t="inlineStr">
+        <is>
+          <t>一级 核心品牌露出（必看）</t>
+        </is>
+      </c>
+      <c r="C6" s="54" t="inlineStr">
         <is>
           <t>941A7769.JPG</t>
         </is>
       </c>
-      <c r="C6" s="76" t="inlineStr">
+      <c r="D6" s="95" t="inlineStr">
         <is>
           <t>2026-05-22 13:17:12</t>
         </is>
       </c>
-      <c r="D6" s="47" t="inlineStr">
-        <is>
-          <t>主会场展台立牌：绿城中国 / GREENTOWN 可辨</t>
-        </is>
-      </c>
-      <c r="E6" s="76" t="inlineStr">
+      <c r="E6" s="54" t="inlineStr">
+        <is>
+          <t>展台立牌：绿城中国 GREENTOWN</t>
+        </is>
+      </c>
+      <c r="F6" s="95" t="inlineStr">
         <is>
           <t>主会场</t>
         </is>
       </c>
-      <c r="F6" s="76" t="inlineStr">
+      <c r="G6" s="95" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1" s="17">
-      <c r="A7" s="76" t="inlineStr">
+      <c r="A7" s="95" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B7" s="47" t="inlineStr">
+      <c r="B7" s="51" t="inlineStr">
+        <is>
+          <t>一级 核心品牌露出（必看）</t>
+        </is>
+      </c>
+      <c r="C7" s="54" t="inlineStr">
+        <is>
+          <t>941A8810.JPG</t>
+        </is>
+      </c>
+      <c r="D7" s="95" t="inlineStr">
+        <is>
+          <t>2026-05-22 19:50:04</t>
+        </is>
+      </c>
+      <c r="E7" s="54" t="inlineStr">
+        <is>
+          <t>晚宴大屏播放绿城中国品牌片</t>
+        </is>
+      </c>
+      <c r="F7" s="95" t="inlineStr">
+        <is>
+          <t>晚宴冠名</t>
+        </is>
+      </c>
+      <c r="G7" s="95" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+    </row>
+    <row r="8" ht="22" customHeight="1" s="17">
+      <c r="A8" s="95" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="B8" s="54" t="inlineStr">
+        <is>
+          <t>二级 主会场执行（重点）</t>
+        </is>
+      </c>
+      <c r="C8" s="54" t="inlineStr">
         <is>
           <t>941A7768.JPG</t>
         </is>
       </c>
-      <c r="C7" s="76" t="inlineStr">
+      <c r="D8" s="95" t="inlineStr">
         <is>
           <t>2026-05-22 13:16:51</t>
         </is>
       </c>
-      <c r="D7" s="47" t="inlineStr">
-        <is>
-          <t>展台接待：绿城立牌、礼袋与纸质物料，嘉宾问询</t>
-        </is>
-      </c>
-      <c r="E7" s="76" t="inlineStr">
+      <c r="E8" s="54" t="inlineStr">
+        <is>
+          <t>展台接待：绿城立牌、礼袋与物料</t>
+        </is>
+      </c>
+      <c r="F8" s="95" t="inlineStr">
         <is>
           <t>主会场</t>
         </is>
       </c>
-      <c r="F7" s="76" t="inlineStr">
+      <c r="G8" s="95" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
     </row>
-    <row r="8" ht="22" customHeight="1" s="17">
-      <c r="A8" s="76" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="B8" s="47" t="inlineStr">
+    <row r="9" ht="22" customHeight="1" s="17">
+      <c r="A9" s="95" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="B9" s="54" t="inlineStr">
+        <is>
+          <t>二级 主会场执行（重点）</t>
+        </is>
+      </c>
+      <c r="C9" s="54" t="inlineStr">
+        <is>
+          <t>941A7832.JPG</t>
+        </is>
+      </c>
+      <c r="D9" s="95" t="inlineStr">
+        <is>
+          <t>2026-05-22 13:37:45</t>
+        </is>
+      </c>
+      <c r="E9" s="54" t="inlineStr">
+        <is>
+          <t>主会场双屏同款主视觉（含晚宴冠名·绿城中国）</t>
+        </is>
+      </c>
+      <c r="F9" s="95" t="inlineStr">
+        <is>
+          <t>主会场</t>
+        </is>
+      </c>
+      <c r="G9" s="95" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="22" customHeight="1" s="17">
+      <c r="A10" s="95" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="B10" s="54" t="inlineStr">
+        <is>
+          <t>二级 主会场执行（重点）</t>
+        </is>
+      </c>
+      <c r="C10" s="54" t="inlineStr">
+        <is>
+          <t>941A7825.JPG</t>
+        </is>
+      </c>
+      <c r="D10" s="95" t="inlineStr">
+        <is>
+          <t>2026-05-22 13:36:38</t>
+        </is>
+      </c>
+      <c r="E10" s="54" t="inlineStr">
+        <is>
+          <t>主持现场：主会场露出</t>
+        </is>
+      </c>
+      <c r="F10" s="95" t="inlineStr">
+        <is>
+          <t>主会场</t>
+        </is>
+      </c>
+      <c r="G10" s="95" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+    </row>
+    <row r="11" ht="22" customHeight="1" s="17">
+      <c r="A11" s="95" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="B11" s="54" t="inlineStr">
+        <is>
+          <t>二级 主会场执行（重点）</t>
+        </is>
+      </c>
+      <c r="C11" s="54" t="inlineStr">
+        <is>
+          <t>00_banner.jpg</t>
+        </is>
+      </c>
+      <c r="D11" s="95" t="inlineStr">
+        <is>
+          <t>主视觉 KV（相册 Banner）</t>
+        </is>
+      </c>
+      <c r="E11" s="54" t="inlineStr">
+        <is>
+          <t>主视觉 KV：战略合作名单含绿城中国</t>
+        </is>
+      </c>
+      <c r="F11" s="95" t="inlineStr">
+        <is>
+          <t>主会场/宣发</t>
+        </is>
+      </c>
+      <c r="G11" s="95" t="inlineStr">
+        <is>
+          <t>是</t>
+        </is>
+      </c>
+    </row>
+    <row r="12" ht="22" customHeight="1" s="17">
+      <c r="A12" s="95" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="B12" s="54" t="inlineStr">
+        <is>
+          <t>三级 冠名位合影核验</t>
+        </is>
+      </c>
+      <c r="C12" s="54" t="inlineStr">
         <is>
           <t>941A7776.JPG</t>
         </is>
       </c>
-      <c r="C8" s="76" t="inlineStr">
+      <c r="D12" s="95" t="inlineStr">
         <is>
           <t>2026-05-22 13:18:16</t>
         </is>
       </c>
-      <c r="D8" s="47" t="inlineStr">
-        <is>
-          <t>主背景板合影：晚宴冠名位「绿城中国」可核验</t>
-        </is>
-      </c>
-      <c r="E8" s="76" t="inlineStr">
+      <c r="E12" s="54" t="inlineStr">
+        <is>
+          <t>主背景板合影核验冠名位</t>
+        </is>
+      </c>
+      <c r="F12" s="95" t="inlineStr">
         <is>
           <t>晚宴冠名</t>
         </is>
       </c>
-      <c r="F8" s="76" t="inlineStr">
+      <c r="G12" s="95" t="inlineStr">
         <is>
           <t>是</t>
         </is>
       </c>
     </row>
-    <row r="9" ht="22" customHeight="1" s="17">
-      <c r="A9" s="76" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="B9" s="47" t="inlineStr">
-        <is>
-          <t>941A7832.JPG</t>
-        </is>
-      </c>
-      <c r="C9" s="76" t="inlineStr">
-        <is>
-          <t>2026-05-22 13:37:45</t>
-        </is>
-      </c>
-      <c r="D9" s="47" t="inlineStr">
-        <is>
-          <t>主会场双屏主视觉与背景板同款，含晚宴冠名·绿城中国</t>
-        </is>
-      </c>
-      <c r="E9" s="76" t="inlineStr">
+    <row r="13" ht="22" customHeight="1" s="17">
+      <c r="A13" s="60" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="B13" s="62" t="inlineStr">
+        <is>
+          <t>三级 冠名位合影核验</t>
+        </is>
+      </c>
+      <c r="C13" s="62" t="inlineStr">
+        <is>
+          <t>941A7777.JPG</t>
+        </is>
+      </c>
+      <c r="D13" s="60" t="inlineStr">
+        <is>
+          <t>2026-05-22 13:19:01</t>
+        </is>
+      </c>
+      <c r="E13" s="62" t="inlineStr">
+        <is>
+          <t>主背景板合影（冠名位特写）</t>
+        </is>
+      </c>
+      <c r="F13" s="60" t="inlineStr">
+        <is>
+          <t>晚宴冠名</t>
+        </is>
+      </c>
+      <c r="G13" s="60" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="14" ht="22" customHeight="1" s="17">
+      <c r="A14" s="60" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="B14" s="62" t="inlineStr">
+        <is>
+          <t>三级 冠名位合影核验</t>
+        </is>
+      </c>
+      <c r="C14" s="62" t="inlineStr">
+        <is>
+          <t>941A7779.JPG</t>
+        </is>
+      </c>
+      <c r="D14" s="60" t="inlineStr">
+        <is>
+          <t>2026-05-22 13:19:08</t>
+        </is>
+      </c>
+      <c r="E14" s="62" t="inlineStr">
+        <is>
+          <t>主背景板双人合影核验冠名位</t>
+        </is>
+      </c>
+      <c r="F14" s="60" t="inlineStr">
+        <is>
+          <t>晚宴冠名</t>
+        </is>
+      </c>
+      <c r="G14" s="60" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="15" ht="22" customHeight="1" s="17">
+      <c r="A15" s="60" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="B15" s="62" t="inlineStr">
+        <is>
+          <t>三级 冠名位合影核验</t>
+        </is>
+      </c>
+      <c r="C15" s="62" t="inlineStr">
+        <is>
+          <t>941A7782.JPG</t>
+        </is>
+      </c>
+      <c r="D15" s="60" t="inlineStr">
+        <is>
+          <t>2026-05-22 13:19:19</t>
+        </is>
+      </c>
+      <c r="E15" s="62" t="inlineStr">
+        <is>
+          <t>主背景板合影：晚宴冠名战略合作伙伴·绿城中国</t>
+        </is>
+      </c>
+      <c r="F15" s="60" t="inlineStr">
+        <is>
+          <t>晚宴冠名</t>
+        </is>
+      </c>
+      <c r="G15" s="60" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="22" customHeight="1" s="17">
+      <c r="A16" s="60" t="inlineStr">
+        <is>
+          <t>13</t>
+        </is>
+      </c>
+      <c r="B16" s="62" t="inlineStr">
+        <is>
+          <t>四级 主办致辞现场</t>
+        </is>
+      </c>
+      <c r="C16" s="62" t="inlineStr">
+        <is>
+          <t>941A7851.JPG</t>
+        </is>
+      </c>
+      <c r="D16" s="60" t="inlineStr">
+        <is>
+          <t>2026-05-22 13:40:52</t>
+        </is>
+      </c>
+      <c r="E16" s="62" t="inlineStr">
+        <is>
+          <t>主办致辞全景：主会场双屏与讲台</t>
+        </is>
+      </c>
+      <c r="F16" s="60" t="inlineStr">
         <is>
           <t>主会场</t>
         </is>
       </c>
-      <c r="F9" s="76" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="22" customHeight="1" s="17">
-      <c r="A10" s="76" t="inlineStr">
-        <is>
-          <t>7</t>
-        </is>
-      </c>
-      <c r="B10" s="47" t="inlineStr">
-        <is>
-          <t>941A7825.JPG</t>
-        </is>
-      </c>
-      <c r="C10" s="76" t="inlineStr">
-        <is>
-          <t>2026-05-22 13:36:38</t>
-        </is>
-      </c>
-      <c r="D10" s="47" t="inlineStr">
-        <is>
-          <t>主持环节主会场全幅露出，便于核验现场执行</t>
-        </is>
-      </c>
-      <c r="E10" s="76" t="inlineStr">
+      <c r="G16" s="60" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="17" ht="22" customHeight="1" s="17">
+      <c r="A17" s="60" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="B17" s="62" t="inlineStr">
+        <is>
+          <t>四级 主办致辞现场</t>
+        </is>
+      </c>
+      <c r="C17" s="62" t="inlineStr">
+        <is>
+          <t>941A7836.JPG</t>
+        </is>
+      </c>
+      <c r="D17" s="60" t="inlineStr">
+        <is>
+          <t>2026-05-22 13:39:31</t>
+        </is>
+      </c>
+      <c r="E17" s="62" t="inlineStr">
+        <is>
+          <t>主办致辞：姚志勇，主会场主视觉</t>
+        </is>
+      </c>
+      <c r="F17" s="60" t="inlineStr">
         <is>
           <t>主会场</t>
         </is>
       </c>
-      <c r="F10" s="76" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="22" customHeight="1" s="17">
-      <c r="A11" s="76" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="B11" s="47" t="inlineStr">
-        <is>
-          <t>941A8810.JPG</t>
-        </is>
-      </c>
-      <c r="C11" s="76" t="inlineStr">
-        <is>
-          <t>2026-05-22 19:50:04</t>
-        </is>
-      </c>
-      <c r="D11" s="47" t="inlineStr">
-        <is>
-          <t>晚宴弧形大屏播放绿城中国「理想生活综合服务商」</t>
-        </is>
-      </c>
-      <c r="E11" s="76" t="inlineStr">
+      <c r="G17" s="60" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="18" ht="22" customHeight="1" s="17">
+      <c r="A18" s="60" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="B18" s="62" t="inlineStr">
+        <is>
+          <t>四级 主办致辞现场</t>
+        </is>
+      </c>
+      <c r="C18" s="62" t="inlineStr">
+        <is>
+          <t>941A7849.JPG</t>
+        </is>
+      </c>
+      <c r="D18" s="60" t="inlineStr">
+        <is>
+          <t>2026-05-22 13:40:40</t>
+        </is>
+      </c>
+      <c r="E18" s="62" t="inlineStr">
+        <is>
+          <t>主办致辞讲台特写</t>
+        </is>
+      </c>
+      <c r="F18" s="60" t="inlineStr">
+        <is>
+          <t>主会场</t>
+        </is>
+      </c>
+      <c r="G18" s="60" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="19" ht="22" customHeight="1" s="17">
+      <c r="A19" s="60" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="B19" s="62" t="inlineStr">
+        <is>
+          <t>五级 冠名晚宴氛围</t>
+        </is>
+      </c>
+      <c r="C19" s="62" t="inlineStr">
+        <is>
+          <t>941A8857.JPG</t>
+        </is>
+      </c>
+      <c r="D19" s="60" t="inlineStr">
+        <is>
+          <t>2026-05-22 20:25:29</t>
+        </is>
+      </c>
+      <c r="E19" s="62" t="inlineStr">
+        <is>
+          <t>冠名晚宴合影（江景厅）</t>
+        </is>
+      </c>
+      <c r="F19" s="60" t="inlineStr">
         <is>
           <t>晚宴冠名</t>
         </is>
       </c>
-      <c r="F11" s="76" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="22" customHeight="1" s="17">
-      <c r="A12" s="76" t="inlineStr">
-        <is>
-          <t>9</t>
-        </is>
-      </c>
-      <c r="B12" s="47" t="inlineStr">
-        <is>
-          <t>00_banner.jpg</t>
-        </is>
-      </c>
-      <c r="C12" s="76" t="inlineStr">
-        <is>
-          <t>主视觉 KV（相册 Banner）</t>
-        </is>
-      </c>
-      <c r="D12" s="47" t="inlineStr">
-        <is>
-          <t>主视觉 KV：战略合作伙伴名单含绿城中国</t>
-        </is>
-      </c>
-      <c r="E12" s="76" t="inlineStr">
-        <is>
-          <t>主会场/宣发</t>
-        </is>
-      </c>
-      <c r="F12" s="76" t="inlineStr">
-        <is>
-          <t>是</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="22" customHeight="1" s="17">
-      <c r="A13" s="42" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="B13" s="44" t="inlineStr">
-        <is>
-          <t>941A7777.JPG</t>
-        </is>
-      </c>
-      <c r="C13" s="42" t="inlineStr">
-        <is>
-          <t>2026-05-22 13:19:01</t>
-        </is>
-      </c>
-      <c r="D13" s="44" t="inlineStr">
-        <is>
-          <t>主背景板合影（晚宴冠名位特写）</t>
-        </is>
-      </c>
-      <c r="E13" s="42" t="inlineStr">
+      <c r="G19" s="60" t="inlineStr">
+        <is>
+          <t>否</t>
+        </is>
+      </c>
+    </row>
+    <row r="20" ht="22" customHeight="1" s="17">
+      <c r="A20" s="60" t="inlineStr">
+        <is>
+          <t>17</t>
+        </is>
+      </c>
+      <c r="B20" s="62" t="inlineStr">
+        <is>
+          <t>五级 冠名晚宴氛围</t>
+        </is>
+      </c>
+      <c r="C20" s="62" t="inlineStr">
+        <is>
+          <t>941A8881.JPG</t>
+        </is>
+      </c>
+      <c r="D20" s="60" t="inlineStr">
+        <is>
+          <t>2026-05-22 20:32:54</t>
+        </is>
+      </c>
+      <c r="E20" s="62" t="inlineStr">
+        <is>
+          <t>冠名晚宴桌次（江景厅圆桌）</t>
+        </is>
+      </c>
+      <c r="F20" s="60" t="inlineStr">
         <is>
           <t>晚宴冠名</t>
         </is>
       </c>
-      <c r="F13" s="42" t="inlineStr">
+      <c r="G20" s="60" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
     </row>
-    <row r="14" ht="22" customHeight="1" s="17">
-      <c r="A14" s="42" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
-      <c r="B14" s="44" t="inlineStr">
-        <is>
-          <t>941A7779.JPG</t>
-        </is>
-      </c>
-      <c r="C14" s="42" t="inlineStr">
-        <is>
-          <t>2026-05-22 13:19:08</t>
-        </is>
-      </c>
-      <c r="D14" s="44" t="inlineStr">
-        <is>
-          <t>主背景板双人合影核验冠名位</t>
-        </is>
-      </c>
-      <c r="E14" s="42" t="inlineStr">
+    <row r="21" ht="22" customHeight="1" s="17">
+      <c r="A21" s="60" t="inlineStr">
+        <is>
+          <t>18</t>
+        </is>
+      </c>
+      <c r="B21" s="62" t="inlineStr">
+        <is>
+          <t>五级 冠名晚宴氛围</t>
+        </is>
+      </c>
+      <c r="C21" s="62" t="inlineStr">
+        <is>
+          <t>941A8859.JPG</t>
+        </is>
+      </c>
+      <c r="D21" s="60" t="inlineStr">
+        <is>
+          <t>2026-05-22 20:26:10</t>
+        </is>
+      </c>
+      <c r="E21" s="62" t="inlineStr">
+        <is>
+          <t>冠名晚宴现场举杯</t>
+        </is>
+      </c>
+      <c r="F21" s="60" t="inlineStr">
         <is>
           <t>晚宴冠名</t>
         </is>
       </c>
-      <c r="F14" s="42" t="inlineStr">
+      <c r="G21" s="60" t="inlineStr">
         <is>
           <t>否</t>
         </is>
       </c>
     </row>
-    <row r="15" ht="22" customHeight="1" s="17">
-      <c r="A15" s="42" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="B15" s="44" t="inlineStr">
-        <is>
-          <t>941A7782.JPG</t>
-        </is>
-      </c>
-      <c r="C15" s="42" t="inlineStr">
-        <is>
-          <t>2026-05-22 13:19:19</t>
-        </is>
-      </c>
-      <c r="D15" s="44" t="inlineStr">
-        <is>
-          <t>主背景板合影：晚宴冠名战略合作伙伴·绿城中国</t>
-        </is>
-      </c>
-      <c r="E15" s="42" t="inlineStr">
-        <is>
-          <t>晚宴冠名</t>
-        </is>
-      </c>
-      <c r="F15" s="42" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="22" customHeight="1" s="17">
-      <c r="A16" s="42" t="inlineStr">
-        <is>
-          <t>13</t>
-        </is>
-      </c>
-      <c r="B16" s="44" t="inlineStr">
-        <is>
-          <t>941A7851.JPG</t>
-        </is>
-      </c>
-      <c r="C16" s="42" t="inlineStr">
-        <is>
-          <t>2026-05-22 13:40:52</t>
-        </is>
-      </c>
-      <c r="D16" s="44" t="inlineStr">
-        <is>
-          <t>主办致辞全景：主会场双屏与讲台</t>
-        </is>
-      </c>
-      <c r="E16" s="42" t="inlineStr">
-        <is>
-          <t>主会场</t>
-        </is>
-      </c>
-      <c r="F16" s="42" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="17" ht="22" customHeight="1" s="17">
-      <c r="A17" s="42" t="inlineStr">
-        <is>
-          <t>14</t>
-        </is>
-      </c>
-      <c r="B17" s="44" t="inlineStr">
-        <is>
-          <t>941A7836.JPG</t>
-        </is>
-      </c>
-      <c r="C17" s="42" t="inlineStr">
-        <is>
-          <t>2026-05-22 13:39:31</t>
-        </is>
-      </c>
-      <c r="D17" s="44" t="inlineStr">
-        <is>
-          <t>主办致辞：姚志勇，主会场主视觉</t>
-        </is>
-      </c>
-      <c r="E17" s="42" t="inlineStr">
-        <is>
-          <t>主会场</t>
-        </is>
-      </c>
-      <c r="F17" s="42" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="18" ht="22" customHeight="1" s="17">
-      <c r="A18" s="42" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="B18" s="44" t="inlineStr">
-        <is>
-          <t>941A7849.JPG</t>
-        </is>
-      </c>
-      <c r="C18" s="42" t="inlineStr">
-        <is>
-          <t>2026-05-22 13:40:40</t>
-        </is>
-      </c>
-      <c r="D18" s="44" t="inlineStr">
-        <is>
-          <t>主办致辞讲台特写</t>
-        </is>
-      </c>
-      <c r="E18" s="42" t="inlineStr">
-        <is>
-          <t>主会场</t>
-        </is>
-      </c>
-      <c r="F18" s="42" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="19" ht="22" customHeight="1" s="17">
-      <c r="A19" s="42" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="B19" s="44" t="inlineStr">
-        <is>
-          <t>941A8857.JPG</t>
-        </is>
-      </c>
-      <c r="C19" s="42" t="inlineStr">
-        <is>
-          <t>2026-05-22 20:25:29</t>
-        </is>
-      </c>
-      <c r="D19" s="44" t="inlineStr">
-        <is>
-          <t>冠名晚宴合影（江景厅）</t>
-        </is>
-      </c>
-      <c r="E19" s="42" t="inlineStr">
-        <is>
-          <t>晚宴冠名</t>
-        </is>
-      </c>
-      <c r="F19" s="42" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="20" ht="22" customHeight="1" s="17">
-      <c r="A20" s="42" t="inlineStr">
-        <is>
-          <t>17</t>
-        </is>
-      </c>
-      <c r="B20" s="44" t="inlineStr">
-        <is>
-          <t>941A8881.JPG</t>
-        </is>
-      </c>
-      <c r="C20" s="42" t="inlineStr">
-        <is>
-          <t>2026-05-22 20:32:54</t>
-        </is>
-      </c>
-      <c r="D20" s="44" t="inlineStr">
-        <is>
-          <t>冠名晚宴桌次（江景厅圆桌）</t>
-        </is>
-      </c>
-      <c r="E20" s="42" t="inlineStr">
-        <is>
-          <t>晚宴冠名</t>
-        </is>
-      </c>
-      <c r="F20" s="42" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
-    <row r="21" ht="22" customHeight="1" s="17">
-      <c r="A21" s="42" t="inlineStr">
-        <is>
-          <t>18</t>
-        </is>
-      </c>
-      <c r="B21" s="44" t="inlineStr">
-        <is>
-          <t>941A8859.JPG</t>
-        </is>
-      </c>
-      <c r="C21" s="42" t="inlineStr">
-        <is>
-          <t>2026-05-22 20:26:10</t>
-        </is>
-      </c>
-      <c r="D21" s="44" t="inlineStr">
-        <is>
-          <t>冠名晚宴现场举杯</t>
-        </is>
-      </c>
-      <c r="E21" s="42" t="inlineStr">
-        <is>
-          <t>晚宴冠名</t>
-        </is>
-      </c>
-      <c r="F21" s="42" t="inlineStr">
-        <is>
-          <t>否</t>
-        </is>
-      </c>
-    </row>
   </sheetData>
-  <autoFilter ref="A3:F21"/>
+  <autoFilter ref="A3:G21"/>
   <mergeCells count="2">
-    <mergeCell ref="A2:F2"/>
-    <mergeCell ref="A1:F1"/>
+    <mergeCell ref="A2:G2"/>
+    <mergeCell ref="A1:G1"/>
   </mergeCells>
   <pageMargins left="0.5" right="0.5" top="0.55" bottom="0.55" header="0.2" footer="0.2"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="1" fitToWidth="1"/>

--- a/deliverables/绿城·潮鸣外滩-营销验收单（甲方交付）.xlsx
+++ b/deliverables/绿城·潮鸣外滩-营销验收单（甲方交付）.xlsx
@@ -15,9 +15,9 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="照片索引" sheetId="7" state="visible" r:id="rId7"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm.Print_Area" localSheetId="0">'营销验收单'!$A$2:$D$18</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">'营销验收单'!$A$2:$D$28</definedName>
     <definedName name="_xlnm.Print_Titles" localSheetId="1">'按重要顺序分类'!$1:$2</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'按重要顺序分类'!$A$1:$D$35</definedName>
+    <definedName name="_xlnm.Print_Area" localSheetId="1">'按重要顺序分类'!$A$1:$D$18</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">'权益核验清单'!$A$1:$F$29</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="3">'效果评估表'!$A$1:$D$22</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="4">'赞助权益执行回执'!$A$1:$D$21</definedName>
@@ -33,7 +33,7 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="0"/>
-  <fonts count="50">
+  <fonts count="47">
     <font>
       <name val="等线"/>
       <charset val="134"/>
@@ -236,12 +236,31 @@
       <sz val="8"/>
     </font>
     <font>
-      <name val="微软雅黑"/>
-      <sz val="9"/>
+      <name val="黑体"/>
+      <b val="1"/>
+      <sz val="10"/>
+    </font>
+    <font>
+      <name val="黑体"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="黑体"/>
+      <b val="1"/>
+      <sz val="11"/>
+    </font>
+    <font>
+      <name val="黑体"/>
+      <b val="1"/>
+      <color rgb="00FFFFFF"/>
+      <sz val="12"/>
     </font>
     <font>
       <name val="微软雅黑"/>
-      <sz val="7"/>
+      <b val="1"/>
+      <sz val="10"/>
     </font>
     <font>
       <name val="微软雅黑"/>
@@ -267,46 +286,17 @@
     </font>
     <font>
       <name val="微软雅黑"/>
+      <sz val="9"/>
+    </font>
+    <font>
+      <name val="微软雅黑"/>
       <b val="1"/>
       <color rgb="00FFFFFF"/>
       <sz val="10"/>
     </font>
     <font>
-      <name val="微软雅黑"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="微软雅黑"/>
-      <b val="1"/>
-      <color rgb="00000000"/>
-      <sz val="10"/>
-    </font>
-    <font>
-      <name val="微软雅黑"/>
-      <color rgb="00000000"/>
-      <sz val="10"/>
-    </font>
-    <font>
       <name val="黑体"/>
       <b val="1"/>
-      <sz val="13"/>
-    </font>
-    <font>
-      <name val="黑体"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
-      <sz val="13"/>
-    </font>
-    <font>
-      <name val="黑体"/>
-      <b val="1"/>
-      <sz val="12"/>
-    </font>
-    <font>
-      <name val="黑体"/>
-      <b val="1"/>
-      <color rgb="00FFFFFF"/>
       <sz val="12"/>
     </font>
     <font>
@@ -327,11 +317,6 @@
       <name val="黑体"/>
       <b val="1"/>
       <sz val="18"/>
-    </font>
-    <font>
-      <name val="微软雅黑"/>
-      <b val="1"/>
-      <sz val="10"/>
     </font>
     <font>
       <name val="微软雅黑"/>
@@ -540,12 +525,12 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="00FFFFFF"/>
+        <fgColor rgb="001F6B4A"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="001F6B4A"/>
+        <fgColor rgb="00FFFFFF"/>
       </patternFill>
     </fill>
     <fill>
@@ -915,17 +900,6 @@
     </border>
     <border>
       <left/>
-      <right/>
-      <top style="thin">
-        <color rgb="00000000"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="00000000"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
       <right style="thin">
         <color rgb="00000000"/>
       </right>
@@ -1004,6 +978,17 @@
     <border>
       <left/>
       <right/>
+      <top style="thin">
+        <color rgb="00000000"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="00000000"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top/>
       <bottom style="thin">
         <color rgb="00000000"/>
@@ -1160,7 +1145,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="96">
+  <cellXfs count="86">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment vertical="center"/>
     </xf>
@@ -1223,108 +1208,83 @@
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="20" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="21" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="6" fillId="33" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="33" borderId="27" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="6" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="30" fillId="33" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="28" fillId="33" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="33" borderId="27" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="32" fillId="33" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="29" fillId="0" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="0" fillId="34" borderId="27" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="28" fillId="34" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="35" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="35" borderId="27" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="31" fillId="36" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="36" borderId="27" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="6" fillId="34" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="34" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="37" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="37" borderId="27" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="31" fillId="37" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="31" fillId="34" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="33" fillId="36" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="28" fillId="34" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="28" fillId="0" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="34" fillId="37" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="27" fillId="34" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="0" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="34" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="35" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="37" fillId="33" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="35" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="31" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="32" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="34" fillId="37" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="39" fillId="33" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="34" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="34" fillId="34" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="34" borderId="27" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="29" fillId="35" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="38" fillId="34" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="35" borderId="27" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="35" fillId="34" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="34" fillId="36" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="36" fillId="34" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="35" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="34" fillId="38" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="38" fillId="35" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="36" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="38" fillId="36" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="37" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="37" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="37" fillId="33" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="38" fillId="33" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="36" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="36" borderId="27" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="40" fillId="34" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="36" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="35" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="36" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="39" fillId="37" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="0" fillId="37" borderId="27" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="39" fillId="33" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="33" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="33" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="33" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="36" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="31" fillId="38" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="42" fillId="34" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="35" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1340,20 +1300,22 @@
     <xf numFmtId="0" fontId="26" fillId="36" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="43" fillId="33" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="41" fillId="34" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="44" fillId="33" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="42" fillId="34" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="30" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="29" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="31" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="32" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="33" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="36" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="34" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="35" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="37" pivotButton="0" quotePrefix="0" xfId="0"/>
-    <xf numFmtId="0" fontId="45" fillId="33" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="43" fillId="34" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="28" pivotButton="0" quotePrefix="0" xfId="0"/>
@@ -1361,28 +1323,22 @@
     <xf numFmtId="0" fontId="27" fillId="37" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
+    <xf numFmtId="0" fontId="43" fillId="34" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="41" fillId="38" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="38" fillId="38" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+    </xf>
     <xf numFmtId="0" fontId="45" fillId="33" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="43" fillId="38" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="29" fillId="38" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="47" fillId="36" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="27" fillId="33" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="48" fillId="34" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
     <xf numFmtId="0" fontId="27" fillId="36" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="27" fillId="33" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="27" fillId="34" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="26" fillId="36" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -1391,11 +1347,14 @@
     <xf numFmtId="0" fontId="26" fillId="37" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="26" fillId="33" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="26" fillId="34" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="29" fillId="36" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+    <xf numFmtId="0" fontId="38" fillId="36" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="34" fillId="36" borderId="27" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="49">
@@ -1458,19 +1417,44 @@
 <wsDr xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
   <oneCellAnchor>
     <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>7</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1600200" cy="876300"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="1" name="Image 1" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>5</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1638300" cy="1066800"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="1" name="Image 1" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId1"/>
+      <row>7</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1600200" cy="876300"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="2" name="Image 2" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId2"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -1485,17 +1469,17 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>5</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1638300" cy="1066800"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="2" name="Image 2" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId2"/>
+      <row>7</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1600200" cy="876300"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="3" name="Image 3" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId3"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -1510,17 +1494,42 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>5</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1638300" cy="1066800"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="3" name="Image 3" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId3"/>
+      <row>7</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1600200" cy="876300"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="4" name="Image 4" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId4"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>10</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1600200" cy="876300"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="5" name="Image 5" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId5"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -1535,17 +1544,17 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>7</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1638300" cy="1066800"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="4" name="Image 4" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId4"/>
+      <row>10</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1600200" cy="876300"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="6" name="Image 6" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId6"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -1560,17 +1569,17 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>7</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1638300" cy="1066800"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="5" name="Image 5" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId5"/>
+      <row>10</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1600200" cy="876300"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="7" name="Image 7" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId7"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -1585,17 +1594,42 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>7</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1638300" cy="1066800"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="6" name="Image 6" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId6"/>
+      <row>10</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1600200" cy="876300"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="8" name="Image 8" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId8"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>13</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1600200" cy="876300"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="9" name="Image 9" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId9"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -1610,17 +1644,17 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>9</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1638300" cy="1066800"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="7" name="Image 7" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId7"/>
+      <row>13</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1600200" cy="876300"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="10" name="Image 10" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId10"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -1635,17 +1669,17 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>9</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1638300" cy="1066800"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="8" name="Image 8" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId8"/>
+      <row>13</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1600200" cy="876300"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="11" name="Image 11" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId11"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -1660,17 +1694,167 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>9</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1638300" cy="1066800"/>
-    <pic>
-      <nvPicPr>
-        <cNvPr id="9" name="Image 9" descr="Picture"/>
-        <cNvPicPr/>
-      </nvPicPr>
-      <blipFill>
-        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId9"/>
+      <row>13</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1600200" cy="876300"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="12" name="Image 12" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId12"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>17</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1504950" cy="800100"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="13" name="Image 13" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId13"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>17</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1504950" cy="800100"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="14" name="Image 14" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId14"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>17</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1504950" cy="800100"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="15" name="Image 15" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId15"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>0</col>
+      <colOff>0</colOff>
+      <row>20</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1504950" cy="800100"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="16" name="Image 16" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId16"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>1</col>
+      <colOff>0</colOff>
+      <row>20</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1504950" cy="800100"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="17" name="Image 17" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId17"/>
+        <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+          <a:fillRect/>
+        </a:stretch>
+      </blipFill>
+      <spPr>
+        <a:prstGeom xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" prst="rect"/>
+      </spPr>
+    </pic>
+    <clientData/>
+  </oneCellAnchor>
+  <oneCellAnchor>
+    <from>
+      <col>2</col>
+      <colOff>0</colOff>
+      <row>20</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1504950" cy="800100"/>
+    <pic>
+      <nvPicPr>
+        <cNvPr id="18" name="Image 18" descr="Picture"/>
+        <cNvPicPr/>
+      </nvPicPr>
+      <blipFill>
+        <a:blip xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" cstate="print" r:embed="rId18"/>
         <a:stretch xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
           <a:fillRect/>
         </a:stretch>
@@ -1690,10 +1874,10 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>12</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1771650" cy="1257300"/>
+      <row>3</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1866900" cy="1314450"/>
     <pic>
       <nvPicPr>
         <cNvPr id="1" name="Image 1" descr="Picture"/>
@@ -1715,10 +1899,10 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>12</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1771650" cy="1257300"/>
+      <row>3</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1866900" cy="1314450"/>
     <pic>
       <nvPicPr>
         <cNvPr id="2" name="Image 2" descr="Picture"/>
@@ -1740,10 +1924,10 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>12</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1771650" cy="1257300"/>
+      <row>3</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1866900" cy="1314450"/>
     <pic>
       <nvPicPr>
         <cNvPr id="3" name="Image 3" descr="Picture"/>
@@ -1765,10 +1949,10 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>12</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1771650" cy="1257300"/>
+      <row>3</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1866900" cy="1314450"/>
     <pic>
       <nvPicPr>
         <cNvPr id="4" name="Image 4" descr="Picture"/>
@@ -1790,10 +1974,10 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>17</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1771650" cy="1257300"/>
+      <row>6</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1866900" cy="1314450"/>
     <pic>
       <nvPicPr>
         <cNvPr id="5" name="Image 5" descr="Picture"/>
@@ -1815,10 +1999,10 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>17</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1771650" cy="1257300"/>
+      <row>6</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1866900" cy="1314450"/>
     <pic>
       <nvPicPr>
         <cNvPr id="6" name="Image 6" descr="Picture"/>
@@ -1840,10 +2024,10 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>17</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1771650" cy="1257300"/>
+      <row>6</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1866900" cy="1314450"/>
     <pic>
       <nvPicPr>
         <cNvPr id="7" name="Image 7" descr="Picture"/>
@@ -1865,10 +2049,10 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>17</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1771650" cy="1257300"/>
+      <row>6</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1866900" cy="1314450"/>
     <pic>
       <nvPicPr>
         <cNvPr id="8" name="Image 8" descr="Picture"/>
@@ -1890,10 +2074,10 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>22</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1771650" cy="1257300"/>
+      <row>9</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1866900" cy="1314450"/>
     <pic>
       <nvPicPr>
         <cNvPr id="9" name="Image 9" descr="Picture"/>
@@ -1915,10 +2099,10 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>22</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1771650" cy="1257300"/>
+      <row>9</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1866900" cy="1314450"/>
     <pic>
       <nvPicPr>
         <cNvPr id="10" name="Image 10" descr="Picture"/>
@@ -1940,10 +2124,10 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>22</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1771650" cy="1257300"/>
+      <row>9</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1866900" cy="1314450"/>
     <pic>
       <nvPicPr>
         <cNvPr id="11" name="Image 11" descr="Picture"/>
@@ -1965,10 +2149,10 @@
     <from>
       <col>3</col>
       <colOff>0</colOff>
-      <row>22</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1771650" cy="1257300"/>
+      <row>9</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1866900" cy="1314450"/>
     <pic>
       <nvPicPr>
         <cNvPr id="12" name="Image 12" descr="Picture"/>
@@ -1990,10 +2174,10 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>27</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1771650" cy="1257300"/>
+      <row>13</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1771650" cy="1219200"/>
     <pic>
       <nvPicPr>
         <cNvPr id="13" name="Image 13" descr="Picture"/>
@@ -2015,10 +2199,10 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>27</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1771650" cy="1257300"/>
+      <row>13</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1771650" cy="1219200"/>
     <pic>
       <nvPicPr>
         <cNvPr id="14" name="Image 14" descr="Picture"/>
@@ -2040,10 +2224,10 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>27</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1771650" cy="1257300"/>
+      <row>13</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1771650" cy="1219200"/>
     <pic>
       <nvPicPr>
         <cNvPr id="15" name="Image 15" descr="Picture"/>
@@ -2065,10 +2249,10 @@
     <from>
       <col>0</col>
       <colOff>0</colOff>
-      <row>32</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1771650" cy="1257300"/>
+      <row>16</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1771650" cy="1219200"/>
     <pic>
       <nvPicPr>
         <cNvPr id="16" name="Image 16" descr="Picture"/>
@@ -2090,10 +2274,10 @@
     <from>
       <col>1</col>
       <colOff>0</colOff>
-      <row>32</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1771650" cy="1257300"/>
+      <row>16</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1771650" cy="1219200"/>
     <pic>
       <nvPicPr>
         <cNvPr id="17" name="Image 17" descr="Picture"/>
@@ -2115,10 +2299,10 @@
     <from>
       <col>2</col>
       <colOff>0</colOff>
-      <row>32</row>
-      <rowOff>0</rowOff>
-    </from>
-    <ext cx="1771650" cy="1257300"/>
+      <row>16</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="1771650" cy="1219200"/>
     <pic>
       <nvPicPr>
         <cNvPr id="18" name="Image 18" descr="Picture"/>
@@ -3571,13 +3755,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A2:D21"/>
+  <dimension ref="A2:D28"/>
   <sheetFormatPr baseColWidth="8" defaultColWidth="10.6696428571429" defaultRowHeight="16.8"/>
   <cols>
-    <col width="15.6696428571429" customWidth="1" style="17" min="1" max="1"/>
-    <col width="29.2857142857143" customWidth="1" style="17" min="2" max="2"/>
-    <col width="25.4642857142857" customWidth="1" style="17" min="3" max="3"/>
-    <col width="27.1964285714286" customWidth="1" style="17" min="4" max="4"/>
+    <col width="22" customWidth="1" style="17" min="1" max="1"/>
+    <col width="24" customWidth="1" style="17" min="2" max="2"/>
+    <col width="24" customWidth="1" style="17" min="3" max="3"/>
+    <col width="24" customWidth="1" style="17" min="4" max="4"/>
   </cols>
   <sheetData>
     <row r="2" ht="59" customHeight="1" s="17">
@@ -3640,7 +3824,7 @@
         </is>
       </c>
     </row>
-    <row r="5" ht="118" customHeight="1" s="17">
+    <row r="5" ht="96" customHeight="1" s="17">
       <c r="A5" s="13" t="inlineStr">
         <is>
           <t>事项描述</t>
@@ -3659,245 +3843,320 @@
       <c r="C5" s="22" t="n"/>
       <c r="D5" s="23" t="n"/>
     </row>
-    <row r="6" ht="90" customHeight="1" s="17">
-      <c r="A6" s="13" t="inlineStr">
-        <is>
-          <t>验收照片</t>
-        </is>
-      </c>
-      <c r="B6" s="24" t="n"/>
+    <row r="6" ht="22" customHeight="1" s="17">
+      <c r="A6" s="24" t="inlineStr">
+        <is>
+          <t>验收照片 · 五级排列（18 张全部嵌入）　前三级集中前置：一级核心露出 → 二级主会场 → 三级冠名合影</t>
+        </is>
+      </c>
+      <c r="B6" s="25" t="n"/>
       <c r="C6" s="25" t="n"/>
       <c r="D6" s="25" t="n"/>
     </row>
-    <row r="7" ht="34" customHeight="1" s="17">
-      <c r="A7" s="26" t="n"/>
-      <c r="B7" s="27" t="inlineStr">
-        <is>
-          <t>①议程看板【绿城·潮鸣】晚宴冠名</t>
-        </is>
-      </c>
-      <c r="C7" s="27" t="inlineStr">
-        <is>
-          <t>②主背景板：晚宴冠名·绿城中国</t>
-        </is>
-      </c>
-      <c r="D7" s="27" t="inlineStr">
-        <is>
-          <t>③展台立牌：绿城中国 GREENTOWN</t>
-        </is>
-      </c>
-    </row>
-    <row r="8" ht="90" customHeight="1" s="17">
-      <c r="A8" s="26" t="n"/>
-      <c r="B8" s="25" t="n"/>
-      <c r="C8" s="25" t="n"/>
-      <c r="D8" s="25" t="n"/>
-    </row>
-    <row r="9" ht="34" customHeight="1" s="17">
-      <c r="A9" s="26" t="n"/>
-      <c r="B9" s="27" t="inlineStr">
-        <is>
-          <t>④展台接待：绿城礼袋与物料</t>
-        </is>
-      </c>
-      <c r="C9" s="27" t="inlineStr">
-        <is>
-          <t>⑤主背景板合影核验冠名位</t>
-        </is>
-      </c>
-      <c r="D9" s="27" t="inlineStr">
-        <is>
-          <t>⑥主会场双屏（同款主视觉）</t>
-        </is>
-      </c>
-    </row>
-    <row r="10" ht="90" customHeight="1" s="17">
-      <c r="A10" s="26" t="n"/>
-      <c r="B10" s="25" t="n"/>
-      <c r="C10" s="25" t="n"/>
-      <c r="D10" s="25" t="n"/>
-    </row>
-    <row r="11" ht="34" customHeight="1" s="17">
-      <c r="A11" s="26" t="n"/>
-      <c r="B11" s="27" t="inlineStr">
-        <is>
-          <t>⑦主持现场：主会场露出</t>
-        </is>
-      </c>
-      <c r="C11" s="27" t="inlineStr">
-        <is>
-          <t>⑧晚宴大屏：绿城中国品牌片</t>
-        </is>
-      </c>
-      <c r="D11" s="27" t="inlineStr">
-        <is>
-          <t>⑨主视觉 KV：战略合作含绿城</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="22" customHeight="1" s="17">
-      <c r="A12" s="28" t="n"/>
-      <c r="B12" s="29" t="inlineStr">
-        <is>
-          <t>图①–⑨对应「权益核验清单」。他方品牌展位、晚宴席卡姓名卡不作为潮鸣 logo 证据。</t>
-        </is>
-      </c>
-      <c r="C12" s="30" t="n"/>
-      <c r="D12" s="31" t="n"/>
-    </row>
-    <row r="13" ht="52" customHeight="1" s="17">
-      <c r="A13" s="13" t="inlineStr">
+    <row r="7" ht="20" customHeight="1" s="17">
+      <c r="A7" s="26" t="inlineStr">
+        <is>
+          <t>一级｜核心品牌露出（必看）（4 张）</t>
+        </is>
+      </c>
+      <c r="B7" s="25" t="n"/>
+      <c r="C7" s="25" t="n"/>
+      <c r="D7" s="25" t="n"/>
+    </row>
+    <row r="8" ht="92" customHeight="1" s="17">
+      <c r="A8" s="27" t="n"/>
+      <c r="B8" s="27" t="n"/>
+      <c r="C8" s="27" t="n"/>
+      <c r="D8" s="27" t="n"/>
+    </row>
+    <row r="9" ht="36" customHeight="1" s="17">
+      <c r="A9" s="28" t="inlineStr">
+        <is>
+          <t>议程看板【绿城·潮鸣】星耀北外滩晚宴</t>
+        </is>
+      </c>
+      <c r="B9" s="28" t="inlineStr">
+        <is>
+          <t>主背景板：晚宴冠名战略合作伙伴·绿城中国</t>
+        </is>
+      </c>
+      <c r="C9" s="28" t="inlineStr">
+        <is>
+          <t>展台立牌：绿城中国 GREENTOWN</t>
+        </is>
+      </c>
+      <c r="D9" s="28" t="inlineStr">
+        <is>
+          <t>晚宴大屏播放绿城中国品牌片</t>
+        </is>
+      </c>
+    </row>
+    <row r="10" ht="20" customHeight="1" s="17">
+      <c r="A10" s="29" t="inlineStr">
+        <is>
+          <t>二级｜主会场执行（重点）（4 张）</t>
+        </is>
+      </c>
+      <c r="B10" s="30" t="n"/>
+      <c r="C10" s="30" t="n"/>
+      <c r="D10" s="30" t="n"/>
+    </row>
+    <row r="11" ht="92" customHeight="1" s="17">
+      <c r="A11" s="27" t="n"/>
+      <c r="B11" s="27" t="n"/>
+      <c r="C11" s="27" t="n"/>
+      <c r="D11" s="27" t="n"/>
+    </row>
+    <row r="12" ht="36" customHeight="1" s="17">
+      <c r="A12" s="28" t="inlineStr">
+        <is>
+          <t>展台接待：绿城立牌、礼袋与物料</t>
+        </is>
+      </c>
+      <c r="B12" s="28" t="inlineStr">
+        <is>
+          <t>主会场双屏同款主视觉（含晚宴冠名·绿城中国）</t>
+        </is>
+      </c>
+      <c r="C12" s="28" t="inlineStr">
+        <is>
+          <t>主持现场：主会场露出</t>
+        </is>
+      </c>
+      <c r="D12" s="28" t="inlineStr">
+        <is>
+          <t>主视觉 KV：战略合作名单含绿城中国</t>
+        </is>
+      </c>
+    </row>
+    <row r="13" ht="20" customHeight="1" s="17">
+      <c r="A13" s="31" t="inlineStr">
+        <is>
+          <t>三级｜冠名位合影核验（4 张）</t>
+        </is>
+      </c>
+      <c r="B13" s="32" t="n"/>
+      <c r="C13" s="32" t="n"/>
+      <c r="D13" s="32" t="n"/>
+    </row>
+    <row r="14" ht="92" customHeight="1" s="17">
+      <c r="A14" s="27" t="n"/>
+      <c r="B14" s="33" t="n"/>
+      <c r="C14" s="34" t="n"/>
+      <c r="D14" s="27" t="n"/>
+    </row>
+    <row r="15" ht="36" customHeight="1" s="17">
+      <c r="A15" s="28" t="inlineStr">
+        <is>
+          <t>主背景板合影核验冠名位</t>
+        </is>
+      </c>
+      <c r="B15" s="28" t="inlineStr">
+        <is>
+          <t>主背景板合影（冠名位特写）</t>
+        </is>
+      </c>
+      <c r="C15" s="28" t="inlineStr">
+        <is>
+          <t>主背景板双人合影核验冠名位</t>
+        </is>
+      </c>
+      <c r="D15" s="28" t="inlineStr">
+        <is>
+          <t>主背景板合影：晚宴冠名战略合作伙伴·绿城中国</t>
+        </is>
+      </c>
+    </row>
+    <row r="16" ht="18" customHeight="1" s="17">
+      <c r="A16" s="35" t="inlineStr">
+        <is>
+          <t>四级、五级为补充现场（主办致辞 / 晚宴氛围），仍全部嵌入，不作参观邀约或潮鳴 logo 桌卡证据。</t>
+        </is>
+      </c>
+      <c r="B16" s="36" t="n"/>
+      <c r="C16" s="36" t="n"/>
+      <c r="D16" s="36" t="n"/>
+    </row>
+    <row r="17" ht="20" customHeight="1" s="17">
+      <c r="A17" s="37" t="inlineStr">
+        <is>
+          <t>四级｜主办致辞现场（3 张）</t>
+        </is>
+      </c>
+      <c r="B17" s="36" t="n"/>
+      <c r="C17" s="36" t="n"/>
+      <c r="D17" s="36" t="n"/>
+    </row>
+    <row r="18" ht="84" customHeight="1" s="17">
+      <c r="A18" s="27" t="n"/>
+      <c r="B18" s="33" t="n"/>
+      <c r="C18" s="34" t="n"/>
+      <c r="D18" s="27" t="n"/>
+    </row>
+    <row r="19" ht="36" customHeight="1" s="17">
+      <c r="A19" s="28" t="inlineStr">
+        <is>
+          <t>主办致辞全景：主会场双屏与讲台</t>
+        </is>
+      </c>
+      <c r="B19" s="28" t="inlineStr">
+        <is>
+          <t>主办致辞：姚志勇，主会场主视觉</t>
+        </is>
+      </c>
+      <c r="C19" s="28" t="inlineStr">
+        <is>
+          <t>主办致辞讲台特写</t>
+        </is>
+      </c>
+      <c r="D19" s="27" t="n"/>
+    </row>
+    <row r="20" ht="20" customHeight="1" s="17">
+      <c r="A20" s="38" t="inlineStr">
+        <is>
+          <t>五级｜冠名晚宴氛围（3 张）</t>
+        </is>
+      </c>
+      <c r="B20" s="27" t="n"/>
+      <c r="C20" s="27" t="n"/>
+      <c r="D20" s="27" t="n"/>
+    </row>
+    <row r="21" ht="84" customHeight="1" s="17">
+      <c r="A21" s="27" t="n"/>
+      <c r="B21" s="27" t="n"/>
+      <c r="C21" s="27" t="n"/>
+      <c r="D21" s="27" t="n"/>
+    </row>
+    <row r="22" ht="36" customHeight="1" s="17">
+      <c r="A22" s="28" t="inlineStr">
+        <is>
+          <t>冠名晚宴合影（江景厅）</t>
+        </is>
+      </c>
+      <c r="B22" s="28" t="inlineStr">
+        <is>
+          <t>冠名晚宴桌次（江景厅圆桌）</t>
+        </is>
+      </c>
+      <c r="C22" s="28" t="inlineStr">
+        <is>
+          <t>冠名晚宴现场举杯</t>
+        </is>
+      </c>
+      <c r="D22" s="27" t="n"/>
+    </row>
+    <row r="23" ht="56" customHeight="1" s="17">
+      <c r="A23" s="39" t="inlineStr">
         <is>
           <t>效果评估</t>
         </is>
       </c>
-      <c r="B13" s="32" t="inlineStr">
-        <is>
-          <t>【露出】本页 9 张为封面摘要；全部 18 张已按一级至五级嵌入「按重要顺序分类」。
+      <c r="B23" s="40" t="inlineStr">
+        <is>
+          <t>【露出】本页 18 张按五级全部嵌入，一级至三级集中排在最前。
 【营销评估】非常好（☐）　良好（☑）　一般（☐）　较差（☐）
 【打包验收】四模块整体打包。参观邀约无单独成片、朋友圈九宫格 / 回顾视频未附本表，见「权益核验清单」黄底项。已核验露出效果良好，符合约定要求。</t>
         </is>
       </c>
-      <c r="C13" s="22" t="n"/>
-      <c r="D13" s="23" t="n"/>
-    </row>
-    <row r="14" hidden="1" ht="18" customHeight="1" s="17">
-      <c r="A14" s="26" t="n"/>
-      <c r="B14" s="15" t="inlineStr">
+      <c r="C23" s="27" t="n"/>
+      <c r="D23" s="27" t="n"/>
+    </row>
+    <row r="24" ht="72" customHeight="1" s="17">
+      <c r="A24" s="39" t="inlineStr">
+        <is>
+          <t>附件</t>
+        </is>
+      </c>
+      <c r="B24" s="28" t="inlineStr">
+        <is>
+          <t>①本页 18 张五级排列，前三级集中前置；②「按重要顺序分类」同序大图；③「权益核验清单」按报价单 4 模块嵌全部对应照片；④「效果评估表」；⑤「赞助权益执行回执」；⑥「照片索引」含重要等级；⑦拍立享 https://live.pailixiang.com/album/a12523836160（约 425 张，本表为精华筛选）；⑧全程录像 https://pan.baidu.com/s/1S8cNdqnCR_anuVPD6vlhjg 提取码 8888。不与 2026年3月开盘花束验收混用。未把美年大健康 / 泰隆 / 腾讯云 / 蔚来展位当作绿城露出。</t>
+        </is>
+      </c>
+      <c r="C24" s="27" t="n"/>
+      <c r="D24" s="27" t="n"/>
+    </row>
+    <row r="25" ht="36" customHeight="1" s="17">
+      <c r="A25" s="39" t="inlineStr">
+        <is>
+          <t>验收确认</t>
+        </is>
+      </c>
+      <c r="B25" s="41" t="inlineStr">
         <is>
           <t>执行人/策划负责人</t>
         </is>
       </c>
-      <c r="C14" s="16" t="inlineStr">
-        <is>
-          <t>胡继刚
-13262607888
-（主办执行）
-签字：____________</t>
-        </is>
-      </c>
-      <c r="D14" s="23" t="n"/>
-    </row>
-    <row r="15" hidden="1" ht="18" customHeight="1" s="17">
-      <c r="A15" s="28" t="n"/>
-      <c r="B15" s="15" t="inlineStr">
+      <c r="C25" s="42" t="inlineStr">
+        <is>
+          <t>胡继刚　13262607888（主办执行）　签字：____________</t>
+        </is>
+      </c>
+      <c r="D25" s="27" t="n"/>
+    </row>
+    <row r="26" ht="36" customHeight="1" s="17">
+      <c r="A26" s="27" t="n"/>
+      <c r="B26" s="41" t="inlineStr">
         <is>
           <t>营销负责人</t>
         </is>
       </c>
-      <c r="C15" s="16" t="inlineStr">
-        <is>
-          <t>绿城对接：笪浩 18678408669
-营销负责人签字：____________
-日期：____________</t>
-        </is>
-      </c>
-      <c r="D15" s="23" t="n"/>
-    </row>
-    <row r="16" ht="108" customHeight="1" s="17">
-      <c r="A16" s="13" t="inlineStr">
-        <is>
-          <t>附件</t>
-        </is>
-      </c>
-      <c r="B16" s="33" t="inlineStr">
-        <is>
-          <t>①本页 9 张为封面摘要，含图注；②「按重要顺序分类」将 18 张精华图全部按五级嵌入表格；③「权益核验清单」按报价单 4 模块嵌全部对应照片；④「绿城·潮鸣外滩露出」为大图（同序分级）；⑤「效果评估表」按绿城中国策划活动类效果评估表结构；⑥「赞助权益执行回执」供绿城复核盖章；⑦「照片索引」含重要等级、拍摄时间与模块对照；⑧拍立享直播 https://live.pailixiang.com/album/a12523836160（相册约 425 张，本表为精华筛选）；⑨全程录像 https://pan.baidu.com/s/1S8cNdqnCR_anuVPD6vlhjg 提取码 8888。本表不与 2026年3月开盘花束验收混用。未把美年大健康 / 泰隆银行 / 腾讯云 / 蔚来展位当作绿城露出。</t>
-        </is>
-      </c>
-      <c r="C16" s="22" t="n"/>
-      <c r="D16" s="23" t="n"/>
-    </row>
-    <row r="17" ht="82" customHeight="1" s="17">
-      <c r="A17" s="13" t="inlineStr">
-        <is>
-          <t>验收确认</t>
-        </is>
-      </c>
-      <c r="B17" s="15" t="inlineStr">
-        <is>
-          <t>执行人/策划负责人</t>
-        </is>
-      </c>
-      <c r="C17" s="34" t="inlineStr">
-        <is>
-          <t>胡继刚
-13262607888
-（主办执行）
-签字：____________</t>
-        </is>
-      </c>
-      <c r="D17" s="23" t="n"/>
-    </row>
-    <row r="18" ht="100" customHeight="1" s="17">
-      <c r="A18" s="28" t="n"/>
-      <c r="B18" s="15" t="inlineStr">
-        <is>
-          <t>营销负责人</t>
-        </is>
-      </c>
-      <c r="C18" s="34" t="inlineStr">
-        <is>
-          <t>绿城对接：笪浩 18678408669
-营销负责人签字：____________
-日期：____________</t>
-        </is>
-      </c>
-      <c r="D18" s="23" t="n"/>
-    </row>
-    <row r="19" ht="100" customHeight="1" s="17"/>
-    <row r="20" ht="100" customHeight="1" s="17">
-      <c r="A20" s="35" t="inlineStr">
+      <c r="C26" s="42" t="inlineStr">
+        <is>
+          <t>绿城对接：笪浩 18678408669　签字：____________　日期：____________</t>
+        </is>
+      </c>
+      <c r="D26" s="27" t="n"/>
+    </row>
+    <row r="27" ht="18" customHeight="1" s="17">
+      <c r="A27" s="43" t="inlineStr">
         <is>
           <t>照片直播（拍立享）</t>
         </is>
       </c>
-      <c r="B20" s="36" t="inlineStr">
+      <c r="B27" s="44" t="inlineStr">
         <is>
           <t>https://live.pailixiang.com/album/a12523836160</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="100" customHeight="1" s="17">
-      <c r="A21" s="35" t="inlineStr">
+    <row r="28" ht="18" customHeight="1" s="17">
+      <c r="A28" s="43" t="inlineStr">
         <is>
           <t>全程录像（百度网盘）</t>
         </is>
       </c>
-      <c r="B21" s="36" t="inlineStr">
+      <c r="B28" s="44" t="inlineStr">
         <is>
           <t>https://pan.baidu.com/s/1S8cNdqnCR_anuVPD6vlhjg  提取码：8888</t>
         </is>
       </c>
     </row>
-    <row r="22" ht="100" customHeight="1" s="17"/>
-    <row r="23" ht="100" customHeight="1" s="17"/>
-    <row r="24" ht="100" customHeight="1" s="17"/>
-    <row r="25" ht="100" customHeight="1" s="17"/>
-    <row r="26" ht="100" customHeight="1" s="17"/>
   </sheetData>
-  <mergeCells count="14">
+  <mergeCells count="17">
+    <mergeCell ref="A17:D17"/>
     <mergeCell ref="B5:D5"/>
-    <mergeCell ref="A17:A18"/>
-    <mergeCell ref="C15:D15"/>
-    <mergeCell ref="B20:D20"/>
-    <mergeCell ref="B13:D13"/>
-    <mergeCell ref="C14:D14"/>
-    <mergeCell ref="B12:D12"/>
-    <mergeCell ref="B21:D21"/>
+    <mergeCell ref="A6:D6"/>
+    <mergeCell ref="B23:D23"/>
+    <mergeCell ref="A20:D20"/>
+    <mergeCell ref="A7:D7"/>
+    <mergeCell ref="A16:D16"/>
+    <mergeCell ref="A10:D10"/>
+    <mergeCell ref="C26:D26"/>
+    <mergeCell ref="A13:D13"/>
+    <mergeCell ref="B28:D28"/>
+    <mergeCell ref="A25:A26"/>
+    <mergeCell ref="C25:D25"/>
+    <mergeCell ref="B27:D27"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="C18:D18"/>
-    <mergeCell ref="A6:A12"/>
-    <mergeCell ref="C17:D17"/>
-    <mergeCell ref="B16:D16"/>
-    <mergeCell ref="A13:A15"/>
+    <mergeCell ref="B24:D24"/>
+    <mergeCell ref="A23"/>
   </mergeCells>
   <hyperlinks>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B20" r:id="rId1"/>
-    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B21" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B27" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="B28" r:id="rId2"/>
   </hyperlinks>
   <pageMargins left="0.5" right="0.5" top="0.55" bottom="0.55" header="0.2" footer="0.2"/>
-  <pageSetup orientation="portrait" paperSize="9" scale="69" fitToHeight="1" fitToWidth="1"/>
+  <pageSetup orientation="portrait" paperSize="9" scale="69" fitToHeight="0" fitToWidth="1"/>
   <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId3"/>
 </worksheet>
 </file>
@@ -3909,7 +4168,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
-  <dimension ref="A1:D34"/>
+  <dimension ref="A1:D18"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" style="17" min="1" max="1"/>
@@ -3919,414 +4178,227 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1" s="17">
-      <c r="A1" s="37" t="inlineStr">
+      <c r="A1" s="45" t="inlineStr">
         <is>
           <t>绿城·潮鸣外滩 · 精华照片按重要顺序分类（18 张全部嵌入本表）</t>
         </is>
       </c>
-      <c r="B1" s="38" t="n"/>
-      <c r="C1" s="38" t="n"/>
-      <c r="D1" s="38" t="n"/>
-    </row>
-    <row r="2" ht="36" customHeight="1" s="17">
-      <c r="A2" s="39" t="inlineStr">
-        <is>
-          <t>排序：一级核心品牌露出 → 二级主会场执行 → 三级冠名位合影 → 四级主办致辞 → 五级晚宴氛围。只收录绿城 / 潮鸣 / GREENTOWN 可核验露出。本页表格已嵌入全部精华原图，可直接给甲方按等级复核。</t>
-        </is>
-      </c>
-      <c r="B2" s="40" t="n"/>
-      <c r="C2" s="40" t="n"/>
-      <c r="D2" s="40" t="n"/>
+      <c r="B1" s="25" t="n"/>
+      <c r="C1" s="25" t="n"/>
+      <c r="D1" s="25" t="n"/>
+    </row>
+    <row r="2" ht="28" customHeight="1" s="17">
+      <c r="A2" s="46" t="inlineStr">
+        <is>
+          <t>前三级集中前置（12 张）：一级核心品牌露出 → 二级主会场执行 → 三级冠名位合影。四级主办致辞、五级晚宴氛围为补充（6 张）。合计 18 张全部嵌入。只收录绿城 / 潮鸣 / GREENTOWN 可核验露出。</t>
+        </is>
+      </c>
+      <c r="B2" s="30" t="n"/>
+      <c r="C2" s="30" t="n"/>
+      <c r="D2" s="30" t="n"/>
     </row>
     <row r="3" ht="22" customHeight="1" s="17">
-      <c r="A3" s="41" t="inlineStr">
-        <is>
-          <t>重要等级</t>
-        </is>
-      </c>
-      <c r="B3" s="41" t="inlineStr">
-        <is>
-          <t>分类</t>
-        </is>
-      </c>
-      <c r="C3" s="41" t="inlineStr">
-        <is>
-          <t>张数</t>
-        </is>
-      </c>
-      <c r="D3" s="41" t="inlineStr">
-        <is>
-          <t>核验要点</t>
-        </is>
-      </c>
-    </row>
-    <row r="4" ht="36" customHeight="1" s="17">
-      <c r="A4" s="41" t="inlineStr">
-        <is>
-          <t>一级</t>
-        </is>
-      </c>
-      <c r="B4" s="41" t="inlineStr">
-        <is>
-          <t>核心品牌露出（必看）</t>
-        </is>
-      </c>
-      <c r="C4" s="41" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="D4" s="42" t="inlineStr">
-        <is>
-          <t>绿城 / 潮鸣 / GREENTOWN 字样可直接核验，对应报价主体，建议甲方优先复核。</t>
-        </is>
-      </c>
+      <c r="A3" s="26" t="inlineStr">
+        <is>
+          <t>一级｜核心品牌露出（必看）（4 张）　绿城 / 潮鸣 / GREENTOWN 字样可直接核验，对应报价主体，建议甲方优先复核。</t>
+        </is>
+      </c>
+      <c r="B3" s="25" t="n"/>
+      <c r="C3" s="25" t="n"/>
+      <c r="D3" s="25" t="n"/>
+    </row>
+    <row r="4" ht="138" customHeight="1" s="17">
+      <c r="A4" s="27" t="n"/>
+      <c r="B4" s="27" t="n"/>
+      <c r="C4" s="27" t="n"/>
+      <c r="D4" s="27" t="n"/>
     </row>
     <row r="5" ht="36" customHeight="1" s="17">
-      <c r="A5" s="43" t="inlineStr">
-        <is>
-          <t>二级</t>
-        </is>
-      </c>
-      <c r="B5" s="43" t="inlineStr">
-        <is>
-          <t>主会场执行（重点）</t>
-        </is>
-      </c>
-      <c r="C5" s="43" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="D5" s="44" t="inlineStr">
-        <is>
-          <t>展台接待、双屏、主持、主视觉，证明主会场权益已落地。</t>
-        </is>
-      </c>
-    </row>
-    <row r="6" ht="36" customHeight="1" s="17">
-      <c r="A6" s="45" t="inlineStr">
-        <is>
-          <t>三级</t>
-        </is>
-      </c>
-      <c r="B6" s="45" t="inlineStr">
-        <is>
-          <t>冠名位合影核验</t>
-        </is>
-      </c>
-      <c r="C6" s="45" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="D6" s="46" t="inlineStr">
-        <is>
-          <t>主背景板合影，可复核晚宴冠名位「绿城中国」。</t>
-        </is>
-      </c>
-    </row>
-    <row r="7" ht="36" customHeight="1" s="17">
-      <c r="A7" s="47" t="inlineStr">
-        <is>
-          <t>四级</t>
-        </is>
-      </c>
-      <c r="B7" s="47" t="inlineStr">
-        <is>
-          <t>主办致辞现场</t>
-        </is>
-      </c>
-      <c r="C7" s="47" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="D7" s="48" t="inlineStr">
-        <is>
-          <t>主会场致辞与讲台，补充现场执行；不作参观邀约专项成片。</t>
-        </is>
-      </c>
+      <c r="A5" s="28" t="inlineStr">
+        <is>
+          <t>议程看板【绿城·潮鸣】星耀北外滩晚宴</t>
+        </is>
+      </c>
+      <c r="B5" s="28" t="inlineStr">
+        <is>
+          <t>主背景板：晚宴冠名战略合作伙伴·绿城中国</t>
+        </is>
+      </c>
+      <c r="C5" s="28" t="inlineStr">
+        <is>
+          <t>展台立牌：绿城中国 GREENTOWN</t>
+        </is>
+      </c>
+      <c r="D5" s="28" t="inlineStr">
+        <is>
+          <t>晚宴大屏播放绿城中国品牌片</t>
+        </is>
+      </c>
+    </row>
+    <row r="6" ht="22" customHeight="1" s="17">
+      <c r="A6" s="29" t="inlineStr">
+        <is>
+          <t>二级｜主会场执行（重点）（4 张）　展台接待、双屏、主持、主视觉，证明主会场权益已落地。</t>
+        </is>
+      </c>
+      <c r="B6" s="30" t="n"/>
+      <c r="C6" s="30" t="n"/>
+      <c r="D6" s="30" t="n"/>
+    </row>
+    <row r="7" ht="138" customHeight="1" s="17">
+      <c r="A7" s="27" t="n"/>
+      <c r="B7" s="27" t="n"/>
+      <c r="C7" s="27" t="n"/>
+      <c r="D7" s="27" t="n"/>
     </row>
     <row r="8" ht="36" customHeight="1" s="17">
-      <c r="A8" s="49" t="inlineStr">
-        <is>
-          <t>五级</t>
-        </is>
-      </c>
-      <c r="B8" s="49" t="inlineStr">
-        <is>
-          <t>冠名晚宴氛围</t>
-        </is>
-      </c>
-      <c r="C8" s="49" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="D8" s="50" t="inlineStr">
-        <is>
-          <t>江景厅冠名晚宴现场。席卡为嘉宾姓名卡，不作「潮鳴」logo 桌卡证据。</t>
-        </is>
-      </c>
-    </row>
-    <row r="9" ht="24" customHeight="1" s="17">
-      <c r="A9" s="51" t="inlineStr">
-        <is>
-          <t>合计 18 张，全部按上表顺序嵌在下方各分类单元格中。参观邀约 / 证书 / 朋友圈无成片，不在本页拔高。</t>
-        </is>
-      </c>
-      <c r="B9" s="52" t="n"/>
-      <c r="C9" s="52" t="n"/>
-      <c r="D9" s="52" t="n"/>
-    </row>
-    <row r="11" ht="26" customHeight="1" s="17">
-      <c r="A11" s="53" t="inlineStr">
-        <is>
-          <t>一级｜核心品牌露出（必看）（4 张）</t>
-        </is>
-      </c>
-      <c r="B11" s="38" t="n"/>
-      <c r="C11" s="38" t="n"/>
-      <c r="D11" s="38" t="n"/>
-    </row>
-    <row r="12" ht="22" customHeight="1" s="17">
-      <c r="A12" s="54" t="inlineStr">
-        <is>
-          <t>绿城 / 潮鸣 / GREENTOWN 字样可直接核验，对应报价主体，建议甲方优先复核。</t>
-        </is>
-      </c>
-      <c r="B12" s="52" t="n"/>
-      <c r="C12" s="52" t="n"/>
-      <c r="D12" s="52" t="n"/>
-    </row>
-    <row r="13" ht="132" customHeight="1" s="17">
-      <c r="A13" s="25" t="n"/>
-      <c r="B13" s="25" t="n"/>
-      <c r="C13" s="25" t="n"/>
-      <c r="D13" s="25" t="n"/>
-    </row>
-    <row r="14" ht="36" customHeight="1" s="17">
-      <c r="A14" s="29" t="inlineStr">
-        <is>
-          <t>议程看板【绿城·潮鸣】星耀北外滩晚宴</t>
-        </is>
-      </c>
-      <c r="B14" s="29" t="inlineStr">
-        <is>
-          <t>主背景板：晚宴冠名战略合作伙伴·绿城中国</t>
-        </is>
-      </c>
-      <c r="C14" s="29" t="inlineStr">
-        <is>
-          <t>展台立牌：绿城中国 GREENTOWN</t>
-        </is>
-      </c>
-      <c r="D14" s="29" t="inlineStr">
-        <is>
-          <t>晚宴大屏播放绿城中国品牌片</t>
-        </is>
-      </c>
-    </row>
-    <row r="16" ht="26" customHeight="1" s="17">
-      <c r="A16" s="55" t="inlineStr">
-        <is>
-          <t>二级｜主会场执行（重点）（4 张）</t>
-        </is>
-      </c>
-      <c r="B16" s="40" t="n"/>
-      <c r="C16" s="40" t="n"/>
-      <c r="D16" s="40" t="n"/>
-    </row>
-    <row r="17" ht="22" customHeight="1" s="17">
-      <c r="A17" s="54" t="inlineStr">
-        <is>
-          <t>展台接待、双屏、主持、主视觉，证明主会场权益已落地。</t>
-        </is>
-      </c>
-      <c r="B17" s="52" t="n"/>
-      <c r="C17" s="52" t="n"/>
-      <c r="D17" s="52" t="n"/>
-    </row>
-    <row r="18" ht="132" customHeight="1" s="17">
-      <c r="A18" s="25" t="n"/>
-      <c r="B18" s="25" t="n"/>
-      <c r="C18" s="25" t="n"/>
-      <c r="D18" s="25" t="n"/>
-    </row>
-    <row r="19" ht="36" customHeight="1" s="17">
-      <c r="A19" s="29" t="inlineStr">
+      <c r="A8" s="28" t="inlineStr">
         <is>
           <t>展台接待：绿城立牌、礼袋与物料</t>
         </is>
       </c>
-      <c r="B19" s="29" t="inlineStr">
+      <c r="B8" s="28" t="inlineStr">
         <is>
           <t>主会场双屏同款主视觉（含晚宴冠名·绿城中国）</t>
         </is>
       </c>
-      <c r="C19" s="29" t="inlineStr">
+      <c r="C8" s="28" t="inlineStr">
         <is>
           <t>主持现场：主会场露出</t>
         </is>
       </c>
-      <c r="D19" s="29" t="inlineStr">
+      <c r="D8" s="28" t="inlineStr">
         <is>
           <t>主视觉 KV：战略合作名单含绿城中国</t>
         </is>
       </c>
     </row>
-    <row r="21" ht="26" customHeight="1" s="17">
-      <c r="A21" s="56" t="inlineStr">
-        <is>
-          <t>三级｜冠名位合影核验（4 张）</t>
-        </is>
-      </c>
-      <c r="B21" s="52" t="n"/>
-      <c r="C21" s="52" t="n"/>
-      <c r="D21" s="52" t="n"/>
-    </row>
-    <row r="22" ht="22" customHeight="1" s="17">
-      <c r="A22" s="54" t="inlineStr">
-        <is>
-          <t>主背景板合影，可复核晚宴冠名位「绿城中国」。</t>
-        </is>
-      </c>
-      <c r="B22" s="52" t="n"/>
-      <c r="C22" s="52" t="n"/>
-      <c r="D22" s="52" t="n"/>
-    </row>
-    <row r="23" ht="132" customHeight="1" s="17">
-      <c r="A23" s="25" t="n"/>
-      <c r="B23" s="25" t="n"/>
-      <c r="C23" s="25" t="n"/>
-      <c r="D23" s="25" t="n"/>
-    </row>
-    <row r="24" ht="36" customHeight="1" s="17">
-      <c r="A24" s="29" t="inlineStr">
+    <row r="9" ht="22" customHeight="1" s="17">
+      <c r="A9" s="31" t="inlineStr">
+        <is>
+          <t>三级｜冠名位合影核验（4 张）　主背景板合影，可复核晚宴冠名位「绿城中国」。</t>
+        </is>
+      </c>
+      <c r="B9" s="32" t="n"/>
+      <c r="C9" s="32" t="n"/>
+      <c r="D9" s="32" t="n"/>
+    </row>
+    <row r="10" ht="138" customHeight="1" s="17">
+      <c r="A10" s="27" t="n"/>
+      <c r="B10" s="27" t="n"/>
+      <c r="C10" s="27" t="n"/>
+      <c r="D10" s="27" t="n"/>
+    </row>
+    <row r="11" ht="36" customHeight="1" s="17">
+      <c r="A11" s="28" t="inlineStr">
         <is>
           <t>主背景板合影核验冠名位</t>
         </is>
       </c>
-      <c r="B24" s="29" t="inlineStr">
+      <c r="B11" s="28" t="inlineStr">
         <is>
           <t>主背景板合影（冠名位特写）</t>
         </is>
       </c>
-      <c r="C24" s="29" t="inlineStr">
+      <c r="C11" s="28" t="inlineStr">
         <is>
           <t>主背景板双人合影核验冠名位</t>
         </is>
       </c>
-      <c r="D24" s="29" t="inlineStr">
+      <c r="D11" s="28" t="inlineStr">
         <is>
           <t>主背景板合影：晚宴冠名战略合作伙伴·绿城中国</t>
         </is>
       </c>
     </row>
-    <row r="26" ht="26" customHeight="1" s="17">
-      <c r="A26" s="57" t="inlineStr">
-        <is>
-          <t>四级｜主办致辞现场（3 张）</t>
-        </is>
-      </c>
-      <c r="B26" s="58" t="n"/>
-      <c r="C26" s="58" t="n"/>
-      <c r="D26" s="58" t="n"/>
-    </row>
-    <row r="27" ht="22" customHeight="1" s="17">
-      <c r="A27" s="54" t="inlineStr">
-        <is>
-          <t>主会场致辞与讲台，补充现场执行；不作参观邀约专项成片。</t>
-        </is>
-      </c>
-      <c r="B27" s="52" t="n"/>
-      <c r="C27" s="52" t="n"/>
-      <c r="D27" s="52" t="n"/>
-    </row>
-    <row r="28" ht="132" customHeight="1" s="17">
-      <c r="A28" s="25" t="n"/>
-      <c r="B28" s="25" t="n"/>
-      <c r="C28" s="25" t="n"/>
-      <c r="D28" s="25" t="n"/>
-    </row>
-    <row r="29" ht="36" customHeight="1" s="17">
-      <c r="A29" s="29" t="inlineStr">
+    <row r="12" ht="20" customHeight="1" s="17">
+      <c r="A12" s="47" t="inlineStr">
+        <is>
+          <t>四级、五级补充现场（6 张）　主办致辞不作参观邀约成片；晚宴席卡为嘉宾姓名卡，不作潮鳴 logo 桌卡。</t>
+        </is>
+      </c>
+      <c r="B12" s="36" t="n"/>
+      <c r="C12" s="36" t="n"/>
+      <c r="D12" s="36" t="n"/>
+    </row>
+    <row r="13" ht="22" customHeight="1" s="17">
+      <c r="A13" s="37" t="inlineStr">
+        <is>
+          <t>四级｜主办致辞现场（3 张）　主会场致辞与讲台，补充现场执行；不作参观邀约专项成片。</t>
+        </is>
+      </c>
+      <c r="B13" s="36" t="n"/>
+      <c r="C13" s="36" t="n"/>
+      <c r="D13" s="36" t="n"/>
+    </row>
+    <row r="14" ht="128" customHeight="1" s="17">
+      <c r="A14" s="27" t="n"/>
+      <c r="B14" s="27" t="n"/>
+      <c r="C14" s="27" t="n"/>
+      <c r="D14" s="27" t="n"/>
+    </row>
+    <row r="15" ht="36" customHeight="1" s="17">
+      <c r="A15" s="28" t="inlineStr">
         <is>
           <t>主办致辞全景：主会场双屏与讲台</t>
         </is>
       </c>
-      <c r="B29" s="29" t="inlineStr">
+      <c r="B15" s="28" t="inlineStr">
         <is>
           <t>主办致辞：姚志勇，主会场主视觉</t>
         </is>
       </c>
-      <c r="C29" s="29" t="inlineStr">
+      <c r="C15" s="28" t="inlineStr">
         <is>
           <t>主办致辞讲台特写</t>
         </is>
       </c>
-      <c r="D29" s="25" t="n"/>
-    </row>
-    <row r="31" ht="26" customHeight="1" s="17">
-      <c r="A31" s="59" t="inlineStr">
-        <is>
-          <t>五级｜冠名晚宴氛围（3 张）</t>
-        </is>
-      </c>
-      <c r="B31" s="25" t="n"/>
-      <c r="C31" s="25" t="n"/>
-      <c r="D31" s="25" t="n"/>
-    </row>
-    <row r="32" ht="22" customHeight="1" s="17">
-      <c r="A32" s="54" t="inlineStr">
-        <is>
-          <t>江景厅冠名晚宴现场。席卡为嘉宾姓名卡，不作「潮鳴」logo 桌卡证据。</t>
-        </is>
-      </c>
-      <c r="B32" s="52" t="n"/>
-      <c r="C32" s="52" t="n"/>
-      <c r="D32" s="52" t="n"/>
-    </row>
-    <row r="33" ht="132" customHeight="1" s="17">
-      <c r="A33" s="25" t="n"/>
-      <c r="B33" s="25" t="n"/>
-      <c r="C33" s="25" t="n"/>
-      <c r="D33" s="25" t="n"/>
-    </row>
-    <row r="34" ht="36" customHeight="1" s="17">
-      <c r="A34" s="29" t="inlineStr">
+      <c r="D15" s="27" t="n"/>
+    </row>
+    <row r="16" ht="22" customHeight="1" s="17">
+      <c r="A16" s="38" t="inlineStr">
+        <is>
+          <t>五级｜冠名晚宴氛围（3 张）　江景厅冠名晚宴现场。席卡为嘉宾姓名卡，不作「潮鳴」logo 桌卡证据。</t>
+        </is>
+      </c>
+      <c r="B16" s="27" t="n"/>
+      <c r="C16" s="27" t="n"/>
+      <c r="D16" s="27" t="n"/>
+    </row>
+    <row r="17" ht="128" customHeight="1" s="17">
+      <c r="A17" s="27" t="n"/>
+      <c r="B17" s="27" t="n"/>
+      <c r="C17" s="27" t="n"/>
+      <c r="D17" s="27" t="n"/>
+    </row>
+    <row r="18" ht="36" customHeight="1" s="17">
+      <c r="A18" s="28" t="inlineStr">
         <is>
           <t>冠名晚宴合影（江景厅）</t>
         </is>
       </c>
-      <c r="B34" s="29" t="inlineStr">
+      <c r="B18" s="28" t="inlineStr">
         <is>
           <t>冠名晚宴桌次（江景厅圆桌）</t>
         </is>
       </c>
-      <c r="C34" s="29" t="inlineStr">
+      <c r="C18" s="28" t="inlineStr">
         <is>
           <t>冠名晚宴现场举杯</t>
         </is>
       </c>
-      <c r="D34" s="25" t="n"/>
+      <c r="D18" s="27" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="13">
+  <mergeCells count="8">
     <mergeCell ref="A1:D1"/>
-    <mergeCell ref="A17:D17"/>
     <mergeCell ref="A9:D9"/>
-    <mergeCell ref="A27:D27"/>
-    <mergeCell ref="A31:D31"/>
-    <mergeCell ref="A22:D22"/>
+    <mergeCell ref="A6:D6"/>
     <mergeCell ref="A12:D12"/>
-    <mergeCell ref="A26:D26"/>
-    <mergeCell ref="A21:D21"/>
+    <mergeCell ref="A3:D3"/>
     <mergeCell ref="A2:D2"/>
-    <mergeCell ref="A11:D11"/>
     <mergeCell ref="A16:D16"/>
-    <mergeCell ref="A32:D32"/>
+    <mergeCell ref="A13:D13"/>
   </mergeCells>
   <pageMargins left="0.5" right="0.5" top="0.55" bottom="0.55" header="0.2" footer="0.2"/>
   <pageSetup orientation="landscape" paperSize="9" fitToHeight="0" fitToWidth="1"/>
@@ -4353,248 +4425,248 @@
   </cols>
   <sheetData>
     <row r="1" ht="30" customHeight="1" s="17">
-      <c r="A1" s="37" t="inlineStr">
+      <c r="A1" s="45" t="inlineStr">
         <is>
           <t>绿城·潮鸣外滩 · 晚宴冠名四模块权益核验清单</t>
         </is>
       </c>
-      <c r="B1" s="38" t="n"/>
-      <c r="C1" s="38" t="n"/>
-      <c r="D1" s="38" t="n"/>
-      <c r="E1" s="38" t="n"/>
-      <c r="F1" s="38" t="n"/>
+      <c r="B1" s="25" t="n"/>
+      <c r="C1" s="25" t="n"/>
+      <c r="D1" s="25" t="n"/>
+      <c r="E1" s="25" t="n"/>
+      <c r="F1" s="25" t="n"/>
     </row>
     <row r="2" ht="36" customHeight="1" s="17">
-      <c r="A2" s="39" t="inlineStr">
+      <c r="A2" s="46" t="inlineStr">
         <is>
           <t>活动：2026-05-22 上海·北外滩·一滴水　身份：晚宴冠名战略合作伙伴　金额：含税 ¥100,000（报价单 4 模块整体打包，不拆子项验收）　依据：绿城中国-潮鸣外滩-10万元晚宴冠名服务报价单　本页按四模块嵌全部对应照片；若按重要程度查阅，见工作表「按重要顺序分类」。</t>
         </is>
       </c>
-      <c r="B2" s="40" t="n"/>
-      <c r="C2" s="40" t="n"/>
-      <c r="D2" s="40" t="n"/>
-      <c r="E2" s="40" t="n"/>
-      <c r="F2" s="40" t="n"/>
+      <c r="B2" s="30" t="n"/>
+      <c r="C2" s="30" t="n"/>
+      <c r="D2" s="30" t="n"/>
+      <c r="E2" s="30" t="n"/>
+      <c r="F2" s="30" t="n"/>
     </row>
     <row r="3" ht="22" customHeight="1" s="17">
-      <c r="A3" s="41" t="inlineStr">
+      <c r="A3" s="48" t="inlineStr">
         <is>
           <t>序号</t>
         </is>
       </c>
-      <c r="B3" s="41" t="inlineStr">
+      <c r="B3" s="48" t="inlineStr">
         <is>
           <t>服务模块</t>
         </is>
       </c>
-      <c r="C3" s="41" t="inlineStr">
+      <c r="C3" s="48" t="inlineStr">
         <is>
           <t>约定内容</t>
         </is>
       </c>
-      <c r="D3" s="41" t="inlineStr">
+      <c r="D3" s="48" t="inlineStr">
         <is>
           <t>金额（元）</t>
         </is>
       </c>
-      <c r="E3" s="41" t="inlineStr">
+      <c r="E3" s="48" t="inlineStr">
         <is>
           <t>现场照片核验</t>
         </is>
       </c>
-      <c r="F3" s="41" t="inlineStr">
+      <c r="F3" s="48" t="inlineStr">
         <is>
           <t>结论</t>
         </is>
       </c>
     </row>
     <row r="4" ht="76" customHeight="1" s="17">
-      <c r="A4" s="60" t="inlineStr">
+      <c r="A4" s="49" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B4" s="61" t="inlineStr">
+      <c r="B4" s="50" t="inlineStr">
         <is>
           <t>晚宴冠名和专属权益</t>
         </is>
       </c>
-      <c r="C4" s="62" t="inlineStr">
+      <c r="C4" s="51" t="inlineStr">
         <is>
           <t>晚宴主题冠名、专场PPT/视频、主持人口播、席卡等物料植入</t>
         </is>
       </c>
-      <c r="D4" s="61" t="inlineStr">
+      <c r="D4" s="50" t="inlineStr">
         <is>
           <t>55,000</t>
         </is>
       </c>
-      <c r="E4" s="62" t="inlineStr">
+      <c r="E4" s="51" t="inlineStr">
         <is>
           <t>图①议程看板晚宴冠名【绿城·潮鸣】；图②⑤主背景板「晚宴冠名战略合作伙伴·绿城中国」；图⑧晚宴大屏播放绿城中国品牌片（理想生活综合服务商 / LIGHT HEAT POWER）。现场席卡为嘉宾姓名卡，相册未见单独「潮鳴」logo 桌卡特写。</t>
         </is>
       </c>
-      <c r="F4" s="63" t="inlineStr">
+      <c r="F4" s="52" t="inlineStr">
         <is>
           <t>通过（冠名/品牌片）</t>
         </is>
       </c>
     </row>
     <row r="5" ht="76" customHeight="1" s="17">
-      <c r="A5" s="60" t="inlineStr">
+      <c r="A5" s="49" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B5" s="61" t="inlineStr">
+      <c r="B5" s="50" t="inlineStr">
         <is>
           <t>主会场权益</t>
         </is>
       </c>
-      <c r="C5" s="62" t="inlineStr">
+      <c r="C5" s="51" t="inlineStr">
         <is>
           <t>1号位展台、手拎袋项目物料、视频轮播/奖项颁发画面</t>
         </is>
       </c>
-      <c r="D5" s="61" t="inlineStr">
+      <c r="D5" s="50" t="inlineStr">
         <is>
           <t>30,000</t>
         </is>
       </c>
-      <c r="E5" s="62" t="inlineStr">
+      <c r="E5" s="51" t="inlineStr">
         <is>
           <t>图③展台立牌「绿城中国 GREENTOWN」；图④展台接待（礼袋与物料）；图⑥主会场双屏同款主视觉；图⑨主视觉KV含绿城中国。奖项颁发证书未见特写。</t>
         </is>
       </c>
-      <c r="F5" s="63" t="inlineStr">
+      <c r="F5" s="52" t="inlineStr">
         <is>
           <t>通过（展台/双屏）</t>
         </is>
       </c>
     </row>
     <row r="6" ht="76" customHeight="1" s="17">
-      <c r="A6" s="60" t="inlineStr">
+      <c r="A6" s="49" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B6" s="61" t="inlineStr">
+      <c r="B6" s="50" t="inlineStr">
         <is>
           <t>专场项目参观邀约</t>
         </is>
       </c>
-      <c r="C6" s="62" t="inlineStr">
+      <c r="C6" s="51" t="inlineStr">
         <is>
           <t>论坛/颁奖结束后主持人口播 + 动线引导，邀约前往案场</t>
         </is>
       </c>
-      <c r="D6" s="61" t="inlineStr">
+      <c r="D6" s="50" t="inlineStr">
         <is>
           <t>5,000</t>
         </is>
       </c>
-      <c r="E6" s="62" t="inlineStr">
+      <c r="E6" s="51" t="inlineStr">
         <is>
           <t>图⑦证明主会场主持人口播位已具备。相册未见「参观邀约 / 案场接驳」专项成片，请以全程录像及现场执行回执为准。</t>
         </is>
       </c>
-      <c r="F6" s="64" t="inlineStr">
+      <c r="F6" s="53" t="inlineStr">
         <is>
           <t>待录像核验</t>
         </is>
       </c>
     </row>
     <row r="7" ht="76" customHeight="1" s="17">
-      <c r="A7" s="60" t="inlineStr">
+      <c r="A7" s="49" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B7" s="61" t="inlineStr">
+      <c r="B7" s="50" t="inlineStr">
         <is>
           <t>宣发配合</t>
         </is>
       </c>
-      <c r="C7" s="62" t="inlineStr">
+      <c r="C7" s="51" t="inlineStr">
         <is>
           <t>现场摄影、朋友圈九宫格、回顾视频项目鸣谢、执行回执</t>
         </is>
       </c>
-      <c r="D7" s="61" t="inlineStr">
+      <c r="D7" s="50" t="inlineStr">
         <is>
           <t>10,000</t>
         </is>
       </c>
-      <c r="E7" s="62" t="inlineStr">
+      <c r="E7" s="51" t="inlineStr">
         <is>
           <t>现场摄影：本表精华照片 + 拍立享约 425 张 + 网盘录像。本工作簿「赞助权益执行回执」即执行报告。朋友圈九宫格、回顾视频片头鸣谢未附，不以照片推定已发。</t>
         </is>
       </c>
-      <c r="F7" s="64" t="inlineStr">
+      <c r="F7" s="53" t="inlineStr">
         <is>
           <t>摄影通过；其余待补</t>
         </is>
       </c>
     </row>
     <row r="8" ht="76" customHeight="1" s="17">
-      <c r="A8" s="60" t="inlineStr">
+      <c r="A8" s="49" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="B8" s="61" t="inlineStr">
+      <c r="B8" s="50" t="inlineStr">
         <is>
           <t>合计（含税）</t>
         </is>
       </c>
-      <c r="C8" s="62" t="inlineStr">
+      <c r="C8" s="51" t="inlineStr">
         <is>
           <t>4 模块整体打包，一次性验收</t>
         </is>
       </c>
-      <c r="D8" s="61" t="inlineStr">
+      <c r="D8" s="50" t="inlineStr">
         <is>
           <t>100,000</t>
         </is>
       </c>
-      <c r="E8" s="62" t="inlineStr">
+      <c r="E8" s="51" t="inlineStr">
         <is>
           <t>已核验项以绿城 / 潮鸣字样可辨露出为准；黄底项需录像或另行回执，不在本表拔高为已完成。</t>
         </is>
       </c>
-      <c r="F8" s="64" t="inlineStr">
+      <c r="F8" s="53" t="inlineStr">
         <is>
           <t>主体已交，部分待补</t>
         </is>
       </c>
     </row>
     <row r="9" ht="76" customHeight="1" s="17">
-      <c r="A9" s="60" t="inlineStr">
+      <c r="A9" s="49" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="B9" s="61" t="inlineStr">
+      <c r="B9" s="50" t="inlineStr">
         <is>
           <t>证书</t>
         </is>
       </c>
-      <c r="C9" s="62" t="inlineStr">
+      <c r="C9" s="51" t="inlineStr">
         <is>
           <t>2026年度智慧人居新质资产领军企业 暨卓越战略合作伙伴</t>
         </is>
       </c>
-      <c r="D9" s="61" t="inlineStr">
+      <c r="D9" s="50" t="inlineStr">
         <is>
           <t>—</t>
         </is>
       </c>
-      <c r="E9" s="62" t="inlineStr">
+      <c r="E9" s="51" t="inlineStr">
         <is>
           <t>事项描述已载明颁发。本相册未见证书 / 颁奖特写，不作为已交付证据。</t>
         </is>
       </c>
-      <c r="F9" s="64" t="inlineStr">
+      <c r="F9" s="53" t="inlineStr">
         <is>
           <t>待补照片</t>
         </is>
@@ -4606,259 +4678,259 @@
           <t>验收口径：报价单约定「不逐项贴照片、四模块整体打包」。本清单把精华照片映射到模块，便于甲方复核，不等于把未成片的子项改成已交付。营销评估预勾「良好」，请绿城营销负责人复核签字。本清单仅对应 2026-05-22 峰会，不与 3 月开盘花束验收混用。</t>
         </is>
       </c>
-      <c r="B10" s="52" t="n"/>
-      <c r="C10" s="52" t="n"/>
-      <c r="D10" s="52" t="n"/>
-      <c r="E10" s="52" t="n"/>
-      <c r="F10" s="52" t="n"/>
+      <c r="B10" s="32" t="n"/>
+      <c r="C10" s="32" t="n"/>
+      <c r="D10" s="32" t="n"/>
+      <c r="E10" s="32" t="n"/>
+      <c r="F10" s="32" t="n"/>
     </row>
     <row r="12" ht="24" customHeight="1" s="17">
-      <c r="A12" s="65" t="inlineStr">
+      <c r="A12" s="26" t="inlineStr">
         <is>
           <t>四模块现场证据照片（各模块全部对应图已嵌入，可直接给甲方核对）</t>
         </is>
       </c>
-      <c r="B12" s="38" t="n"/>
-      <c r="C12" s="38" t="n"/>
-      <c r="D12" s="38" t="n"/>
-      <c r="E12" s="38" t="n"/>
-      <c r="F12" s="38" t="n"/>
+      <c r="B12" s="25" t="n"/>
+      <c r="C12" s="25" t="n"/>
+      <c r="D12" s="25" t="n"/>
+      <c r="E12" s="25" t="n"/>
+      <c r="F12" s="25" t="n"/>
     </row>
     <row r="13" ht="22" customHeight="1" s="17">
-      <c r="A13" s="66" t="inlineStr">
+      <c r="A13" s="55" t="inlineStr">
         <is>
           <t>1. 晚宴冠名和专属权益　¥55,000　☑ 已执行（冠名 / 品牌片）　本模块 6 张（全部嵌入）</t>
         </is>
       </c>
-      <c r="B13" s="40" t="n"/>
-      <c r="C13" s="40" t="n"/>
-      <c r="D13" s="40" t="n"/>
-      <c r="E13" s="40" t="n"/>
-      <c r="F13" s="40" t="n"/>
+      <c r="B13" s="30" t="n"/>
+      <c r="C13" s="30" t="n"/>
+      <c r="D13" s="30" t="n"/>
+      <c r="E13" s="30" t="n"/>
+      <c r="F13" s="30" t="n"/>
     </row>
     <row r="14" ht="118" customHeight="1" s="17">
-      <c r="A14" s="25" t="n"/>
-      <c r="B14" s="25" t="n"/>
-      <c r="C14" s="25" t="n"/>
-      <c r="D14" s="25" t="n"/>
-      <c r="E14" s="25" t="n"/>
-      <c r="F14" s="25" t="n"/>
+      <c r="A14" s="27" t="n"/>
+      <c r="B14" s="27" t="n"/>
+      <c r="C14" s="27" t="n"/>
+      <c r="D14" s="27" t="n"/>
+      <c r="E14" s="27" t="n"/>
+      <c r="F14" s="27" t="n"/>
     </row>
     <row r="15" ht="36" customHeight="1" s="17">
-      <c r="A15" s="29" t="inlineStr">
+      <c r="A15" s="28" t="inlineStr">
         <is>
           <t>议程看板【绿城·潮鸣】晚宴</t>
         </is>
       </c>
-      <c r="B15" s="29" t="inlineStr">
+      <c r="B15" s="28" t="inlineStr">
         <is>
           <t>主背景板：晚宴冠名·绿城中国</t>
         </is>
       </c>
-      <c r="C15" s="29" t="inlineStr">
+      <c r="C15" s="28" t="inlineStr">
         <is>
           <t>晚宴大屏绿城中国品牌片</t>
         </is>
       </c>
-      <c r="D15" s="29" t="inlineStr">
+      <c r="D15" s="28" t="inlineStr">
         <is>
           <t>冠名晚宴合影（江景厅）</t>
         </is>
       </c>
-      <c r="E15" s="25" t="n"/>
-      <c r="F15" s="25" t="n"/>
+      <c r="E15" s="27" t="n"/>
+      <c r="F15" s="27" t="n"/>
     </row>
     <row r="16" ht="118" customHeight="1" s="17">
-      <c r="A16" s="25" t="n"/>
-      <c r="B16" s="25" t="n"/>
-      <c r="C16" s="25" t="n"/>
-      <c r="D16" s="25" t="n"/>
-      <c r="E16" s="25" t="n"/>
-      <c r="F16" s="25" t="n"/>
+      <c r="A16" s="27" t="n"/>
+      <c r="B16" s="27" t="n"/>
+      <c r="C16" s="27" t="n"/>
+      <c r="D16" s="27" t="n"/>
+      <c r="E16" s="27" t="n"/>
+      <c r="F16" s="27" t="n"/>
     </row>
     <row r="17" ht="36" customHeight="1" s="17">
-      <c r="A17" s="29" t="inlineStr">
+      <c r="A17" s="28" t="inlineStr">
         <is>
           <t>冠名晚宴现场举杯</t>
         </is>
       </c>
-      <c r="B17" s="29" t="inlineStr">
+      <c r="B17" s="28" t="inlineStr">
         <is>
           <t>冠名晚宴桌次（江景厅）</t>
         </is>
       </c>
-      <c r="C17" s="25" t="n"/>
-      <c r="D17" s="25" t="n"/>
-      <c r="E17" s="25" t="n"/>
-      <c r="F17" s="25" t="n"/>
+      <c r="C17" s="27" t="n"/>
+      <c r="D17" s="27" t="n"/>
+      <c r="E17" s="27" t="n"/>
+      <c r="F17" s="27" t="n"/>
     </row>
     <row r="18" ht="22" customHeight="1" s="17">
-      <c r="A18" s="66" t="inlineStr">
+      <c r="A18" s="55" t="inlineStr">
         <is>
           <t>2. 主会场权益　¥30,000　☑ 已执行（展台 / 双屏）　本模块 8 张（全部嵌入）</t>
         </is>
       </c>
-      <c r="B18" s="40" t="n"/>
-      <c r="C18" s="40" t="n"/>
-      <c r="D18" s="40" t="n"/>
-      <c r="E18" s="40" t="n"/>
-      <c r="F18" s="40" t="n"/>
+      <c r="B18" s="30" t="n"/>
+      <c r="C18" s="30" t="n"/>
+      <c r="D18" s="30" t="n"/>
+      <c r="E18" s="30" t="n"/>
+      <c r="F18" s="30" t="n"/>
     </row>
     <row r="19" ht="118" customHeight="1" s="17">
-      <c r="A19" s="25" t="n"/>
-      <c r="B19" s="25" t="n"/>
-      <c r="C19" s="25" t="n"/>
-      <c r="D19" s="25" t="n"/>
-      <c r="E19" s="25" t="n"/>
-      <c r="F19" s="25" t="n"/>
+      <c r="A19" s="27" t="n"/>
+      <c r="B19" s="27" t="n"/>
+      <c r="C19" s="27" t="n"/>
+      <c r="D19" s="27" t="n"/>
+      <c r="E19" s="27" t="n"/>
+      <c r="F19" s="27" t="n"/>
     </row>
     <row r="20" ht="36" customHeight="1" s="17">
-      <c r="A20" s="29" t="inlineStr">
+      <c r="A20" s="28" t="inlineStr">
         <is>
           <t>展台立牌：绿城中国 GREENTOWN</t>
         </is>
       </c>
-      <c r="B20" s="29" t="inlineStr">
+      <c r="B20" s="28" t="inlineStr">
         <is>
           <t>展台接待：礼袋与物料</t>
         </is>
       </c>
-      <c r="C20" s="29" t="inlineStr">
+      <c r="C20" s="28" t="inlineStr">
         <is>
           <t>主会场双屏同款主视觉</t>
         </is>
       </c>
-      <c r="D20" s="29" t="inlineStr">
+      <c r="D20" s="28" t="inlineStr">
         <is>
           <t>主视觉 KV 含绿城中国</t>
         </is>
       </c>
-      <c r="E20" s="25" t="n"/>
-      <c r="F20" s="25" t="n"/>
+      <c r="E20" s="27" t="n"/>
+      <c r="F20" s="27" t="n"/>
     </row>
     <row r="21" ht="118" customHeight="1" s="17">
-      <c r="A21" s="25" t="n"/>
-      <c r="B21" s="25" t="n"/>
-      <c r="C21" s="25" t="n"/>
-      <c r="D21" s="25" t="n"/>
-      <c r="E21" s="25" t="n"/>
-      <c r="F21" s="25" t="n"/>
+      <c r="A21" s="27" t="n"/>
+      <c r="B21" s="27" t="n"/>
+      <c r="C21" s="27" t="n"/>
+      <c r="D21" s="27" t="n"/>
+      <c r="E21" s="27" t="n"/>
+      <c r="F21" s="27" t="n"/>
     </row>
     <row r="22" ht="36" customHeight="1" s="17">
-      <c r="A22" s="29" t="inlineStr">
+      <c r="A22" s="28" t="inlineStr">
         <is>
           <t>主持现场</t>
         </is>
       </c>
-      <c r="B22" s="29" t="inlineStr">
+      <c r="B22" s="28" t="inlineStr">
         <is>
           <t>主办致辞全景</t>
         </is>
       </c>
-      <c r="C22" s="29" t="inlineStr">
+      <c r="C22" s="28" t="inlineStr">
         <is>
           <t>主办致辞：姚志勇</t>
         </is>
       </c>
-      <c r="D22" s="29" t="inlineStr">
+      <c r="D22" s="28" t="inlineStr">
         <is>
           <t>主办致辞讲台特写</t>
         </is>
       </c>
-      <c r="E22" s="25" t="n"/>
-      <c r="F22" s="25" t="n"/>
+      <c r="E22" s="27" t="n"/>
+      <c r="F22" s="27" t="n"/>
     </row>
     <row r="23" ht="22" customHeight="1" s="17">
-      <c r="A23" s="66" t="inlineStr">
+      <c r="A23" s="55" t="inlineStr">
         <is>
           <t>3. 专场项目参观邀约　¥5,000　☐ 待录像核验（无专项成片）　本模块 2 张（全部嵌入）</t>
         </is>
       </c>
-      <c r="B23" s="40" t="n"/>
-      <c r="C23" s="40" t="n"/>
-      <c r="D23" s="40" t="n"/>
-      <c r="E23" s="40" t="n"/>
-      <c r="F23" s="40" t="n"/>
+      <c r="B23" s="30" t="n"/>
+      <c r="C23" s="30" t="n"/>
+      <c r="D23" s="30" t="n"/>
+      <c r="E23" s="30" t="n"/>
+      <c r="F23" s="30" t="n"/>
     </row>
     <row r="24" ht="118" customHeight="1" s="17">
-      <c r="A24" s="25" t="n"/>
-      <c r="B24" s="25" t="n"/>
-      <c r="C24" s="25" t="n"/>
-      <c r="D24" s="25" t="n"/>
-      <c r="E24" s="25" t="n"/>
-      <c r="F24" s="25" t="n"/>
+      <c r="A24" s="27" t="n"/>
+      <c r="B24" s="27" t="n"/>
+      <c r="C24" s="27" t="n"/>
+      <c r="D24" s="27" t="n"/>
+      <c r="E24" s="27" t="n"/>
+      <c r="F24" s="27" t="n"/>
     </row>
     <row r="25" ht="36" customHeight="1" s="17">
-      <c r="A25" s="29" t="inlineStr">
+      <c r="A25" s="28" t="inlineStr">
         <is>
           <t>主持口播位已具备</t>
         </is>
       </c>
-      <c r="B25" s="29" t="inlineStr">
+      <c r="B25" s="28" t="inlineStr">
         <is>
           <t>主背景板冠名位（非参观成片）</t>
         </is>
       </c>
-      <c r="C25" s="25" t="n"/>
-      <c r="D25" s="25" t="n"/>
-      <c r="E25" s="25" t="n"/>
-      <c r="F25" s="25" t="n"/>
+      <c r="C25" s="27" t="n"/>
+      <c r="D25" s="27" t="n"/>
+      <c r="E25" s="27" t="n"/>
+      <c r="F25" s="27" t="n"/>
     </row>
     <row r="26" ht="28" customHeight="1" s="17">
-      <c r="A26" s="67" t="inlineStr">
+      <c r="A26" s="56" t="inlineStr">
         <is>
           <t>相册未见参观 / 接驳专项成片。上图仅证明主持口播位与冠名位，不作为参观邀约已完成证据。</t>
         </is>
       </c>
-      <c r="B26" s="68" t="n"/>
-      <c r="C26" s="68" t="n"/>
-      <c r="D26" s="68" t="n"/>
-      <c r="E26" s="68" t="n"/>
-      <c r="F26" s="68" t="n"/>
+      <c r="B26" s="57" t="n"/>
+      <c r="C26" s="57" t="n"/>
+      <c r="D26" s="57" t="n"/>
+      <c r="E26" s="57" t="n"/>
+      <c r="F26" s="57" t="n"/>
     </row>
     <row r="27" ht="22" customHeight="1" s="17">
-      <c r="A27" s="66" t="inlineStr">
+      <c r="A27" s="55" t="inlineStr">
         <is>
           <t>4. 宣发配合　¥10,000　☑ 现场摄影已交　☐ 朋友圈 / 回顾视频待补　本模块 4 张（全部嵌入）</t>
         </is>
       </c>
-      <c r="B27" s="40" t="n"/>
-      <c r="C27" s="40" t="n"/>
-      <c r="D27" s="40" t="n"/>
-      <c r="E27" s="40" t="n"/>
-      <c r="F27" s="40" t="n"/>
+      <c r="B27" s="30" t="n"/>
+      <c r="C27" s="30" t="n"/>
+      <c r="D27" s="30" t="n"/>
+      <c r="E27" s="30" t="n"/>
+      <c r="F27" s="30" t="n"/>
     </row>
     <row r="28" ht="118" customHeight="1" s="17">
-      <c r="A28" s="25" t="n"/>
-      <c r="B28" s="25" t="n"/>
-      <c r="C28" s="25" t="n"/>
-      <c r="D28" s="25" t="n"/>
-      <c r="E28" s="25" t="n"/>
-      <c r="F28" s="25" t="n"/>
+      <c r="A28" s="27" t="n"/>
+      <c r="B28" s="27" t="n"/>
+      <c r="C28" s="27" t="n"/>
+      <c r="D28" s="27" t="n"/>
+      <c r="E28" s="27" t="n"/>
+      <c r="F28" s="27" t="n"/>
     </row>
     <row r="29" ht="36" customHeight="1" s="17">
-      <c r="A29" s="29" t="inlineStr">
+      <c r="A29" s="28" t="inlineStr">
         <is>
           <t>主背景板合影（执行回执用）</t>
         </is>
       </c>
-      <c r="B29" s="29" t="inlineStr">
+      <c r="B29" s="28" t="inlineStr">
         <is>
           <t>主背景板双人合影核验冠名</t>
         </is>
       </c>
-      <c r="C29" s="29" t="inlineStr">
+      <c r="C29" s="28" t="inlineStr">
         <is>
           <t>主背景板合影核验冠名</t>
         </is>
       </c>
-      <c r="D29" s="29" t="inlineStr">
+      <c r="D29" s="28" t="inlineStr">
         <is>
           <t>冠名晚宴桌次</t>
         </is>
       </c>
-      <c r="E29" s="25" t="n"/>
-      <c r="F29" s="25" t="n"/>
+      <c r="E29" s="27" t="n"/>
+      <c r="F29" s="27" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="9">
@@ -4895,225 +4967,225 @@
   </cols>
   <sheetData>
     <row r="1" ht="32" customHeight="1" s="17">
-      <c r="A1" s="37" t="inlineStr">
+      <c r="A1" s="45" t="inlineStr">
         <is>
           <t>绿城中国策划活动类效果评估表</t>
         </is>
       </c>
-      <c r="B1" s="38" t="n"/>
-      <c r="C1" s="38" t="n"/>
-      <c r="D1" s="38" t="n"/>
+      <c r="B1" s="25" t="n"/>
+      <c r="C1" s="25" t="n"/>
+      <c r="D1" s="25" t="n"/>
     </row>
     <row r="2" ht="22" customHeight="1" s="17">
-      <c r="A2" s="69" t="inlineStr">
+      <c r="A2" s="58" t="inlineStr">
         <is>
           <t>（冠名、活动赞助、活动执行等）　项目：绿城·潮鸣外滩　活动：2026-05-22 晚宴冠名</t>
         </is>
       </c>
-      <c r="B2" s="40" t="n"/>
-      <c r="C2" s="40" t="n"/>
-      <c r="D2" s="40" t="n"/>
+      <c r="B2" s="30" t="n"/>
+      <c r="C2" s="30" t="n"/>
+      <c r="D2" s="30" t="n"/>
     </row>
     <row r="3" ht="28" customHeight="1" s="17">
-      <c r="A3" s="70" t="inlineStr">
+      <c r="A3" s="59" t="inlineStr">
         <is>
           <t>活动主题</t>
         </is>
       </c>
-      <c r="B3" s="71" t="inlineStr">
+      <c r="B3" s="60" t="inlineStr">
         <is>
           <t>【绿城·潮鸣】星耀北外滩——AI领袖定制晚宴</t>
         </is>
       </c>
-      <c r="C3" s="25" t="n"/>
-      <c r="D3" s="25" t="n"/>
+      <c r="C3" s="27" t="n"/>
+      <c r="D3" s="27" t="n"/>
     </row>
     <row r="4" ht="28" customHeight="1" s="17">
-      <c r="A4" s="70" t="inlineStr">
+      <c r="A4" s="59" t="inlineStr">
         <is>
           <t>活动举办时间</t>
         </is>
       </c>
-      <c r="B4" s="72" t="inlineStr">
+      <c r="B4" s="61" t="inlineStr">
         <is>
           <t>2026年5月22日 13:00–20:30　　上海·北外滩·一滴水</t>
         </is>
       </c>
-      <c r="C4" s="25" t="n"/>
-      <c r="D4" s="25" t="n"/>
+      <c r="C4" s="27" t="n"/>
+      <c r="D4" s="27" t="n"/>
     </row>
     <row r="5" ht="28" customHeight="1" s="17">
-      <c r="A5" s="70" t="inlineStr">
+      <c r="A5" s="59" t="inlineStr">
         <is>
           <t>活动
 现场氛围</t>
         </is>
       </c>
-      <c r="B5" s="29" t="inlineStr">
+      <c r="B5" s="28" t="inlineStr">
         <is>
           <t>①议程看板【绿城·潮鸣】晚宴冠名</t>
         </is>
       </c>
-      <c r="C5" s="31" t="n"/>
-      <c r="D5" s="29" t="inlineStr">
+      <c r="C5" s="62" t="n"/>
+      <c r="D5" s="28" t="inlineStr">
         <is>
           <t>②主背景板：晚宴冠名·绿城中国</t>
         </is>
       </c>
     </row>
     <row r="6" ht="78" customHeight="1" s="17">
-      <c r="A6" s="25" t="n"/>
-      <c r="B6" s="25" t="n"/>
-      <c r="C6" s="73" t="n"/>
-      <c r="D6" s="25" t="n"/>
+      <c r="A6" s="27" t="n"/>
+      <c r="B6" s="27" t="n"/>
+      <c r="C6" s="63" t="n"/>
+      <c r="D6" s="27" t="n"/>
     </row>
     <row r="7" ht="78" customHeight="1" s="17">
-      <c r="A7" s="25" t="n"/>
-      <c r="B7" s="74" t="n"/>
-      <c r="C7" s="75" t="n"/>
-      <c r="D7" s="76" t="n"/>
+      <c r="A7" s="27" t="n"/>
+      <c r="B7" s="64" t="n"/>
+      <c r="C7" s="65" t="n"/>
+      <c r="D7" s="66" t="n"/>
     </row>
     <row r="8" ht="78" customHeight="1" s="17">
-      <c r="A8" s="25" t="n"/>
-      <c r="B8" s="77" t="n"/>
-      <c r="C8" s="78" t="n"/>
-      <c r="D8" s="79" t="n"/>
+      <c r="A8" s="27" t="n"/>
+      <c r="B8" s="67" t="n"/>
+      <c r="C8" s="68" t="n"/>
+      <c r="D8" s="69" t="n"/>
     </row>
     <row r="9" ht="28" customHeight="1" s="17">
-      <c r="A9" s="25" t="n"/>
-      <c r="B9" s="29" t="inlineStr">
+      <c r="A9" s="27" t="n"/>
+      <c r="B9" s="28" t="inlineStr">
         <is>
           <t>③展台立牌：绿城中国 GREENTOWN</t>
         </is>
       </c>
-      <c r="C9" s="31" t="n"/>
-      <c r="D9" s="29" t="inlineStr">
+      <c r="C9" s="62" t="n"/>
+      <c r="D9" s="28" t="inlineStr">
         <is>
           <t>⑧晚宴大屏：绿城中国品牌片</t>
         </is>
       </c>
     </row>
     <row r="10" ht="78" customHeight="1" s="17">
-      <c r="A10" s="25" t="n"/>
-      <c r="B10" s="25" t="n"/>
-      <c r="C10" s="73" t="n"/>
-      <c r="D10" s="25" t="n"/>
+      <c r="A10" s="27" t="n"/>
+      <c r="B10" s="27" t="n"/>
+      <c r="C10" s="63" t="n"/>
+      <c r="D10" s="27" t="n"/>
     </row>
     <row r="11" ht="78" customHeight="1" s="17">
-      <c r="A11" s="25" t="n"/>
-      <c r="B11" s="74" t="n"/>
-      <c r="C11" s="75" t="n"/>
-      <c r="D11" s="76" t="n"/>
+      <c r="A11" s="27" t="n"/>
+      <c r="B11" s="64" t="n"/>
+      <c r="C11" s="65" t="n"/>
+      <c r="D11" s="66" t="n"/>
     </row>
     <row r="12" ht="78" customHeight="1" s="17">
-      <c r="A12" s="25" t="n"/>
-      <c r="B12" s="77" t="n"/>
-      <c r="C12" s="78" t="n"/>
-      <c r="D12" s="79" t="n"/>
+      <c r="A12" s="27" t="n"/>
+      <c r="B12" s="67" t="n"/>
+      <c r="C12" s="68" t="n"/>
+      <c r="D12" s="69" t="n"/>
     </row>
     <row r="13" ht="24" customHeight="1" s="17">
-      <c r="A13" s="70" t="inlineStr">
+      <c r="A13" s="59" t="inlineStr">
         <is>
           <t>策划负责人填写</t>
         </is>
       </c>
-      <c r="B13" s="66" t="inlineStr">
+      <c r="B13" s="55" t="inlineStr">
         <is>
           <t>总体活动评价：</t>
         </is>
       </c>
-      <c r="C13" s="30" t="n"/>
-      <c r="D13" s="31" t="n"/>
+      <c r="C13" s="70" t="n"/>
+      <c r="D13" s="62" t="n"/>
     </row>
     <row r="14" ht="36" customHeight="1" s="17">
-      <c r="A14" s="25" t="n"/>
-      <c r="B14" s="80" t="inlineStr">
+      <c r="A14" s="27" t="n"/>
+      <c r="B14" s="71" t="inlineStr">
         <is>
           <t>本次活动为「2026人工智能商业化落地与硬核投资破局峰会」晚宴冠名。绿城中国 | 绿城·潮鸣外滩作为晚宴冠名战略合作伙伴，主背景板、议程看板、展台立牌、主会场双屏及晚宴大屏品牌片均完成品牌露出。按照约定完成整体策划与执行，现场氛围良好，活动取得圆满成功。</t>
         </is>
       </c>
-      <c r="C14" s="81" t="n"/>
-      <c r="D14" s="73" t="n"/>
+      <c r="C14" s="72" t="n"/>
+      <c r="D14" s="63" t="n"/>
     </row>
     <row r="15" ht="36" customHeight="1" s="17">
-      <c r="A15" s="25" t="n"/>
-      <c r="B15" s="77" t="n"/>
-      <c r="C15" s="82" t="n"/>
-      <c r="D15" s="78" t="n"/>
+      <c r="A15" s="27" t="n"/>
+      <c r="B15" s="67" t="n"/>
+      <c r="C15" s="73" t="n"/>
+      <c r="D15" s="68" t="n"/>
     </row>
     <row r="16" ht="32" customHeight="1" s="17">
-      <c r="A16" s="25" t="n"/>
-      <c r="B16" s="83" t="inlineStr">
+      <c r="A16" s="27" t="n"/>
+      <c r="B16" s="74" t="inlineStr">
         <is>
           <t>策划负责人签名：胡继刚 ____________________　　日期：2026-05-22　　（请补签）</t>
         </is>
       </c>
-      <c r="C16" s="30" t="n"/>
-      <c r="D16" s="31" t="n"/>
+      <c r="C16" s="70" t="n"/>
+      <c r="D16" s="62" t="n"/>
     </row>
     <row r="17" ht="24" customHeight="1" s="17">
-      <c r="A17" s="70" t="inlineStr">
+      <c r="A17" s="59" t="inlineStr">
         <is>
           <t>营销负责人填写</t>
         </is>
       </c>
-      <c r="B17" s="66" t="inlineStr">
+      <c r="B17" s="55" t="inlineStr">
         <is>
           <t>对活动【总体效果】评估（文字说明）：</t>
         </is>
       </c>
-      <c r="C17" s="30" t="n"/>
-      <c r="D17" s="31" t="n"/>
+      <c r="C17" s="70" t="n"/>
+      <c r="D17" s="62" t="n"/>
     </row>
     <row r="18" ht="42" customHeight="1" s="17">
-      <c r="A18" s="25" t="n"/>
-      <c r="B18" s="84" t="inlineStr">
+      <c r="A18" s="27" t="n"/>
+      <c r="B18" s="75" t="inlineStr">
         <is>
           <t>绿城中国 / 潮鸣字样可辨露出已核验，效果良好，符合约定要求。参观邀约口播、朋友圈九宫格、回顾视频、证书特写见执行回执待补项，不在此拔高。</t>
         </is>
       </c>
-      <c r="C18" s="30" t="n"/>
-      <c r="D18" s="31" t="n"/>
+      <c r="C18" s="70" t="n"/>
+      <c r="D18" s="62" t="n"/>
     </row>
     <row r="19" ht="28" customHeight="1" s="17">
-      <c r="A19" s="25" t="n"/>
-      <c r="B19" s="85" t="inlineStr">
+      <c r="A19" s="27" t="n"/>
+      <c r="B19" s="76" t="inlineStr">
         <is>
           <t>非常好（☐）　　良好（☑）　　一般（☐）　　较差（☐）</t>
         </is>
       </c>
-      <c r="C19" s="30" t="n"/>
-      <c r="D19" s="31" t="n"/>
+      <c r="C19" s="70" t="n"/>
+      <c r="D19" s="62" t="n"/>
     </row>
     <row r="20" ht="42" customHeight="1" s="17">
-      <c r="A20" s="25" t="n"/>
-      <c r="B20" s="86" t="inlineStr">
+      <c r="A20" s="27" t="n"/>
+      <c r="B20" s="77" t="inlineStr">
         <is>
           <t>勾选说明：按《基础营销验收单》模板默认口径「效果良好，符合要求」预勾「良好」，不拔高为「非常好」。请绿城营销负责人复核。</t>
         </is>
       </c>
-      <c r="C20" s="30" t="n"/>
-      <c r="D20" s="31" t="n"/>
+      <c r="C20" s="70" t="n"/>
+      <c r="D20" s="62" t="n"/>
     </row>
     <row r="21" ht="32" customHeight="1" s="17">
-      <c r="A21" s="25" t="n"/>
-      <c r="B21" s="83" t="inlineStr">
+      <c r="A21" s="27" t="n"/>
+      <c r="B21" s="74" t="inlineStr">
         <is>
           <t>营销负责人签名：____________________　　日期：____________________　　对接：笪浩 18678408669（评估表请补签）</t>
         </is>
       </c>
-      <c r="C21" s="30" t="n"/>
-      <c r="D21" s="31" t="n"/>
+      <c r="C21" s="70" t="n"/>
+      <c r="D21" s="62" t="n"/>
     </row>
     <row r="22" ht="36" customHeight="1" s="17">
-      <c r="A22" s="62" t="inlineStr">
+      <c r="A22" s="51" t="inlineStr">
         <is>
           <t>详见附件：本工作簿「按重要顺序分类」（18 张分级）「营销验收单」「权益核验清单」「赞助权益执行回执」及拍立享相册、网盘录像。合作金额含税 ¥100,000，四模块整体打包。本表仅对应 5 月 22 日峰会。</t>
         </is>
       </c>
-      <c r="B22" s="25" t="n"/>
-      <c r="C22" s="25" t="n"/>
-      <c r="D22" s="25" t="n"/>
+      <c r="B22" s="27" t="n"/>
+      <c r="C22" s="27" t="n"/>
+      <c r="D22" s="27" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="22">
@@ -5163,304 +5235,304 @@
   </cols>
   <sheetData>
     <row r="1" ht="36" customHeight="1" s="17">
-      <c r="A1" s="37" t="inlineStr">
+      <c r="A1" s="45" t="inlineStr">
         <is>
           <t>赞助权益执行回执</t>
         </is>
       </c>
-      <c r="B1" s="38" t="n"/>
-      <c r="C1" s="38" t="n"/>
-      <c r="D1" s="38" t="n"/>
+      <c r="B1" s="25" t="n"/>
+      <c r="C1" s="25" t="n"/>
+      <c r="D1" s="25" t="n"/>
     </row>
     <row r="2" ht="32" customHeight="1" s="17">
-      <c r="A2" s="39" t="inlineStr">
+      <c r="A2" s="46" t="inlineStr">
         <is>
           <t>依据《绿城中国-潮鸣外滩-10万元晚宴冠名服务报价单》：大会结束后 7 个自然日内，由主办向绿城一次性出具本回执，作为四模块整体验收依据。</t>
         </is>
       </c>
-      <c r="B2" s="40" t="n"/>
-      <c r="C2" s="40" t="n"/>
-      <c r="D2" s="40" t="n"/>
+      <c r="B2" s="30" t="n"/>
+      <c r="C2" s="30" t="n"/>
+      <c r="D2" s="30" t="n"/>
     </row>
     <row r="3" ht="28" customHeight="1" s="17">
-      <c r="A3" s="87" t="inlineStr">
+      <c r="A3" s="39" t="inlineStr">
         <is>
           <t>出具方（主办）</t>
         </is>
       </c>
-      <c r="B3" s="88" t="inlineStr">
+      <c r="B3" s="42" t="inlineStr">
         <is>
           <t>上海市杨浦区科技企业联合会</t>
         </is>
       </c>
-      <c r="C3" s="87" t="inlineStr">
+      <c r="C3" s="39" t="inlineStr">
         <is>
           <t>接收方（赞助）</t>
         </is>
       </c>
-      <c r="D3" s="88" t="inlineStr">
+      <c r="D3" s="42" t="inlineStr">
         <is>
           <t>上海绿城泓盛建设发展有限公司</t>
         </is>
       </c>
     </row>
     <row r="4" ht="28" customHeight="1" s="17">
-      <c r="A4" s="87" t="inlineStr">
+      <c r="A4" s="39" t="inlineStr">
         <is>
           <t>对接人</t>
         </is>
       </c>
-      <c r="B4" s="88" t="inlineStr">
+      <c r="B4" s="42" t="inlineStr">
         <is>
           <t>胡继刚　13262607888</t>
         </is>
       </c>
-      <c r="C4" s="87" t="inlineStr">
+      <c r="C4" s="39" t="inlineStr">
         <is>
           <t>对接人</t>
         </is>
       </c>
-      <c r="D4" s="88" t="inlineStr">
+      <c r="D4" s="42" t="inlineStr">
         <is>
           <t>笪浩　18678408669</t>
         </is>
       </c>
     </row>
     <row r="5" ht="28" customHeight="1" s="17">
-      <c r="A5" s="87" t="inlineStr">
+      <c r="A5" s="39" t="inlineStr">
         <is>
           <t>活动名称</t>
         </is>
       </c>
-      <c r="B5" s="88" t="inlineStr">
+      <c r="B5" s="42" t="inlineStr">
         <is>
           <t>2026人工智能商业化落地与硬核投资破局峰会</t>
         </is>
       </c>
-      <c r="C5" s="87" t="inlineStr">
+      <c r="C5" s="39" t="inlineStr">
         <is>
           <t>活动时间/地点</t>
         </is>
       </c>
-      <c r="D5" s="88" t="inlineStr">
+      <c r="D5" s="42" t="inlineStr">
         <is>
           <t>2026-05-22　上海·北外滩·一滴水</t>
         </is>
       </c>
     </row>
     <row r="6" ht="28" customHeight="1" s="17">
-      <c r="A6" s="87" t="inlineStr">
+      <c r="A6" s="39" t="inlineStr">
         <is>
           <t>合作身份</t>
         </is>
       </c>
-      <c r="B6" s="88" t="inlineStr">
+      <c r="B6" s="42" t="inlineStr">
         <is>
           <t>晚宴冠名战略合作伙伴</t>
         </is>
       </c>
-      <c r="C6" s="87" t="inlineStr">
+      <c r="C6" s="39" t="inlineStr">
         <is>
           <t>合作金额</t>
         </is>
       </c>
-      <c r="D6" s="88" t="inlineStr">
+      <c r="D6" s="42" t="inlineStr">
         <is>
           <t>人民币 100,000 元整（含税）</t>
         </is>
       </c>
     </row>
     <row r="7" ht="28" customHeight="1" s="17">
-      <c r="A7" s="87" t="inlineStr">
+      <c r="A7" s="39" t="inlineStr">
         <is>
           <t>晚宴场次</t>
         </is>
       </c>
-      <c r="B7" s="88" t="inlineStr">
+      <c r="B7" s="42" t="inlineStr">
         <is>
           <t>【绿城·潮鸣】星耀北外滩——AI领袖定制晚宴</t>
         </is>
       </c>
-      <c r="C7" s="87" t="inlineStr">
+      <c r="C7" s="39" t="inlineStr">
         <is>
           <t>项目品牌</t>
         </is>
       </c>
-      <c r="D7" s="88" t="inlineStr">
+      <c r="D7" s="42" t="inlineStr">
         <is>
           <t>绿城中国 · 绿城·潮鸣外滩</t>
         </is>
       </c>
     </row>
     <row r="8" ht="24" customHeight="1" s="17">
-      <c r="A8" s="89" t="inlineStr">
+      <c r="A8" s="78" t="inlineStr">
         <is>
           <t>四模块执行确认（整体打包，不拆子项计价）</t>
         </is>
       </c>
-      <c r="B8" s="38" t="n"/>
-      <c r="C8" s="38" t="n"/>
-      <c r="D8" s="38" t="n"/>
+      <c r="B8" s="25" t="n"/>
+      <c r="C8" s="25" t="n"/>
+      <c r="D8" s="25" t="n"/>
     </row>
     <row r="9" ht="22" customHeight="1" s="17">
-      <c r="A9" s="41" t="inlineStr">
+      <c r="A9" s="48" t="inlineStr">
         <is>
           <t>模块</t>
         </is>
       </c>
-      <c r="B9" s="41" t="inlineStr">
+      <c r="B9" s="48" t="inlineStr">
         <is>
           <t>金额（元）</t>
         </is>
       </c>
-      <c r="C9" s="41" t="inlineStr">
+      <c r="C9" s="48" t="inlineStr">
         <is>
           <t>执行结论</t>
         </is>
       </c>
-      <c r="D9" s="41" t="inlineStr">
+      <c r="D9" s="48" t="inlineStr">
         <is>
           <t>代表性证据</t>
         </is>
       </c>
     </row>
     <row r="10" ht="48" customHeight="1" s="17">
-      <c r="A10" s="61" t="inlineStr">
+      <c r="A10" s="50" t="inlineStr">
         <is>
           <t>1. 晚宴冠名和专属权益</t>
         </is>
       </c>
-      <c r="B10" s="61" t="inlineStr">
+      <c r="B10" s="50" t="inlineStr">
         <is>
           <t>55,000</t>
         </is>
       </c>
-      <c r="C10" s="63" t="inlineStr">
+      <c r="C10" s="52" t="inlineStr">
         <is>
           <t>☑ 已执行（冠名/品牌片）</t>
         </is>
       </c>
-      <c r="D10" s="62" t="inlineStr">
+      <c r="D10" s="51" t="inlineStr">
         <is>
           <t>议程看板【绿城·潮鸣】晚宴；主背景板「晚宴冠名战略合作伙伴·绿城中国」；晚宴大屏绿城中国品牌片</t>
         </is>
       </c>
     </row>
     <row r="11" ht="48" customHeight="1" s="17">
-      <c r="A11" s="61" t="inlineStr">
+      <c r="A11" s="50" t="inlineStr">
         <is>
           <t>2. 主会场权益</t>
         </is>
       </c>
-      <c r="B11" s="61" t="inlineStr">
+      <c r="B11" s="50" t="inlineStr">
         <is>
           <t>30,000</t>
         </is>
       </c>
-      <c r="C11" s="63" t="inlineStr">
+      <c r="C11" s="52" t="inlineStr">
         <is>
           <t>☑ 已执行（展台/双屏）</t>
         </is>
       </c>
-      <c r="D11" s="62" t="inlineStr">
+      <c r="D11" s="51" t="inlineStr">
         <is>
           <t>展台立牌「绿城中国 GREENTOWN」；展台接待礼袋物料；主会场双屏同款主视觉；主视觉KV含绿城中国</t>
         </is>
       </c>
     </row>
     <row r="12" ht="48" customHeight="1" s="17">
-      <c r="A12" s="61" t="inlineStr">
+      <c r="A12" s="50" t="inlineStr">
         <is>
           <t>3. 专场项目参观邀约</t>
         </is>
       </c>
-      <c r="B12" s="61" t="inlineStr">
+      <c r="B12" s="50" t="inlineStr">
         <is>
           <t>5,000</t>
         </is>
       </c>
-      <c r="C12" s="64" t="inlineStr">
+      <c r="C12" s="53" t="inlineStr">
         <is>
           <t>☐ 待录像核验</t>
         </is>
       </c>
-      <c r="D12" s="62" t="inlineStr">
+      <c r="D12" s="51" t="inlineStr">
         <is>
           <t>主持人口播位已具备。相册未见参观/接驳专项成片，请以全程录像确认是否口播执行。</t>
         </is>
       </c>
     </row>
     <row r="13" ht="48" customHeight="1" s="17">
-      <c r="A13" s="61" t="inlineStr">
+      <c r="A13" s="50" t="inlineStr">
         <is>
           <t>4. 宣发配合</t>
         </is>
       </c>
-      <c r="B13" s="61" t="inlineStr">
+      <c r="B13" s="50" t="inlineStr">
         <is>
           <t>10,000</t>
         </is>
       </c>
-      <c r="C13" s="64" t="inlineStr">
+      <c r="C13" s="53" t="inlineStr">
         <is>
           <t>☑ 摄影已交　☐ 其余待补</t>
         </is>
       </c>
-      <c r="D13" s="62" t="inlineStr">
+      <c r="D13" s="51" t="inlineStr">
         <is>
           <t>现场摄影+本回执。朋友圈九宫格、回顾视频片头鸣谢未附本回执。</t>
         </is>
       </c>
     </row>
     <row r="14" ht="48" customHeight="1" s="17">
-      <c r="A14" s="61" t="inlineStr">
+      <c r="A14" s="50" t="inlineStr">
         <is>
           <t>合计（含税）</t>
         </is>
       </c>
-      <c r="B14" s="61" t="inlineStr">
+      <c r="B14" s="50" t="inlineStr">
         <is>
           <t>100,000</t>
         </is>
       </c>
-      <c r="C14" s="64" t="inlineStr">
+      <c r="C14" s="53" t="inlineStr">
         <is>
           <t>主体已交，部分待补</t>
         </is>
       </c>
-      <c r="D14" s="62" t="inlineStr">
+      <c r="D14" s="51" t="inlineStr">
         <is>
           <t>四模块整体打包验收。已核验项以绿城/潮鸣字样可辨露出为准。</t>
         </is>
       </c>
     </row>
     <row r="15" ht="52" customHeight="1" s="17">
-      <c r="A15" s="62" t="inlineStr">
-        <is>
-          <t>证据目录：①营销验收单（封面 9 张）②按重要顺序分类（18 张全部按五级嵌入）③权益核验清单 ④效果评估表 ⑤绿城·潮鸣外滩露出大图 ⑥拍立享 https://live.pailixiang.com/album/a12523836160（约 425 张）⑦网盘录像 https://pan.baidu.com/s/1S8cNdqnCR_anuVPD6vlhjg 提取码 8888。证书特写未见，不以本回执推定证书已颁。</t>
-        </is>
-      </c>
-      <c r="B15" s="25" t="n"/>
-      <c r="C15" s="25" t="n"/>
-      <c r="D15" s="25" t="n"/>
+      <c r="A15" s="51" t="inlineStr">
+        <is>
+          <t>证据目录：①营销验收单（18 张五级排列，前三级集中前置）②按重要顺序分类（同序）③权益核验清单 ④效果评估表 ⑤绿城·潮鸣外滩露出大图 ⑥拍立享 https://live.pailixiang.com/album/a12523836160（约 425 张）⑦网盘录像 https://pan.baidu.com/s/1S8cNdqnCR_anuVPD6vlhjg 提取码 8888。证书特写未见，不以本回执推定证书已颁。</t>
+        </is>
+      </c>
+      <c r="B15" s="27" t="n"/>
+      <c r="C15" s="27" t="n"/>
+      <c r="D15" s="27" t="n"/>
     </row>
     <row r="16" ht="56" customHeight="1" s="17">
-      <c r="A16" s="90" t="inlineStr">
+      <c r="A16" s="79" t="inlineStr">
         <is>
           <t>总体结论：晚宴冠名与主会场露出已按约定落地，效果良好，符合要求（预勾「良好」）。参观邀约、朋友圈九宫格、回顾视频、证书特写为待补项，不影响四模块整体打包之主体验收，由绿城营销负责人复核后签字盖章。本回执不与 2026 年 3 月开盘花束验收混用。</t>
         </is>
       </c>
-      <c r="B16" s="52" t="n"/>
-      <c r="C16" s="52" t="n"/>
-      <c r="D16" s="52" t="n"/>
+      <c r="B16" s="32" t="n"/>
+      <c r="C16" s="32" t="n"/>
+      <c r="D16" s="32" t="n"/>
     </row>
     <row r="17" ht="36" customHeight="1" s="17">
-      <c r="A17" s="87" t="inlineStr">
+      <c r="A17" s="39" t="inlineStr">
         <is>
           <t>主办方（出具）</t>
         </is>
       </c>
-      <c r="B17" s="91" t="inlineStr">
+      <c r="B17" s="80" t="inlineStr">
         <is>
           <t>单位：上海市杨浦区科技企业联合会
 授权代表：胡继刚
@@ -5469,12 +5541,12 @@
 （公章）</t>
         </is>
       </c>
-      <c r="C17" s="87" t="inlineStr">
+      <c r="C17" s="39" t="inlineStr">
         <is>
           <t>赞助方（接收）</t>
         </is>
       </c>
-      <c r="D17" s="91" t="inlineStr">
+      <c r="D17" s="80" t="inlineStr">
         <is>
           <t>单位：上海绿城泓盛建设发展有限公司
 授权代表：____________________
@@ -5485,44 +5557,44 @@
       </c>
     </row>
     <row r="18" ht="72" customHeight="1" s="17">
-      <c r="A18" s="79" t="n"/>
-      <c r="B18" s="25" t="n"/>
-      <c r="C18" s="79" t="n"/>
-      <c r="D18" s="25" t="n"/>
+      <c r="A18" s="69" t="n"/>
+      <c r="B18" s="27" t="n"/>
+      <c r="C18" s="69" t="n"/>
+      <c r="D18" s="27" t="n"/>
     </row>
     <row r="19" ht="22" customHeight="1" s="17">
-      <c r="A19" s="89" t="inlineStr">
+      <c r="A19" s="78" t="inlineStr">
         <is>
           <t>回执附图（代表性证据，已嵌入本页）</t>
         </is>
       </c>
-      <c r="B19" s="38" t="n"/>
-      <c r="C19" s="38" t="n"/>
-      <c r="D19" s="38" t="n"/>
+      <c r="B19" s="25" t="n"/>
+      <c r="C19" s="25" t="n"/>
+      <c r="D19" s="25" t="n"/>
     </row>
     <row r="20" ht="118" customHeight="1" s="17">
-      <c r="A20" s="25" t="n"/>
-      <c r="B20" s="25" t="n"/>
-      <c r="C20" s="25" t="n"/>
-      <c r="D20" s="25" t="n"/>
+      <c r="A20" s="27" t="n"/>
+      <c r="B20" s="27" t="n"/>
+      <c r="C20" s="27" t="n"/>
+      <c r="D20" s="27" t="n"/>
     </row>
     <row r="21" ht="32" customHeight="1" s="17">
-      <c r="A21" s="29" t="inlineStr">
+      <c r="A21" s="28" t="inlineStr">
         <is>
           <t>议程看板【绿城·潮鸣】晚宴冠名</t>
         </is>
       </c>
-      <c r="B21" s="29" t="inlineStr">
+      <c r="B21" s="28" t="inlineStr">
         <is>
           <t>展台立牌：绿城中国 GREENTOWN</t>
         </is>
       </c>
-      <c r="C21" s="29" t="inlineStr">
+      <c r="C21" s="28" t="inlineStr">
         <is>
           <t>晚宴大屏绿城中国品牌片</t>
         </is>
       </c>
-      <c r="D21" s="29" t="inlineStr">
+      <c r="D21" s="28" t="inlineStr">
         <is>
           <t>主背景板：晚宴冠名·绿城中国</t>
         </is>
@@ -5564,276 +5636,276 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1" s="17">
-      <c r="A1" s="37" t="inlineStr">
+      <c r="A1" s="45" t="inlineStr">
         <is>
           <t>绿城中国｜绿城·潮鸣外滩 现场露出精华照片（按重要顺序 · 甲方交付）</t>
         </is>
       </c>
-      <c r="B1" s="38" t="n"/>
-      <c r="C1" s="38" t="n"/>
-      <c r="D1" s="38" t="n"/>
+      <c r="B1" s="25" t="n"/>
+      <c r="C1" s="25" t="n"/>
+      <c r="D1" s="25" t="n"/>
     </row>
     <row r="2" ht="36" customHeight="1" s="17">
-      <c r="A2" s="39" t="inlineStr">
+      <c r="A2" s="46" t="inlineStr">
         <is>
           <t>活动时间：2026-05-22　地点：上海·北外滩·一滴水　本页 18 张按一级→五级排列（与「按重要顺序分类」同序）　完整相册约 425 张：https://live.pailixiang.com/album/a12523836160　录像：https://pan.baidu.com/s/1S8cNdqnCR_anuVPD6vlhjg（提取码 8888）</t>
         </is>
       </c>
-      <c r="B2" s="40" t="n"/>
-      <c r="C2" s="40" t="n"/>
-      <c r="D2" s="40" t="n"/>
+      <c r="B2" s="30" t="n"/>
+      <c r="C2" s="30" t="n"/>
+      <c r="D2" s="30" t="n"/>
     </row>
     <row r="4" ht="28" customHeight="1" s="17">
-      <c r="A4" s="89" t="inlineStr">
+      <c r="A4" s="78" t="inlineStr">
         <is>
           <t>一级｜核心品牌露出（必看）（4 张）　绿城 / 潮鸣 / GREENTOWN 字样可直接核验，对应报价主体，建议甲方优先复核。</t>
         </is>
       </c>
-      <c r="B4" s="38" t="n"/>
-      <c r="C4" s="38" t="n"/>
-      <c r="D4" s="38" t="n"/>
+      <c r="B4" s="25" t="n"/>
+      <c r="C4" s="25" t="n"/>
+      <c r="D4" s="25" t="n"/>
     </row>
     <row r="5" ht="168" customHeight="1" s="17">
-      <c r="A5" s="25" t="n"/>
-      <c r="B5" s="25" t="n"/>
-      <c r="C5" s="25" t="n"/>
-      <c r="D5" s="25" t="n"/>
+      <c r="A5" s="27" t="n"/>
+      <c r="B5" s="27" t="n"/>
+      <c r="C5" s="27" t="n"/>
+      <c r="D5" s="27" t="n"/>
     </row>
     <row r="6" ht="36" customHeight="1" s="17">
-      <c r="A6" s="62" t="inlineStr">
+      <c r="A6" s="51" t="inlineStr">
         <is>
           <t>1. 议程看板【绿城·潮鸣】星耀北外滩晚宴</t>
         </is>
       </c>
-      <c r="B6" s="31" t="n"/>
-      <c r="C6" s="62" t="inlineStr">
+      <c r="B6" s="62" t="n"/>
+      <c r="C6" s="51" t="inlineStr">
         <is>
           <t>2. 主背景板：晚宴冠名战略合作伙伴·绿城中国</t>
         </is>
       </c>
-      <c r="D6" s="31" t="n"/>
+      <c r="D6" s="62" t="n"/>
     </row>
     <row r="7" ht="168" customHeight="1" s="17">
-      <c r="A7" s="25" t="n"/>
-      <c r="B7" s="25" t="n"/>
-      <c r="C7" s="25" t="n"/>
-      <c r="D7" s="25" t="n"/>
+      <c r="A7" s="27" t="n"/>
+      <c r="B7" s="27" t="n"/>
+      <c r="C7" s="27" t="n"/>
+      <c r="D7" s="27" t="n"/>
     </row>
     <row r="8" ht="36" customHeight="1" s="17">
-      <c r="A8" s="62" t="inlineStr">
+      <c r="A8" s="51" t="inlineStr">
         <is>
           <t>3. 展台立牌：绿城中国 GREENTOWN</t>
         </is>
       </c>
-      <c r="B8" s="31" t="n"/>
-      <c r="C8" s="62" t="inlineStr">
+      <c r="B8" s="62" t="n"/>
+      <c r="C8" s="51" t="inlineStr">
         <is>
           <t>4. 晚宴大屏播放绿城中国品牌片</t>
         </is>
       </c>
-      <c r="D8" s="31" t="n"/>
+      <c r="D8" s="62" t="n"/>
     </row>
     <row r="9" ht="28" customHeight="1" s="17">
-      <c r="A9" s="66" t="inlineStr">
+      <c r="A9" s="55" t="inlineStr">
         <is>
           <t>二级｜主会场执行（重点）（4 张）　展台接待、双屏、主持、主视觉，证明主会场权益已落地。</t>
         </is>
       </c>
-      <c r="B9" s="40" t="n"/>
-      <c r="C9" s="40" t="n"/>
-      <c r="D9" s="40" t="n"/>
+      <c r="B9" s="30" t="n"/>
+      <c r="C9" s="30" t="n"/>
+      <c r="D9" s="30" t="n"/>
     </row>
     <row r="10" ht="168" customHeight="1" s="17">
-      <c r="A10" s="25" t="n"/>
-      <c r="B10" s="25" t="n"/>
-      <c r="C10" s="25" t="n"/>
-      <c r="D10" s="25" t="n"/>
+      <c r="A10" s="27" t="n"/>
+      <c r="B10" s="27" t="n"/>
+      <c r="C10" s="27" t="n"/>
+      <c r="D10" s="27" t="n"/>
     </row>
     <row r="11" ht="36" customHeight="1" s="17">
-      <c r="A11" s="62" t="inlineStr">
+      <c r="A11" s="51" t="inlineStr">
         <is>
           <t>5. 展台接待：绿城立牌、礼袋与物料</t>
         </is>
       </c>
-      <c r="B11" s="31" t="n"/>
-      <c r="C11" s="62" t="inlineStr">
+      <c r="B11" s="62" t="n"/>
+      <c r="C11" s="51" t="inlineStr">
         <is>
           <t>6. 主会场双屏同款主视觉（含晚宴冠名·绿城中国）</t>
         </is>
       </c>
-      <c r="D11" s="31" t="n"/>
+      <c r="D11" s="62" t="n"/>
     </row>
     <row r="12" ht="168" customHeight="1" s="17">
-      <c r="A12" s="25" t="n"/>
-      <c r="B12" s="25" t="n"/>
-      <c r="C12" s="25" t="n"/>
-      <c r="D12" s="25" t="n"/>
+      <c r="A12" s="27" t="n"/>
+      <c r="B12" s="27" t="n"/>
+      <c r="C12" s="27" t="n"/>
+      <c r="D12" s="27" t="n"/>
     </row>
     <row r="13" ht="36" customHeight="1" s="17">
-      <c r="A13" s="62" t="inlineStr">
+      <c r="A13" s="51" t="inlineStr">
         <is>
           <t>7. 主持现场：主会场露出</t>
         </is>
       </c>
-      <c r="B13" s="31" t="n"/>
-      <c r="C13" s="62" t="inlineStr">
+      <c r="B13" s="62" t="n"/>
+      <c r="C13" s="51" t="inlineStr">
         <is>
           <t>8. 主视觉 KV：战略合作名单含绿城中国</t>
         </is>
       </c>
-      <c r="D13" s="31" t="n"/>
+      <c r="D13" s="62" t="n"/>
     </row>
     <row r="14" ht="28" customHeight="1" s="17">
-      <c r="A14" s="92" t="inlineStr">
+      <c r="A14" s="81" t="inlineStr">
         <is>
           <t>三级｜冠名位合影核验（4 张）　主背景板合影，可复核晚宴冠名位「绿城中国」。</t>
         </is>
       </c>
-      <c r="B14" s="52" t="n"/>
-      <c r="C14" s="52" t="n"/>
-      <c r="D14" s="52" t="n"/>
+      <c r="B14" s="32" t="n"/>
+      <c r="C14" s="32" t="n"/>
+      <c r="D14" s="32" t="n"/>
     </row>
     <row r="15" ht="168" customHeight="1" s="17">
-      <c r="A15" s="25" t="n"/>
-      <c r="B15" s="25" t="n"/>
-      <c r="C15" s="25" t="n"/>
-      <c r="D15" s="25" t="n"/>
+      <c r="A15" s="27" t="n"/>
+      <c r="B15" s="27" t="n"/>
+      <c r="C15" s="27" t="n"/>
+      <c r="D15" s="27" t="n"/>
     </row>
     <row r="16" ht="36" customHeight="1" s="17">
-      <c r="A16" s="62" t="inlineStr">
+      <c r="A16" s="51" t="inlineStr">
         <is>
           <t>9. 主背景板合影核验冠名位</t>
         </is>
       </c>
-      <c r="B16" s="31" t="n"/>
-      <c r="C16" s="62" t="inlineStr">
+      <c r="B16" s="62" t="n"/>
+      <c r="C16" s="51" t="inlineStr">
         <is>
           <t>10. 主背景板合影（冠名位特写）</t>
         </is>
       </c>
-      <c r="D16" s="31" t="n"/>
+      <c r="D16" s="62" t="n"/>
     </row>
     <row r="17" ht="168" customHeight="1" s="17">
-      <c r="A17" s="25" t="n"/>
-      <c r="B17" s="25" t="n"/>
-      <c r="C17" s="25" t="n"/>
-      <c r="D17" s="25" t="n"/>
+      <c r="A17" s="27" t="n"/>
+      <c r="B17" s="27" t="n"/>
+      <c r="C17" s="27" t="n"/>
+      <c r="D17" s="27" t="n"/>
     </row>
     <row r="18" ht="36" customHeight="1" s="17">
-      <c r="A18" s="62" t="inlineStr">
+      <c r="A18" s="51" t="inlineStr">
         <is>
           <t>11. 主背景板双人合影核验冠名位</t>
         </is>
       </c>
-      <c r="B18" s="31" t="n"/>
-      <c r="C18" s="62" t="inlineStr">
+      <c r="B18" s="62" t="n"/>
+      <c r="C18" s="51" t="inlineStr">
         <is>
           <t>12. 主背景板合影：晚宴冠名战略合作伙伴·绿城中国</t>
         </is>
       </c>
-      <c r="D18" s="31" t="n"/>
+      <c r="D18" s="62" t="n"/>
     </row>
     <row r="19" ht="28" customHeight="1" s="17">
-      <c r="A19" s="93" t="inlineStr">
+      <c r="A19" s="82" t="inlineStr">
         <is>
           <t>四级｜主办致辞现场（3 张）　主会场致辞与讲台，补充现场执行；不作参观邀约专项成片。</t>
         </is>
       </c>
-      <c r="B19" s="58" t="n"/>
-      <c r="C19" s="58" t="n"/>
-      <c r="D19" s="58" t="n"/>
+      <c r="B19" s="36" t="n"/>
+      <c r="C19" s="36" t="n"/>
+      <c r="D19" s="36" t="n"/>
     </row>
     <row r="20" ht="168" customHeight="1" s="17">
-      <c r="A20" s="25" t="n"/>
-      <c r="B20" s="25" t="n"/>
-      <c r="C20" s="25" t="n"/>
-      <c r="D20" s="25" t="n"/>
+      <c r="A20" s="27" t="n"/>
+      <c r="B20" s="27" t="n"/>
+      <c r="C20" s="27" t="n"/>
+      <c r="D20" s="27" t="n"/>
     </row>
     <row r="21" ht="36" customHeight="1" s="17">
-      <c r="A21" s="62" t="inlineStr">
+      <c r="A21" s="51" t="inlineStr">
         <is>
           <t>13. 主办致辞全景：主会场双屏与讲台</t>
         </is>
       </c>
-      <c r="B21" s="31" t="n"/>
-      <c r="C21" s="62" t="inlineStr">
+      <c r="B21" s="62" t="n"/>
+      <c r="C21" s="51" t="inlineStr">
         <is>
           <t>14. 主办致辞：姚志勇，主会场主视觉</t>
         </is>
       </c>
-      <c r="D21" s="31" t="n"/>
+      <c r="D21" s="62" t="n"/>
     </row>
     <row r="22" ht="168" customHeight="1" s="17">
-      <c r="A22" s="25" t="n"/>
-      <c r="B22" s="25" t="n"/>
-      <c r="C22" s="25" t="n"/>
-      <c r="D22" s="25" t="n"/>
+      <c r="A22" s="27" t="n"/>
+      <c r="B22" s="27" t="n"/>
+      <c r="C22" s="27" t="n"/>
+      <c r="D22" s="27" t="n"/>
     </row>
     <row r="23" ht="36" customHeight="1" s="17">
-      <c r="A23" s="62" t="inlineStr">
+      <c r="A23" s="51" t="inlineStr">
         <is>
           <t>15. 主办致辞讲台特写</t>
         </is>
       </c>
-      <c r="B23" s="31" t="n"/>
-      <c r="C23" s="25" t="n"/>
-      <c r="D23" s="25" t="n"/>
+      <c r="B23" s="62" t="n"/>
+      <c r="C23" s="27" t="n"/>
+      <c r="D23" s="27" t="n"/>
     </row>
     <row r="24" ht="28" customHeight="1" s="17">
-      <c r="A24" s="94" t="inlineStr">
+      <c r="A24" s="83" t="inlineStr">
         <is>
           <t>五级｜冠名晚宴氛围（3 张）　江景厅冠名晚宴现场。席卡为嘉宾姓名卡，不作「潮鳴」logo 桌卡证据。</t>
         </is>
       </c>
-      <c r="B24" s="25" t="n"/>
-      <c r="C24" s="25" t="n"/>
-      <c r="D24" s="25" t="n"/>
+      <c r="B24" s="27" t="n"/>
+      <c r="C24" s="27" t="n"/>
+      <c r="D24" s="27" t="n"/>
     </row>
     <row r="25" ht="168" customHeight="1" s="17">
-      <c r="A25" s="25" t="n"/>
-      <c r="B25" s="25" t="n"/>
-      <c r="C25" s="25" t="n"/>
-      <c r="D25" s="25" t="n"/>
+      <c r="A25" s="27" t="n"/>
+      <c r="B25" s="27" t="n"/>
+      <c r="C25" s="27" t="n"/>
+      <c r="D25" s="27" t="n"/>
     </row>
     <row r="26" ht="36" customHeight="1" s="17">
-      <c r="A26" s="62" t="inlineStr">
+      <c r="A26" s="51" t="inlineStr">
         <is>
           <t>16. 冠名晚宴合影（江景厅）</t>
         </is>
       </c>
-      <c r="B26" s="31" t="n"/>
-      <c r="C26" s="62" t="inlineStr">
+      <c r="B26" s="62" t="n"/>
+      <c r="C26" s="51" t="inlineStr">
         <is>
           <t>17. 冠名晚宴桌次（江景厅圆桌）</t>
         </is>
       </c>
-      <c r="D26" s="31" t="n"/>
+      <c r="D26" s="62" t="n"/>
     </row>
     <row r="27" ht="168" customHeight="1" s="17">
-      <c r="A27" s="25" t="n"/>
-      <c r="B27" s="25" t="n"/>
-      <c r="C27" s="25" t="n"/>
-      <c r="D27" s="25" t="n"/>
+      <c r="A27" s="27" t="n"/>
+      <c r="B27" s="27" t="n"/>
+      <c r="C27" s="27" t="n"/>
+      <c r="D27" s="27" t="n"/>
     </row>
     <row r="28" ht="36" customHeight="1" s="17">
-      <c r="A28" s="62" t="inlineStr">
+      <c r="A28" s="51" t="inlineStr">
         <is>
           <t>18. 冠名晚宴现场举杯</t>
         </is>
       </c>
-      <c r="B28" s="31" t="n"/>
-      <c r="C28" s="25" t="n"/>
-      <c r="D28" s="25" t="n"/>
+      <c r="B28" s="62" t="n"/>
+      <c r="C28" s="27" t="n"/>
+      <c r="D28" s="27" t="n"/>
     </row>
     <row r="30" ht="42" customHeight="1" s="17">
-      <c r="A30" s="62" t="inlineStr">
+      <c r="A30" s="51" t="inlineStr">
         <is>
           <t>说明：本页只收录绿城中国、绿城·潮鸣、GREENTOWN 可辨露出及冠名晚宴现场。未收录美年大健康、泰隆银行、腾讯云、蔚来、长江商学院等他方展位。完整 425 张以拍立享为准；MP4 以网盘「5.22」为准。不与开盘花束混用。</t>
         </is>
       </c>
-      <c r="B30" s="25" t="n"/>
-      <c r="C30" s="25" t="n"/>
-      <c r="D30" s="25" t="n"/>
+      <c r="B30" s="27" t="n"/>
+      <c r="C30" s="27" t="n"/>
+      <c r="D30" s="27" t="n"/>
     </row>
   </sheetData>
   <mergeCells count="26">
@@ -5893,75 +5965,75 @@
   </cols>
   <sheetData>
     <row r="1" ht="28" customHeight="1" s="17">
-      <c r="A1" s="37" t="inlineStr">
+      <c r="A1" s="45" t="inlineStr">
         <is>
           <t>绿城·潮鸣外滩露出 · 精华照片索引（按重要等级）</t>
         </is>
       </c>
-      <c r="B1" s="38" t="n"/>
-      <c r="C1" s="38" t="n"/>
-      <c r="D1" s="38" t="n"/>
-      <c r="E1" s="38" t="n"/>
-      <c r="F1" s="38" t="n"/>
-      <c r="G1" s="38" t="n"/>
+      <c r="B1" s="25" t="n"/>
+      <c r="C1" s="25" t="n"/>
+      <c r="D1" s="25" t="n"/>
+      <c r="E1" s="25" t="n"/>
+      <c r="F1" s="25" t="n"/>
+      <c r="G1" s="25" t="n"/>
     </row>
     <row r="2" ht="28" customHeight="1" s="17">
-      <c r="A2" s="39" t="inlineStr">
+      <c r="A2" s="46" t="inlineStr">
         <is>
           <t>按一级→五级排列，与「按重要顺序分类」同序。拍摄时间取自拍立享相册元数据。不收录他方展位（美年大健康、泰隆银行、腾讯云、蔚来、长江商学院）。</t>
         </is>
       </c>
-      <c r="B2" s="40" t="n"/>
-      <c r="C2" s="40" t="n"/>
-      <c r="D2" s="40" t="n"/>
-      <c r="E2" s="40" t="n"/>
-      <c r="F2" s="40" t="n"/>
-      <c r="G2" s="40" t="n"/>
+      <c r="B2" s="30" t="n"/>
+      <c r="C2" s="30" t="n"/>
+      <c r="D2" s="30" t="n"/>
+      <c r="E2" s="30" t="n"/>
+      <c r="F2" s="30" t="n"/>
+      <c r="G2" s="30" t="n"/>
     </row>
     <row r="3">
-      <c r="A3" s="41" t="inlineStr">
+      <c r="A3" s="48" t="inlineStr">
         <is>
           <t>图号</t>
         </is>
       </c>
-      <c r="B3" s="41" t="inlineStr">
+      <c r="B3" s="48" t="inlineStr">
         <is>
           <t>重要等级</t>
         </is>
       </c>
-      <c r="C3" s="41" t="inlineStr">
+      <c r="C3" s="48" t="inlineStr">
         <is>
           <t>文件名</t>
         </is>
       </c>
-      <c r="D3" s="41" t="inlineStr">
+      <c r="D3" s="48" t="inlineStr">
         <is>
           <t>拍摄时间</t>
         </is>
       </c>
-      <c r="E3" s="41" t="inlineStr">
+      <c r="E3" s="48" t="inlineStr">
         <is>
           <t>露出点</t>
         </is>
       </c>
-      <c r="F3" s="41" t="inlineStr">
+      <c r="F3" s="48" t="inlineStr">
         <is>
           <t>对应模块</t>
         </is>
       </c>
-      <c r="G3" s="41" t="inlineStr">
-        <is>
-          <t>封面</t>
+      <c r="G3" s="48" t="inlineStr">
+        <is>
+          <t>位置</t>
         </is>
       </c>
     </row>
     <row r="4" ht="22" customHeight="1" s="17">
-      <c r="A4" s="95" t="inlineStr">
+      <c r="A4" s="84" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="B4" s="51" t="inlineStr">
+      <c r="B4" s="85" t="inlineStr">
         <is>
           <t>一级 核心品牌露出（必看）</t>
         </is>
@@ -5971,7 +6043,7 @@
           <t>941A7785.JPG</t>
         </is>
       </c>
-      <c r="D4" s="95" t="inlineStr">
+      <c r="D4" s="84" t="inlineStr">
         <is>
           <t>2026-05-22 13:20:53</t>
         </is>
@@ -5981,24 +6053,24 @@
           <t>议程看板【绿城·潮鸣】星耀北外滩晚宴</t>
         </is>
       </c>
-      <c r="F4" s="95" t="inlineStr">
+      <c r="F4" s="84" t="inlineStr">
         <is>
           <t>晚宴冠名</t>
         </is>
       </c>
-      <c r="G4" s="95" t="inlineStr">
-        <is>
-          <t>是</t>
+      <c r="G4" s="84" t="inlineStr">
+        <is>
+          <t>前三级</t>
         </is>
       </c>
     </row>
     <row r="5" ht="22" customHeight="1" s="17">
-      <c r="A5" s="95" t="inlineStr">
+      <c r="A5" s="84" t="inlineStr">
         <is>
           <t>2</t>
         </is>
       </c>
-      <c r="B5" s="51" t="inlineStr">
+      <c r="B5" s="85" t="inlineStr">
         <is>
           <t>一级 核心品牌露出（必看）</t>
         </is>
@@ -6008,7 +6080,7 @@
           <t>941A7663.JPG</t>
         </is>
       </c>
-      <c r="D5" s="95" t="inlineStr">
+      <c r="D5" s="84" t="inlineStr">
         <is>
           <t>2026-05-22 12:54:38</t>
         </is>
@@ -6018,24 +6090,24 @@
           <t>主背景板：晚宴冠名战略合作伙伴·绿城中国</t>
         </is>
       </c>
-      <c r="F5" s="95" t="inlineStr">
+      <c r="F5" s="84" t="inlineStr">
         <is>
           <t>晚宴冠名</t>
         </is>
       </c>
-      <c r="G5" s="95" t="inlineStr">
-        <is>
-          <t>是</t>
+      <c r="G5" s="84" t="inlineStr">
+        <is>
+          <t>前三级</t>
         </is>
       </c>
     </row>
     <row r="6" ht="22" customHeight="1" s="17">
-      <c r="A6" s="95" t="inlineStr">
+      <c r="A6" s="84" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="B6" s="51" t="inlineStr">
+      <c r="B6" s="85" t="inlineStr">
         <is>
           <t>一级 核心品牌露出（必看）</t>
         </is>
@@ -6045,7 +6117,7 @@
           <t>941A7769.JPG</t>
         </is>
       </c>
-      <c r="D6" s="95" t="inlineStr">
+      <c r="D6" s="84" t="inlineStr">
         <is>
           <t>2026-05-22 13:17:12</t>
         </is>
@@ -6055,24 +6127,24 @@
           <t>展台立牌：绿城中国 GREENTOWN</t>
         </is>
       </c>
-      <c r="F6" s="95" t="inlineStr">
+      <c r="F6" s="84" t="inlineStr">
         <is>
           <t>主会场</t>
         </is>
       </c>
-      <c r="G6" s="95" t="inlineStr">
-        <is>
-          <t>是</t>
+      <c r="G6" s="84" t="inlineStr">
+        <is>
+          <t>前三级</t>
         </is>
       </c>
     </row>
     <row r="7" ht="22" customHeight="1" s="17">
-      <c r="A7" s="95" t="inlineStr">
+      <c r="A7" s="84" t="inlineStr">
         <is>
           <t>4</t>
         </is>
       </c>
-      <c r="B7" s="51" t="inlineStr">
+      <c r="B7" s="85" t="inlineStr">
         <is>
           <t>一级 核心品牌露出（必看）</t>
         </is>
@@ -6082,7 +6154,7 @@
           <t>941A8810.JPG</t>
         </is>
       </c>
-      <c r="D7" s="95" t="inlineStr">
+      <c r="D7" s="84" t="inlineStr">
         <is>
           <t>2026-05-22 19:50:04</t>
         </is>
@@ -6092,19 +6164,19 @@
           <t>晚宴大屏播放绿城中国品牌片</t>
         </is>
       </c>
-      <c r="F7" s="95" t="inlineStr">
+      <c r="F7" s="84" t="inlineStr">
         <is>
           <t>晚宴冠名</t>
         </is>
       </c>
-      <c r="G7" s="95" t="inlineStr">
-        <is>
-          <t>是</t>
+      <c r="G7" s="84" t="inlineStr">
+        <is>
+          <t>前三级</t>
         </is>
       </c>
     </row>
     <row r="8" ht="22" customHeight="1" s="17">
-      <c r="A8" s="95" t="inlineStr">
+      <c r="A8" s="84" t="inlineStr">
         <is>
           <t>5</t>
         </is>
@@ -6119,7 +6191,7 @@
           <t>941A7768.JPG</t>
         </is>
       </c>
-      <c r="D8" s="95" t="inlineStr">
+      <c r="D8" s="84" t="inlineStr">
         <is>
           <t>2026-05-22 13:16:51</t>
         </is>
@@ -6129,19 +6201,19 @@
           <t>展台接待：绿城立牌、礼袋与物料</t>
         </is>
       </c>
-      <c r="F8" s="95" t="inlineStr">
+      <c r="F8" s="84" t="inlineStr">
         <is>
           <t>主会场</t>
         </is>
       </c>
-      <c r="G8" s="95" t="inlineStr">
-        <is>
-          <t>是</t>
+      <c r="G8" s="84" t="inlineStr">
+        <is>
+          <t>前三级</t>
         </is>
       </c>
     </row>
     <row r="9" ht="22" customHeight="1" s="17">
-      <c r="A9" s="95" t="inlineStr">
+      <c r="A9" s="84" t="inlineStr">
         <is>
           <t>6</t>
         </is>
@@ -6156,7 +6228,7 @@
           <t>941A7832.JPG</t>
         </is>
       </c>
-      <c r="D9" s="95" t="inlineStr">
+      <c r="D9" s="84" t="inlineStr">
         <is>
           <t>2026-05-22 13:37:45</t>
         </is>
@@ -6166,19 +6238,19 @@
           <t>主会场双屏同款主视觉（含晚宴冠名·绿城中国）</t>
         </is>
       </c>
-      <c r="F9" s="95" t="inlineStr">
+      <c r="F9" s="84" t="inlineStr">
         <is>
           <t>主会场</t>
         </is>
       </c>
-      <c r="G9" s="95" t="inlineStr">
-        <is>
-          <t>是</t>
+      <c r="G9" s="84" t="inlineStr">
+        <is>
+          <t>前三级</t>
         </is>
       </c>
     </row>
     <row r="10" ht="22" customHeight="1" s="17">
-      <c r="A10" s="95" t="inlineStr">
+      <c r="A10" s="84" t="inlineStr">
         <is>
           <t>7</t>
         </is>
@@ -6193,7 +6265,7 @@
           <t>941A7825.JPG</t>
         </is>
       </c>
-      <c r="D10" s="95" t="inlineStr">
+      <c r="D10" s="84" t="inlineStr">
         <is>
           <t>2026-05-22 13:36:38</t>
         </is>
@@ -6203,19 +6275,19 @@
           <t>主持现场：主会场露出</t>
         </is>
       </c>
-      <c r="F10" s="95" t="inlineStr">
+      <c r="F10" s="84" t="inlineStr">
         <is>
           <t>主会场</t>
         </is>
       </c>
-      <c r="G10" s="95" t="inlineStr">
-        <is>
-          <t>是</t>
+      <c r="G10" s="84" t="inlineStr">
+        <is>
+          <t>前三级</t>
         </is>
       </c>
     </row>
     <row r="11" ht="22" customHeight="1" s="17">
-      <c r="A11" s="95" t="inlineStr">
+      <c r="A11" s="84" t="inlineStr">
         <is>
           <t>8</t>
         </is>
@@ -6230,7 +6302,7 @@
           <t>00_banner.jpg</t>
         </is>
       </c>
-      <c r="D11" s="95" t="inlineStr">
+      <c r="D11" s="84" t="inlineStr">
         <is>
           <t>主视觉 KV（相册 Banner）</t>
         </is>
@@ -6240,19 +6312,19 @@
           <t>主视觉 KV：战略合作名单含绿城中国</t>
         </is>
       </c>
-      <c r="F11" s="95" t="inlineStr">
+      <c r="F11" s="84" t="inlineStr">
         <is>
           <t>主会场/宣发</t>
         </is>
       </c>
-      <c r="G11" s="95" t="inlineStr">
-        <is>
-          <t>是</t>
+      <c r="G11" s="84" t="inlineStr">
+        <is>
+          <t>前三级</t>
         </is>
       </c>
     </row>
     <row r="12" ht="22" customHeight="1" s="17">
-      <c r="A12" s="95" t="inlineStr">
+      <c r="A12" s="84" t="inlineStr">
         <is>
           <t>9</t>
         </is>
@@ -6267,7 +6339,7 @@
           <t>941A7776.JPG</t>
         </is>
       </c>
-      <c r="D12" s="95" t="inlineStr">
+      <c r="D12" s="84" t="inlineStr">
         <is>
           <t>2026-05-22 13:18:16</t>
         </is>
@@ -6277,347 +6349,347 @@
           <t>主背景板合影核验冠名位</t>
         </is>
       </c>
-      <c r="F12" s="95" t="inlineStr">
+      <c r="F12" s="84" t="inlineStr">
         <is>
           <t>晚宴冠名</t>
         </is>
       </c>
-      <c r="G12" s="95" t="inlineStr">
-        <is>
-          <t>是</t>
+      <c r="G12" s="84" t="inlineStr">
+        <is>
+          <t>前三级</t>
         </is>
       </c>
     </row>
     <row r="13" ht="22" customHeight="1" s="17">
-      <c r="A13" s="60" t="inlineStr">
+      <c r="A13" s="84" t="inlineStr">
         <is>
           <t>10</t>
         </is>
       </c>
-      <c r="B13" s="62" t="inlineStr">
+      <c r="B13" s="54" t="inlineStr">
         <is>
           <t>三级 冠名位合影核验</t>
         </is>
       </c>
-      <c r="C13" s="62" t="inlineStr">
+      <c r="C13" s="54" t="inlineStr">
         <is>
           <t>941A7777.JPG</t>
         </is>
       </c>
-      <c r="D13" s="60" t="inlineStr">
+      <c r="D13" s="84" t="inlineStr">
         <is>
           <t>2026-05-22 13:19:01</t>
         </is>
       </c>
-      <c r="E13" s="62" t="inlineStr">
+      <c r="E13" s="54" t="inlineStr">
         <is>
           <t>主背景板合影（冠名位特写）</t>
         </is>
       </c>
-      <c r="F13" s="60" t="inlineStr">
+      <c r="F13" s="84" t="inlineStr">
         <is>
           <t>晚宴冠名</t>
         </is>
       </c>
-      <c r="G13" s="60" t="inlineStr">
-        <is>
-          <t>否</t>
+      <c r="G13" s="84" t="inlineStr">
+        <is>
+          <t>前三级</t>
         </is>
       </c>
     </row>
     <row r="14" ht="22" customHeight="1" s="17">
-      <c r="A14" s="60" t="inlineStr">
+      <c r="A14" s="84" t="inlineStr">
         <is>
           <t>11</t>
         </is>
       </c>
-      <c r="B14" s="62" t="inlineStr">
+      <c r="B14" s="54" t="inlineStr">
         <is>
           <t>三级 冠名位合影核验</t>
         </is>
       </c>
-      <c r="C14" s="62" t="inlineStr">
+      <c r="C14" s="54" t="inlineStr">
         <is>
           <t>941A7779.JPG</t>
         </is>
       </c>
-      <c r="D14" s="60" t="inlineStr">
+      <c r="D14" s="84" t="inlineStr">
         <is>
           <t>2026-05-22 13:19:08</t>
         </is>
       </c>
-      <c r="E14" s="62" t="inlineStr">
+      <c r="E14" s="54" t="inlineStr">
         <is>
           <t>主背景板双人合影核验冠名位</t>
         </is>
       </c>
-      <c r="F14" s="60" t="inlineStr">
+      <c r="F14" s="84" t="inlineStr">
         <is>
           <t>晚宴冠名</t>
         </is>
       </c>
-      <c r="G14" s="60" t="inlineStr">
-        <is>
-          <t>否</t>
+      <c r="G14" s="84" t="inlineStr">
+        <is>
+          <t>前三级</t>
         </is>
       </c>
     </row>
     <row r="15" ht="22" customHeight="1" s="17">
-      <c r="A15" s="60" t="inlineStr">
+      <c r="A15" s="84" t="inlineStr">
         <is>
           <t>12</t>
         </is>
       </c>
-      <c r="B15" s="62" t="inlineStr">
+      <c r="B15" s="54" t="inlineStr">
         <is>
           <t>三级 冠名位合影核验</t>
         </is>
       </c>
-      <c r="C15" s="62" t="inlineStr">
+      <c r="C15" s="54" t="inlineStr">
         <is>
           <t>941A7782.JPG</t>
         </is>
       </c>
-      <c r="D15" s="60" t="inlineStr">
+      <c r="D15" s="84" t="inlineStr">
         <is>
           <t>2026-05-22 13:19:19</t>
         </is>
       </c>
-      <c r="E15" s="62" t="inlineStr">
+      <c r="E15" s="54" t="inlineStr">
         <is>
           <t>主背景板合影：晚宴冠名战略合作伙伴·绿城中国</t>
         </is>
       </c>
-      <c r="F15" s="60" t="inlineStr">
+      <c r="F15" s="84" t="inlineStr">
         <is>
           <t>晚宴冠名</t>
         </is>
       </c>
-      <c r="G15" s="60" t="inlineStr">
-        <is>
-          <t>否</t>
+      <c r="G15" s="84" t="inlineStr">
+        <is>
+          <t>前三级</t>
         </is>
       </c>
     </row>
     <row r="16" ht="22" customHeight="1" s="17">
-      <c r="A16" s="60" t="inlineStr">
+      <c r="A16" s="49" t="inlineStr">
         <is>
           <t>13</t>
         </is>
       </c>
-      <c r="B16" s="62" t="inlineStr">
+      <c r="B16" s="51" t="inlineStr">
         <is>
           <t>四级 主办致辞现场</t>
         </is>
       </c>
-      <c r="C16" s="62" t="inlineStr">
+      <c r="C16" s="51" t="inlineStr">
         <is>
           <t>941A7851.JPG</t>
         </is>
       </c>
-      <c r="D16" s="60" t="inlineStr">
+      <c r="D16" s="49" t="inlineStr">
         <is>
           <t>2026-05-22 13:40:52</t>
         </is>
       </c>
-      <c r="E16" s="62" t="inlineStr">
+      <c r="E16" s="51" t="inlineStr">
         <is>
           <t>主办致辞全景：主会场双屏与讲台</t>
         </is>
       </c>
-      <c r="F16" s="60" t="inlineStr">
+      <c r="F16" s="49" t="inlineStr">
         <is>
           <t>主会场</t>
         </is>
       </c>
-      <c r="G16" s="60" t="inlineStr">
-        <is>
-          <t>否</t>
+      <c r="G16" s="49" t="inlineStr">
+        <is>
+          <t>四五级补充</t>
         </is>
       </c>
     </row>
     <row r="17" ht="22" customHeight="1" s="17">
-      <c r="A17" s="60" t="inlineStr">
+      <c r="A17" s="49" t="inlineStr">
         <is>
           <t>14</t>
         </is>
       </c>
-      <c r="B17" s="62" t="inlineStr">
+      <c r="B17" s="51" t="inlineStr">
         <is>
           <t>四级 主办致辞现场</t>
         </is>
       </c>
-      <c r="C17" s="62" t="inlineStr">
+      <c r="C17" s="51" t="inlineStr">
         <is>
           <t>941A7836.JPG</t>
         </is>
       </c>
-      <c r="D17" s="60" t="inlineStr">
+      <c r="D17" s="49" t="inlineStr">
         <is>
           <t>2026-05-22 13:39:31</t>
         </is>
       </c>
-      <c r="E17" s="62" t="inlineStr">
+      <c r="E17" s="51" t="inlineStr">
         <is>
           <t>主办致辞：姚志勇，主会场主视觉</t>
         </is>
       </c>
-      <c r="F17" s="60" t="inlineStr">
+      <c r="F17" s="49" t="inlineStr">
         <is>
           <t>主会场</t>
         </is>
       </c>
-      <c r="G17" s="60" t="inlineStr">
-        <is>
-          <t>否</t>
+      <c r="G17" s="49" t="inlineStr">
+        <is>
+          <t>四五级补充</t>
         </is>
       </c>
     </row>
     <row r="18" ht="22" customHeight="1" s="17">
-      <c r="A18" s="60" t="inlineStr">
+      <c r="A18" s="49" t="inlineStr">
         <is>
           <t>15</t>
         </is>
       </c>
-      <c r="B18" s="62" t="inlineStr">
+      <c r="B18" s="51" t="inlineStr">
         <is>
           <t>四级 主办致辞现场</t>
         </is>
       </c>
-      <c r="C18" s="62" t="inlineStr">
+      <c r="C18" s="51" t="inlineStr">
         <is>
           <t>941A7849.JPG</t>
         </is>
       </c>
-      <c r="D18" s="60" t="inlineStr">
+      <c r="D18" s="49" t="inlineStr">
         <is>
           <t>2026-05-22 13:40:40</t>
         </is>
       </c>
-      <c r="E18" s="62" t="inlineStr">
+      <c r="E18" s="51" t="inlineStr">
         <is>
           <t>主办致辞讲台特写</t>
         </is>
       </c>
-      <c r="F18" s="60" t="inlineStr">
+      <c r="F18" s="49" t="inlineStr">
         <is>
           <t>主会场</t>
         </is>
       </c>
-      <c r="G18" s="60" t="inlineStr">
-        <is>
-          <t>否</t>
+      <c r="G18" s="49" t="inlineStr">
+        <is>
+          <t>四五级补充</t>
         </is>
       </c>
     </row>
     <row r="19" ht="22" customHeight="1" s="17">
-      <c r="A19" s="60" t="inlineStr">
+      <c r="A19" s="49" t="inlineStr">
         <is>
           <t>16</t>
         </is>
       </c>
-      <c r="B19" s="62" t="inlineStr">
+      <c r="B19" s="51" t="inlineStr">
         <is>
           <t>五级 冠名晚宴氛围</t>
         </is>
       </c>
-      <c r="C19" s="62" t="inlineStr">
+      <c r="C19" s="51" t="inlineStr">
         <is>
           <t>941A8857.JPG</t>
         </is>
       </c>
-      <c r="D19" s="60" t="inlineStr">
+      <c r="D19" s="49" t="inlineStr">
         <is>
           <t>2026-05-22 20:25:29</t>
         </is>
       </c>
-      <c r="E19" s="62" t="inlineStr">
+      <c r="E19" s="51" t="inlineStr">
         <is>
           <t>冠名晚宴合影（江景厅）</t>
         </is>
       </c>
-      <c r="F19" s="60" t="inlineStr">
+      <c r="F19" s="49" t="inlineStr">
         <is>
           <t>晚宴冠名</t>
         </is>
       </c>
-      <c r="G19" s="60" t="inlineStr">
-        <is>
-          <t>否</t>
+      <c r="G19" s="49" t="inlineStr">
+        <is>
+          <t>四五级补充</t>
         </is>
       </c>
     </row>
     <row r="20" ht="22" customHeight="1" s="17">
-      <c r="A20" s="60" t="inlineStr">
+      <c r="A20" s="49" t="inlineStr">
         <is>
           <t>17</t>
         </is>
       </c>
-      <c r="B20" s="62" t="inlineStr">
+      <c r="B20" s="51" t="inlineStr">
         <is>
           <t>五级 冠名晚宴氛围</t>
         </is>
       </c>
-      <c r="C20" s="62" t="inlineStr">
+      <c r="C20" s="51" t="inlineStr">
         <is>
           <t>941A8881.JPG</t>
         </is>
       </c>
-      <c r="D20" s="60" t="inlineStr">
+      <c r="D20" s="49" t="inlineStr">
         <is>
           <t>2026-05-22 20:32:54</t>
         </is>
       </c>
-      <c r="E20" s="62" t="inlineStr">
+      <c r="E20" s="51" t="inlineStr">
         <is>
           <t>冠名晚宴桌次（江景厅圆桌）</t>
         </is>
       </c>
-      <c r="F20" s="60" t="inlineStr">
+      <c r="F20" s="49" t="inlineStr">
         <is>
           <t>晚宴冠名</t>
         </is>
       </c>
-      <c r="G20" s="60" t="inlineStr">
-        <is>
-          <t>否</t>
+      <c r="G20" s="49" t="inlineStr">
+        <is>
+          <t>四五级补充</t>
         </is>
       </c>
     </row>
     <row r="21" ht="22" customHeight="1" s="17">
-      <c r="A21" s="60" t="inlineStr">
+      <c r="A21" s="49" t="inlineStr">
         <is>
           <t>18</t>
         </is>
       </c>
-      <c r="B21" s="62" t="inlineStr">
+      <c r="B21" s="51" t="inlineStr">
         <is>
           <t>五级 冠名晚宴氛围</t>
         </is>
       </c>
-      <c r="C21" s="62" t="inlineStr">
+      <c r="C21" s="51" t="inlineStr">
         <is>
           <t>941A8859.JPG</t>
         </is>
       </c>
-      <c r="D21" s="60" t="inlineStr">
+      <c r="D21" s="49" t="inlineStr">
         <is>
           <t>2026-05-22 20:26:10</t>
         </is>
       </c>
-      <c r="E21" s="62" t="inlineStr">
+      <c r="E21" s="51" t="inlineStr">
         <is>
           <t>冠名晚宴现场举杯</t>
         </is>
       </c>
-      <c r="F21" s="60" t="inlineStr">
+      <c r="F21" s="49" t="inlineStr">
         <is>
           <t>晚宴冠名</t>
         </is>
       </c>
-      <c r="G21" s="60" t="inlineStr">
-        <is>
-          <t>否</t>
+      <c r="G21" s="49" t="inlineStr">
+        <is>
+          <t>四五级补充</t>
         </is>
       </c>
     </row>
